--- a/output/2025-07-11.xlsx
+++ b/output/2025-07-11.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.53</v>
+        <v>3.51</v>
       </c>
       <c r="F14" t="n">
-        <v>10.97</v>
+        <v>11.73</v>
       </c>
       <c r="G14" t="n">
-        <v>130.1</v>
+        <v>113.9</v>
       </c>
       <c r="H14" t="n">
-        <v>5.1</v>
+        <v>10.7</v>
       </c>
       <c r="I14" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>-43.15</v>
+        <v>-4.75</v>
       </c>
       <c r="K14" t="n">
-        <v>-38.48</v>
+        <v>-116.29</v>
       </c>
       <c r="L14" t="n">
-        <v>57.81</v>
+        <v>116.39</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:46:49</t>
+          <t>04:45:53</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.16</v>
+        <v>3.66</v>
       </c>
       <c r="F15" t="n">
-        <v>10.68</v>
+        <v>10.96</v>
       </c>
       <c r="G15" t="n">
-        <v>127.1</v>
+        <v>125.5</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3</v>
+        <v>11.2</v>
       </c>
       <c r="I15" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-17.26</v>
+        <v>-198.73</v>
       </c>
       <c r="K15" t="n">
-        <v>38.94</v>
+        <v>313.22</v>
       </c>
       <c r="L15" t="n">
-        <v>42.6</v>
+        <v>370.95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:48:03</t>
+          <t>04:48:29</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8</v>
+        <v>3.97</v>
       </c>
       <c r="F16" t="n">
-        <v>10.52</v>
+        <v>10.86</v>
       </c>
       <c r="G16" t="n">
-        <v>118.9</v>
+        <v>127.4</v>
       </c>
       <c r="H16" t="n">
-        <v>10.2</v>
+        <v>13.9</v>
       </c>
       <c r="I16" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-41.01</v>
+        <v>-176.18</v>
       </c>
       <c r="K16" t="n">
-        <v>18.65</v>
+        <v>316.39</v>
       </c>
       <c r="L16" t="n">
-        <v>45.05</v>
+        <v>362.14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:52:17</t>
+          <t>04:52:28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.67</v>
+        <v>3.97</v>
       </c>
       <c r="F17" t="n">
-        <v>11.69</v>
+        <v>11.28</v>
       </c>
       <c r="G17" t="n">
-        <v>120.2</v>
+        <v>122.8</v>
       </c>
       <c r="H17" t="n">
-        <v>18.2</v>
+        <v>11.9</v>
       </c>
       <c r="I17" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>74.69</v>
+        <v>-92.45</v>
       </c>
       <c r="K17" t="n">
-        <v>-10.26</v>
+        <v>176.85</v>
       </c>
       <c r="L17" t="n">
-        <v>75.39</v>
+        <v>199.55</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:53:54</t>
+          <t>04:54:18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.83</v>
+        <v>4.25</v>
       </c>
       <c r="F18" t="n">
-        <v>11.61</v>
+        <v>10.5</v>
       </c>
       <c r="G18" t="n">
-        <v>129.2</v>
+        <v>133.2</v>
       </c>
       <c r="H18" t="n">
-        <v>14.8</v>
+        <v>5.4</v>
       </c>
       <c r="I18" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>-81.12</v>
+        <v>61.46</v>
       </c>
       <c r="K18" t="n">
-        <v>-95.15000000000001</v>
+        <v>414.36</v>
       </c>
       <c r="L18" t="n">
-        <v>125.04</v>
+        <v>418.89</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:55:43</t>
+          <t>04:55:50</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.71</v>
+        <v>3.28</v>
       </c>
       <c r="F19" t="n">
-        <v>10.84</v>
+        <v>11.32</v>
       </c>
       <c r="G19" t="n">
-        <v>116.2</v>
+        <v>110.9</v>
       </c>
       <c r="H19" t="n">
-        <v>13.6</v>
+        <v>7.5</v>
       </c>
       <c r="I19" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>116.41</v>
+        <v>80.7</v>
       </c>
       <c r="K19" t="n">
-        <v>-99.38</v>
+        <v>-31.14</v>
       </c>
       <c r="L19" t="n">
-        <v>153.06</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:00:59</t>
+          <t>05:00:12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.73</v>
+        <v>4.12</v>
       </c>
       <c r="F20" t="n">
-        <v>10.41</v>
+        <v>10.12</v>
       </c>
       <c r="G20" t="n">
-        <v>115.1</v>
+        <v>138.3</v>
       </c>
       <c r="H20" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="I20" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-34.29</v>
+        <v>-4.54</v>
       </c>
       <c r="K20" t="n">
-        <v>252.48</v>
+        <v>-107.38</v>
       </c>
       <c r="L20" t="n">
-        <v>254.8</v>
+        <v>107.48</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:02:07</t>
+          <t>05:02:21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.88</v>
+        <v>3.05</v>
       </c>
       <c r="F21" t="n">
-        <v>11.47</v>
+        <v>10.63</v>
       </c>
       <c r="G21" t="n">
-        <v>116.5</v>
+        <v>121.7</v>
       </c>
       <c r="H21" t="n">
-        <v>12.6</v>
+        <v>14.9</v>
       </c>
       <c r="I21" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-67.38</v>
+        <v>-201.35</v>
       </c>
       <c r="K21" t="n">
-        <v>-98.54000000000001</v>
+        <v>-381.81</v>
       </c>
       <c r="L21" t="n">
-        <v>119.37</v>
+        <v>431.65</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:04:37</t>
+          <t>05:04:45</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>4.22</v>
+        <v>3.94</v>
       </c>
       <c r="F22" t="n">
-        <v>10.66</v>
+        <v>11.05</v>
       </c>
       <c r="G22" t="n">
-        <v>126.2</v>
+        <v>105.6</v>
       </c>
       <c r="H22" t="n">
-        <v>21.7</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>129.73</v>
+        <v>-124.47</v>
       </c>
       <c r="K22" t="n">
-        <v>336.97</v>
+        <v>-19.14</v>
       </c>
       <c r="L22" t="n">
-        <v>361.07</v>
+        <v>125.94</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:08:30</t>
+          <t>05:07:46</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.86</v>
+        <v>4.29</v>
       </c>
       <c r="F23" t="n">
-        <v>11.53</v>
+        <v>10.25</v>
       </c>
       <c r="G23" t="n">
-        <v>114.9</v>
+        <v>118.9</v>
       </c>
       <c r="H23" t="n">
-        <v>12.6</v>
+        <v>6.7</v>
       </c>
       <c r="I23" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>289.82</v>
+        <v>389.99</v>
       </c>
       <c r="K23" t="n">
-        <v>-45.84</v>
+        <v>-166.55</v>
       </c>
       <c r="L23" t="n">
-        <v>293.43</v>
+        <v>424.06</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:10:56</t>
+          <t>05:09:58</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="F24" t="n">
-        <v>10.92</v>
+        <v>11.9</v>
       </c>
       <c r="G24" t="n">
-        <v>120.5</v>
+        <v>138.9</v>
       </c>
       <c r="H24" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="I24" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>99.94</v>
+        <v>-365.69</v>
       </c>
       <c r="K24" t="n">
-        <v>52.54</v>
+        <v>-210.95</v>
       </c>
       <c r="L24" t="n">
-        <v>112.91</v>
+        <v>422.17</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:12:10</t>
+          <t>05:10:26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.64</v>
+        <v>3.83</v>
       </c>
       <c r="F25" t="n">
-        <v>10.77</v>
+        <v>10.94</v>
       </c>
       <c r="G25" t="n">
-        <v>127.6</v>
+        <v>118.7</v>
       </c>
       <c r="H25" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="I25" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>248.4</v>
+        <v>176.69</v>
       </c>
       <c r="K25" t="n">
-        <v>-212.84</v>
+        <v>687.01</v>
       </c>
       <c r="L25" t="n">
-        <v>327.12</v>
+        <v>709.37</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:17:53</t>
+          <t>05:16:33</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.18</v>
+        <v>3.82</v>
       </c>
       <c r="F26" t="n">
-        <v>10.52</v>
+        <v>10.65</v>
       </c>
       <c r="G26" t="n">
-        <v>120.1</v>
+        <v>123.5</v>
       </c>
       <c r="H26" t="n">
-        <v>16.7</v>
+        <v>7</v>
       </c>
       <c r="I26" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>330.91</v>
+        <v>-927.45</v>
       </c>
       <c r="K26" t="n">
-        <v>-259.53</v>
+        <v>-129.59</v>
       </c>
       <c r="L26" t="n">
-        <v>420.54</v>
+        <v>936.46</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:19:54</t>
+          <t>05:18:23</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.57</v>
+        <v>3.61</v>
       </c>
       <c r="F27" t="n">
-        <v>11.58</v>
+        <v>10.79</v>
       </c>
       <c r="G27" t="n">
-        <v>129.4</v>
+        <v>134.5</v>
       </c>
       <c r="H27" t="n">
-        <v>7.3</v>
+        <v>13.9</v>
       </c>
       <c r="I27" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>187.03</v>
+        <v>-624.58</v>
       </c>
       <c r="K27" t="n">
-        <v>6.76</v>
+        <v>-191.56</v>
       </c>
       <c r="L27" t="n">
-        <v>187.16</v>
+        <v>653.29</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:22:08</t>
+          <t>05:19:57</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.63</v>
+        <v>3.74</v>
       </c>
       <c r="F28" t="n">
-        <v>10.79</v>
+        <v>10.64</v>
       </c>
       <c r="G28" t="n">
-        <v>126.5</v>
+        <v>126.7</v>
       </c>
       <c r="H28" t="n">
-        <v>4.9</v>
+        <v>14.2</v>
       </c>
       <c r="I28" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>-130.21</v>
+        <v>-117.82</v>
       </c>
       <c r="K28" t="n">
-        <v>393.87</v>
+        <v>206.97</v>
       </c>
       <c r="L28" t="n">
-        <v>414.83</v>
+        <v>238.15</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:31:00</t>
+          <t>05:29:35</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>4.16</v>
+        <v>3.65</v>
       </c>
       <c r="F29" t="n">
-        <v>11.81</v>
+        <v>11.23</v>
       </c>
       <c r="G29" t="n">
-        <v>121.9</v>
+        <v>124.3</v>
       </c>
       <c r="H29" t="n">
-        <v>9.9</v>
+        <v>13.1</v>
       </c>
       <c r="I29" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J29" t="n">
-        <v>-25.4</v>
+        <v>-299.6</v>
       </c>
       <c r="K29" t="n">
-        <v>45.07</v>
+        <v>-12.18</v>
       </c>
       <c r="L29" t="n">
-        <v>51.73</v>
+        <v>299.85</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:33:30</t>
+          <t>05:30:39</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.96</v>
+        <v>3.39</v>
       </c>
       <c r="F30" t="n">
-        <v>10.75</v>
+        <v>10.79</v>
       </c>
       <c r="G30" t="n">
-        <v>131.7</v>
+        <v>121.2</v>
       </c>
       <c r="H30" t="n">
-        <v>9</v>
+        <v>12.2</v>
       </c>
       <c r="I30" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>66.20999999999999</v>
+        <v>-160.76</v>
       </c>
       <c r="K30" t="n">
-        <v>39.26</v>
+        <v>41.13</v>
       </c>
       <c r="L30" t="n">
-        <v>76.98</v>
+        <v>165.93</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:34:14</t>
+          <t>05:32:38</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="F31" t="n">
-        <v>10.67</v>
+        <v>10.88</v>
       </c>
       <c r="G31" t="n">
-        <v>99.3</v>
+        <v>119</v>
       </c>
       <c r="H31" t="n">
-        <v>10.2</v>
+        <v>7.1</v>
       </c>
       <c r="I31" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>69.91</v>
+        <v>116.21</v>
       </c>
       <c r="K31" t="n">
-        <v>27.7</v>
+        <v>-65.84999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>75.2</v>
+        <v>133.57</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:38:17</t>
+          <t>05:37:08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.99</v>
+        <v>3.55</v>
       </c>
       <c r="F32" t="n">
-        <v>11.08</v>
+        <v>10.76</v>
       </c>
       <c r="G32" t="n">
-        <v>125.9</v>
+        <v>125.2</v>
       </c>
       <c r="H32" t="n">
-        <v>14.3</v>
+        <v>4.7</v>
       </c>
       <c r="I32" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>30.86</v>
+        <v>152.57</v>
       </c>
       <c r="K32" t="n">
-        <v>19.47</v>
+        <v>-125.41</v>
       </c>
       <c r="L32" t="n">
-        <v>36.49</v>
+        <v>197.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:40:22</t>
+          <t>05:38:10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.75</v>
+        <v>4.07</v>
       </c>
       <c r="F33" t="n">
-        <v>11.42</v>
+        <v>10.56</v>
       </c>
       <c r="G33" t="n">
-        <v>130.4</v>
+        <v>134.3</v>
       </c>
       <c r="H33" t="n">
-        <v>14.5</v>
+        <v>9.1</v>
       </c>
       <c r="I33" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>65.78</v>
+        <v>-122.2</v>
       </c>
       <c r="K33" t="n">
-        <v>49.2</v>
+        <v>363.44</v>
       </c>
       <c r="L33" t="n">
-        <v>82.14</v>
+        <v>383.44</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:42:28</t>
+          <t>05:40:12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1468,31 +1468,31 @@
         <v>3.48</v>
       </c>
       <c r="F34" t="n">
-        <v>11.11</v>
+        <v>10.57</v>
       </c>
       <c r="G34" t="n">
-        <v>130.4</v>
+        <v>123.3</v>
       </c>
       <c r="H34" t="n">
-        <v>6.9</v>
+        <v>3.2</v>
       </c>
       <c r="I34" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>7.47</v>
+        <v>195.13</v>
       </c>
       <c r="K34" t="n">
-        <v>2.83</v>
+        <v>-196.66</v>
       </c>
       <c r="L34" t="n">
-        <v>7.99</v>
+        <v>277.04</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:46:43</t>
+          <t>05:45:13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.39</v>
+        <v>3.49</v>
       </c>
       <c r="F35" t="n">
-        <v>10.82</v>
+        <v>10.69</v>
       </c>
       <c r="G35" t="n">
-        <v>127.5</v>
+        <v>135.2</v>
       </c>
       <c r="H35" t="n">
-        <v>12.8</v>
+        <v>13.5</v>
       </c>
       <c r="I35" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>131.97</v>
+        <v>-179</v>
       </c>
       <c r="K35" t="n">
-        <v>-14.8</v>
+        <v>-198.79</v>
       </c>
       <c r="L35" t="n">
-        <v>132.8</v>
+        <v>267.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:47:44</t>
+          <t>05:46:51</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.11</v>
+        <v>3.51</v>
       </c>
       <c r="F36" t="n">
-        <v>10.53</v>
+        <v>11.09</v>
       </c>
       <c r="G36" t="n">
-        <v>126.2</v>
+        <v>118.3</v>
       </c>
       <c r="H36" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I36" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-48.95</v>
+        <v>72.08</v>
       </c>
       <c r="K36" t="n">
-        <v>-114.23</v>
+        <v>-267.89</v>
       </c>
       <c r="L36" t="n">
-        <v>124.28</v>
+        <v>277.42</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:48:58</t>
+          <t>05:49:07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.52</v>
+        <v>3.53</v>
       </c>
       <c r="F37" t="n">
-        <v>11.65</v>
+        <v>10.71</v>
       </c>
       <c r="G37" t="n">
-        <v>139.6</v>
+        <v>123.7</v>
       </c>
       <c r="H37" t="n">
-        <v>9.300000000000001</v>
+        <v>11.4</v>
       </c>
       <c r="I37" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>-35.78</v>
+        <v>463.21</v>
       </c>
       <c r="K37" t="n">
-        <v>-25.4</v>
+        <v>-18.91</v>
       </c>
       <c r="L37" t="n">
-        <v>43.87</v>
+        <v>463.6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:54:28</t>
+          <t>05:54:06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.75</v>
+        <v>3.22</v>
       </c>
       <c r="F38" t="n">
-        <v>10.68</v>
+        <v>10.66</v>
       </c>
       <c r="G38" t="n">
-        <v>136.5</v>
+        <v>121.5</v>
       </c>
       <c r="H38" t="n">
-        <v>10.3</v>
+        <v>11.6</v>
       </c>
       <c r="I38" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>200.1</v>
+        <v>56.8</v>
       </c>
       <c r="K38" t="n">
-        <v>116.18</v>
+        <v>-469.58</v>
       </c>
       <c r="L38" t="n">
-        <v>231.39</v>
+        <v>473.01</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:55:39</t>
+          <t>05:56:16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.68</v>
+        <v>3.78</v>
       </c>
       <c r="F39" t="n">
-        <v>11.39</v>
+        <v>10.47</v>
       </c>
       <c r="G39" t="n">
-        <v>129.5</v>
+        <v>133.1</v>
       </c>
       <c r="H39" t="n">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="I39" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>221.71</v>
+        <v>288.77</v>
       </c>
       <c r="K39" t="n">
-        <v>223.71</v>
+        <v>22.31</v>
       </c>
       <c r="L39" t="n">
-        <v>314.96</v>
+        <v>289.63</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:56:51</t>
+          <t>05:57:05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.18</v>
+        <v>4.23</v>
       </c>
       <c r="F40" t="n">
-        <v>11.25</v>
+        <v>12.32</v>
       </c>
       <c r="G40" t="n">
-        <v>119.7</v>
+        <v>121.3</v>
       </c>
       <c r="H40" t="n">
-        <v>9.1</v>
+        <v>6.2</v>
       </c>
       <c r="I40" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-36.15</v>
+        <v>322.19</v>
       </c>
       <c r="K40" t="n">
-        <v>-101.96</v>
+        <v>222.53</v>
       </c>
       <c r="L40" t="n">
-        <v>108.18</v>
+        <v>391.57</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:01:09</t>
+          <t>06:02:19</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.48</v>
+        <v>3.84</v>
       </c>
       <c r="F41" t="n">
-        <v>10.93</v>
+        <v>11.41</v>
       </c>
       <c r="G41" t="n">
-        <v>128.1</v>
+        <v>128.4</v>
       </c>
       <c r="H41" t="n">
-        <v>11.2</v>
+        <v>10.5</v>
       </c>
       <c r="I41" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>115.65</v>
+        <v>-426.86</v>
       </c>
       <c r="K41" t="n">
-        <v>451.41</v>
+        <v>-519.36</v>
       </c>
       <c r="L41" t="n">
-        <v>465.99</v>
+        <v>672.26</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:02:20</t>
+          <t>06:03:14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.69</v>
+        <v>4</v>
       </c>
       <c r="F42" t="n">
-        <v>11.31</v>
+        <v>11.11</v>
       </c>
       <c r="G42" t="n">
-        <v>116.5</v>
+        <v>140.3</v>
       </c>
       <c r="H42" t="n">
-        <v>6.7</v>
+        <v>5.6</v>
       </c>
       <c r="I42" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>121.27</v>
+        <v>-38.06</v>
       </c>
       <c r="K42" t="n">
-        <v>-375.55</v>
+        <v>362.29</v>
       </c>
       <c r="L42" t="n">
-        <v>394.64</v>
+        <v>364.28</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:03:47</t>
+          <t>06:04:21</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="F43" t="n">
-        <v>10.77</v>
+        <v>11.22</v>
       </c>
       <c r="G43" t="n">
-        <v>114</v>
+        <v>119.1</v>
       </c>
       <c r="H43" t="n">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="I43" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>268.75</v>
+        <v>607.13</v>
       </c>
       <c r="K43" t="n">
-        <v>482.59</v>
+        <v>-205.67</v>
       </c>
       <c r="L43" t="n">
-        <v>552.37</v>
+        <v>641.02</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:15:19</t>
+          <t>06:13:29</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.17</v>
+        <v>4.23</v>
       </c>
       <c r="F44" t="n">
-        <v>10.19</v>
+        <v>10.77</v>
       </c>
       <c r="G44" t="n">
-        <v>123.9</v>
+        <v>136</v>
       </c>
       <c r="H44" t="n">
-        <v>10.3</v>
+        <v>14.1</v>
       </c>
       <c r="I44" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>7.71</v>
+        <v>53.4</v>
       </c>
       <c r="K44" t="n">
-        <v>-39.98</v>
+        <v>91.19</v>
       </c>
       <c r="L44" t="n">
-        <v>40.72</v>
+        <v>105.68</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:16:10</t>
+          <t>06:14:07</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.24</v>
+        <v>4.3</v>
       </c>
       <c r="F45" t="n">
-        <v>10.65</v>
+        <v>10.98</v>
       </c>
       <c r="G45" t="n">
-        <v>112.8</v>
+        <v>114.8</v>
       </c>
       <c r="H45" t="n">
-        <v>8.1</v>
+        <v>12.1</v>
       </c>
       <c r="I45" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>43.15</v>
+        <v>1.73</v>
       </c>
       <c r="K45" t="n">
-        <v>-9.470000000000001</v>
+        <v>179.3</v>
       </c>
       <c r="L45" t="n">
-        <v>44.18</v>
+        <v>179.31</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:17:59</t>
+          <t>06:15:44</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.36</v>
+        <v>3.85</v>
       </c>
       <c r="F46" t="n">
-        <v>11.1</v>
+        <v>10.78</v>
       </c>
       <c r="G46" t="n">
-        <v>120.8</v>
+        <v>129.6</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="I46" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>-28.44</v>
+        <v>-197.75</v>
       </c>
       <c r="K46" t="n">
-        <v>-20.62</v>
+        <v>60.66</v>
       </c>
       <c r="L46" t="n">
-        <v>35.13</v>
+        <v>206.85</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:23:03</t>
+          <t>06:20:11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.1</v>
+        <v>4.02</v>
       </c>
       <c r="F47" t="n">
-        <v>11.25</v>
+        <v>10.09</v>
       </c>
       <c r="G47" t="n">
-        <v>124.8</v>
+        <v>137.1</v>
       </c>
       <c r="H47" t="n">
-        <v>10.8</v>
+        <v>12.5</v>
       </c>
       <c r="I47" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>37</v>
+        <v>-325.09</v>
       </c>
       <c r="K47" t="n">
-        <v>-98.22</v>
+        <v>-164.4</v>
       </c>
       <c r="L47" t="n">
-        <v>104.96</v>
+        <v>364.29</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:24:44</t>
+          <t>06:22:29</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="F48" t="n">
-        <v>10.53</v>
+        <v>11.11</v>
       </c>
       <c r="G48" t="n">
-        <v>111.7</v>
+        <v>132.2</v>
       </c>
       <c r="H48" t="n">
-        <v>5.3</v>
+        <v>10.9</v>
       </c>
       <c r="I48" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-45.58</v>
+        <v>-161.54</v>
       </c>
       <c r="K48" t="n">
-        <v>-85.03</v>
+        <v>158.64</v>
       </c>
       <c r="L48" t="n">
-        <v>96.48</v>
+        <v>226.4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:25:45</t>
+          <t>06:23:17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.3</v>
+        <v>2.72</v>
       </c>
       <c r="F49" t="n">
-        <v>11.13</v>
+        <v>10.28</v>
       </c>
       <c r="G49" t="n">
-        <v>126.1</v>
+        <v>142.8</v>
       </c>
       <c r="H49" t="n">
-        <v>14.1</v>
+        <v>12.4</v>
       </c>
       <c r="I49" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>144.25</v>
+        <v>29.7</v>
       </c>
       <c r="K49" t="n">
-        <v>-65.20999999999999</v>
+        <v>41.57</v>
       </c>
       <c r="L49" t="n">
-        <v>158.31</v>
+        <v>51.09</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:28:55</t>
+          <t>06:27:18</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.92</v>
+        <v>4.41</v>
       </c>
       <c r="F50" t="n">
-        <v>10.93</v>
+        <v>10.47</v>
       </c>
       <c r="G50" t="n">
-        <v>123.8</v>
+        <v>124.5</v>
       </c>
       <c r="H50" t="n">
-        <v>9.300000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="I50" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>-142.81</v>
+        <v>300.62</v>
       </c>
       <c r="K50" t="n">
-        <v>-55.99</v>
+        <v>263.14</v>
       </c>
       <c r="L50" t="n">
-        <v>153.39</v>
+        <v>399.52</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:30:12</t>
+          <t>06:27:54</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.09</v>
+        <v>4.17</v>
       </c>
       <c r="F51" t="n">
-        <v>11.28</v>
+        <v>11.43</v>
       </c>
       <c r="G51" t="n">
-        <v>122.8</v>
+        <v>127.7</v>
       </c>
       <c r="H51" t="n">
-        <v>12.8</v>
+        <v>6.8</v>
       </c>
       <c r="I51" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>13.08</v>
+        <v>-139.98</v>
       </c>
       <c r="K51" t="n">
-        <v>29.26</v>
+        <v>-392.93</v>
       </c>
       <c r="L51" t="n">
-        <v>32.05</v>
+        <v>417.12</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:31:29</t>
+          <t>06:30:11</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.68</v>
+        <v>3.42</v>
       </c>
       <c r="F52" t="n">
-        <v>10.72</v>
+        <v>10.79</v>
       </c>
       <c r="G52" t="n">
-        <v>124</v>
+        <v>116.6</v>
       </c>
       <c r="H52" t="n">
-        <v>12.3</v>
+        <v>2.3</v>
       </c>
       <c r="I52" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>-72.09999999999999</v>
+        <v>-89.72</v>
       </c>
       <c r="K52" t="n">
-        <v>58.99</v>
+        <v>-384.96</v>
       </c>
       <c r="L52" t="n">
-        <v>93.15000000000001</v>
+        <v>395.28</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:36:45</t>
+          <t>06:35:11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.02</v>
+        <v>3.98</v>
       </c>
       <c r="F53" t="n">
-        <v>11.31</v>
+        <v>10.44</v>
       </c>
       <c r="G53" t="n">
-        <v>135.2</v>
+        <v>133.5</v>
       </c>
       <c r="H53" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="I53" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>114.02</v>
+        <v>220.87</v>
       </c>
       <c r="K53" t="n">
-        <v>-50.72</v>
+        <v>-275.45</v>
       </c>
       <c r="L53" t="n">
-        <v>124.79</v>
+        <v>353.07</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:38:48</t>
+          <t>06:37:21</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.98</v>
+        <v>4.47</v>
       </c>
       <c r="F54" t="n">
-        <v>10.87</v>
+        <v>10.33</v>
       </c>
       <c r="G54" t="n">
-        <v>125.6</v>
+        <v>131.3</v>
       </c>
       <c r="H54" t="n">
-        <v>10.8</v>
+        <v>9</v>
       </c>
       <c r="I54" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>238.5</v>
+        <v>-93.13</v>
       </c>
       <c r="K54" t="n">
-        <v>59.34</v>
+        <v>353.77</v>
       </c>
       <c r="L54" t="n">
-        <v>245.78</v>
+        <v>365.83</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:41:13</t>
+          <t>06:40:05</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="F55" t="n">
-        <v>11.57</v>
+        <v>11.1</v>
       </c>
       <c r="G55" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="H55" t="n">
-        <v>7.4</v>
+        <v>11.1</v>
       </c>
       <c r="I55" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>184.17</v>
+        <v>-74.91</v>
       </c>
       <c r="K55" t="n">
-        <v>86.78</v>
+        <v>143.66</v>
       </c>
       <c r="L55" t="n">
-        <v>203.59</v>
+        <v>162.01</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:47:16</t>
+          <t>06:45:01</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.3</v>
+        <v>4.76</v>
       </c>
       <c r="F56" t="n">
-        <v>10.46</v>
+        <v>10.52</v>
       </c>
       <c r="G56" t="n">
-        <v>141.1</v>
+        <v>119.7</v>
       </c>
       <c r="H56" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>-316.78</v>
+        <v>55.65</v>
       </c>
       <c r="K56" t="n">
-        <v>173.03</v>
+        <v>480.5</v>
       </c>
       <c r="L56" t="n">
-        <v>360.96</v>
+        <v>483.72</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:49:42</t>
+          <t>06:47:34</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.02</v>
+        <v>4.18</v>
       </c>
       <c r="F57" t="n">
-        <v>10.96</v>
+        <v>10.42</v>
       </c>
       <c r="G57" t="n">
-        <v>131.2</v>
+        <v>135.9</v>
       </c>
       <c r="H57" t="n">
-        <v>10.8</v>
+        <v>11.4</v>
       </c>
       <c r="I57" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>-31.64</v>
+        <v>303.04</v>
       </c>
       <c r="K57" t="n">
-        <v>-469.56</v>
+        <v>-30.3</v>
       </c>
       <c r="L57" t="n">
-        <v>470.62</v>
+        <v>304.55</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:51:32</t>
+          <t>06:48:37</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.99</v>
+        <v>4.47</v>
       </c>
       <c r="F58" t="n">
-        <v>10.99</v>
+        <v>11.31</v>
       </c>
       <c r="G58" t="n">
-        <v>116.3</v>
+        <v>131.5</v>
       </c>
       <c r="H58" t="n">
-        <v>9.300000000000001</v>
+        <v>11</v>
       </c>
       <c r="I58" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>249.53</v>
+        <v>-96.15000000000001</v>
       </c>
       <c r="K58" t="n">
-        <v>285.27</v>
+        <v>427.36</v>
       </c>
       <c r="L58" t="n">
-        <v>379</v>
+        <v>438.04</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:04:59</t>
+          <t>06:58:36</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.17</v>
+        <v>3.73</v>
       </c>
       <c r="F59" t="n">
-        <v>10.31</v>
+        <v>10.63</v>
       </c>
       <c r="G59" t="n">
-        <v>124.5</v>
+        <v>134.9</v>
       </c>
       <c r="H59" t="n">
-        <v>8.1</v>
+        <v>12.3</v>
       </c>
       <c r="I59" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>75.06</v>
+        <v>-68.75</v>
       </c>
       <c r="K59" t="n">
-        <v>59.42</v>
+        <v>157.61</v>
       </c>
       <c r="L59" t="n">
-        <v>95.73</v>
+        <v>171.95</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:05:58</t>
+          <t>07:01:04</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.91</v>
+        <v>4.5</v>
       </c>
       <c r="F60" t="n">
-        <v>11.39</v>
+        <v>11.02</v>
       </c>
       <c r="G60" t="n">
-        <v>131.1</v>
+        <v>134.2</v>
       </c>
       <c r="H60" t="n">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>-2.39</v>
+        <v>167.78</v>
       </c>
       <c r="K60" t="n">
-        <v>-38.9</v>
+        <v>-65.78</v>
       </c>
       <c r="L60" t="n">
-        <v>38.98</v>
+        <v>180.21</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:07:25</t>
+          <t>07:02:40</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4</v>
+        <v>3.79</v>
       </c>
       <c r="F61" t="n">
-        <v>11.13</v>
+        <v>11.16</v>
       </c>
       <c r="G61" t="n">
-        <v>113.7</v>
+        <v>138.1</v>
       </c>
       <c r="H61" t="n">
-        <v>12.6</v>
+        <v>12.9</v>
       </c>
       <c r="I61" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>26.22</v>
+        <v>140.87</v>
       </c>
       <c r="K61" t="n">
-        <v>-139.4</v>
+        <v>-154.45</v>
       </c>
       <c r="L61" t="n">
-        <v>141.85</v>
+        <v>209.05</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:11:39</t>
+          <t>07:07:50</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.1</v>
+        <v>4.52</v>
       </c>
       <c r="F62" t="n">
-        <v>10.51</v>
+        <v>11.25</v>
       </c>
       <c r="G62" t="n">
-        <v>126.5</v>
+        <v>117.3</v>
       </c>
       <c r="H62" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="I62" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>66.55</v>
+        <v>-9.09</v>
       </c>
       <c r="K62" t="n">
-        <v>28.69</v>
+        <v>-343.89</v>
       </c>
       <c r="L62" t="n">
-        <v>72.47</v>
+        <v>344.01</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:13:16</t>
+          <t>07:10:12</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.71</v>
+        <v>3.88</v>
       </c>
       <c r="F63" t="n">
-        <v>11.09</v>
+        <v>10.83</v>
       </c>
       <c r="G63" t="n">
-        <v>128.2</v>
+        <v>103.8</v>
       </c>
       <c r="H63" t="n">
-        <v>10.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-59.38</v>
+        <v>-165.65</v>
       </c>
       <c r="K63" t="n">
-        <v>-96.83</v>
+        <v>164.99</v>
       </c>
       <c r="L63" t="n">
-        <v>113.59</v>
+        <v>233.79</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:14:21</t>
+          <t>07:11:18</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.7</v>
+        <v>3.44</v>
       </c>
       <c r="F64" t="n">
-        <v>11.96</v>
+        <v>10.61</v>
       </c>
       <c r="G64" t="n">
-        <v>122.8</v>
+        <v>119.4</v>
       </c>
       <c r="H64" t="n">
-        <v>16.6</v>
+        <v>7.4</v>
       </c>
       <c r="I64" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>24.29</v>
+        <v>78.09</v>
       </c>
       <c r="K64" t="n">
-        <v>-12.46</v>
+        <v>-290.88</v>
       </c>
       <c r="L64" t="n">
-        <v>27.3</v>
+        <v>301.18</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:18:24</t>
+          <t>07:15:19</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.88</v>
+        <v>4.45</v>
       </c>
       <c r="F65" t="n">
-        <v>11.57</v>
+        <v>10.49</v>
       </c>
       <c r="G65" t="n">
-        <v>132.2</v>
+        <v>121.3</v>
       </c>
       <c r="H65" t="n">
-        <v>12.7</v>
+        <v>4.7</v>
       </c>
       <c r="I65" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>-11.98</v>
+        <v>-31.4</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.97</v>
+        <v>-352.73</v>
       </c>
       <c r="L65" t="n">
-        <v>12.02</v>
+        <v>354.13</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:20:23</t>
+          <t>07:16:51</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.53</v>
+        <v>4.16</v>
       </c>
       <c r="F66" t="n">
-        <v>10.86</v>
+        <v>11.47</v>
       </c>
       <c r="G66" t="n">
-        <v>144.4</v>
+        <v>132.4</v>
       </c>
       <c r="H66" t="n">
-        <v>8.800000000000001</v>
+        <v>20.2</v>
       </c>
       <c r="I66" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-186.73</v>
+        <v>-489.57</v>
       </c>
       <c r="K66" t="n">
-        <v>141.16</v>
+        <v>-95.18000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>234.08</v>
+        <v>498.73</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:22:53</t>
+          <t>07:18:29</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.33</v>
+        <v>4.69</v>
       </c>
       <c r="F67" t="n">
-        <v>11.71</v>
+        <v>10.92</v>
       </c>
       <c r="G67" t="n">
-        <v>108.7</v>
+        <v>129.4</v>
       </c>
       <c r="H67" t="n">
-        <v>12.6</v>
+        <v>7.1</v>
       </c>
       <c r="I67" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-260.89</v>
+        <v>195.46</v>
       </c>
       <c r="K67" t="n">
-        <v>-21</v>
+        <v>713.23</v>
       </c>
       <c r="L67" t="n">
-        <v>261.73</v>
+        <v>739.53</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:26:07</t>
+          <t>07:23:10</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.52</v>
+        <v>4.53</v>
       </c>
       <c r="F68" t="n">
-        <v>11.28</v>
+        <v>10.62</v>
       </c>
       <c r="G68" t="n">
-        <v>136.6</v>
+        <v>133.6</v>
       </c>
       <c r="H68" t="n">
-        <v>12.4</v>
+        <v>2</v>
       </c>
       <c r="I68" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>127.45</v>
+        <v>594.09</v>
       </c>
       <c r="K68" t="n">
-        <v>161.35</v>
+        <v>196.28</v>
       </c>
       <c r="L68" t="n">
-        <v>205.62</v>
+        <v>625.67</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:27:21</t>
+          <t>07:24:39</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.14</v>
+        <v>3.81</v>
       </c>
       <c r="F69" t="n">
-        <v>10.62</v>
+        <v>11.57</v>
       </c>
       <c r="G69" t="n">
-        <v>139.7</v>
+        <v>128.2</v>
       </c>
       <c r="H69" t="n">
-        <v>10</v>
+        <v>12.4</v>
       </c>
       <c r="I69" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>-70.81999999999999</v>
+        <v>-276.92</v>
       </c>
       <c r="K69" t="n">
-        <v>80.42</v>
+        <v>146.3</v>
       </c>
       <c r="L69" t="n">
-        <v>107.16</v>
+        <v>313.19</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:29:38</t>
+          <t>07:26:05</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.81</v>
+        <v>4.24</v>
       </c>
       <c r="F70" t="n">
-        <v>10.91</v>
+        <v>10.77</v>
       </c>
       <c r="G70" t="n">
-        <v>117.9</v>
+        <v>128.9</v>
       </c>
       <c r="H70" t="n">
-        <v>9.9</v>
+        <v>13.2</v>
       </c>
       <c r="I70" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>456.1</v>
+        <v>-108.83</v>
       </c>
       <c r="K70" t="n">
-        <v>-194.81</v>
+        <v>-395.24</v>
       </c>
       <c r="L70" t="n">
-        <v>495.96</v>
+        <v>409.95</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:35:15</t>
+          <t>07:29:39</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.81</v>
+        <v>4.06</v>
       </c>
       <c r="F71" t="n">
-        <v>11.26</v>
+        <v>11.38</v>
       </c>
       <c r="G71" t="n">
-        <v>133.6</v>
+        <v>125.4</v>
       </c>
       <c r="H71" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I71" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>-125.58</v>
+        <v>-386.67</v>
       </c>
       <c r="K71" t="n">
-        <v>-102.46</v>
+        <v>851.17</v>
       </c>
       <c r="L71" t="n">
-        <v>162.07</v>
+        <v>934.88</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:37:21</t>
+          <t>07:31:44</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.41</v>
+        <v>3.24</v>
       </c>
       <c r="F72" t="n">
-        <v>10.69</v>
+        <v>11.09</v>
       </c>
       <c r="G72" t="n">
-        <v>142.7</v>
+        <v>137.7</v>
       </c>
       <c r="H72" t="n">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="I72" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>-238.22</v>
+        <v>60.67</v>
       </c>
       <c r="K72" t="n">
-        <v>-265.02</v>
+        <v>-371.94</v>
       </c>
       <c r="L72" t="n">
-        <v>356.35</v>
+        <v>376.86</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:39:23</t>
+          <t>07:33:02</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.38</v>
+        <v>3.5</v>
       </c>
       <c r="F73" t="n">
-        <v>11.65</v>
+        <v>11.42</v>
       </c>
       <c r="G73" t="n">
-        <v>126</v>
+        <v>134.8</v>
       </c>
       <c r="H73" t="n">
-        <v>4.6</v>
+        <v>7.7</v>
       </c>
       <c r="I73" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>406.71</v>
+        <v>-130.97</v>
       </c>
       <c r="K73" t="n">
-        <v>-140.95</v>
+        <v>-741.23</v>
       </c>
       <c r="L73" t="n">
-        <v>430.44</v>
+        <v>752.71</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:47:21</t>
+          <t>07:42:44</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.35</v>
+        <v>3.41</v>
       </c>
       <c r="F74" t="n">
-        <v>11.01</v>
+        <v>11.07</v>
       </c>
       <c r="G74" t="n">
-        <v>115.4</v>
+        <v>127.9</v>
       </c>
       <c r="H74" t="n">
-        <v>3.9</v>
+        <v>12.9</v>
       </c>
       <c r="I74" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>-93.01000000000001</v>
+        <v>185.41</v>
       </c>
       <c r="K74" t="n">
-        <v>30.52</v>
+        <v>-224.22</v>
       </c>
       <c r="L74" t="n">
-        <v>97.89</v>
+        <v>290.95</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:49:19</t>
+          <t>07:44:55</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.18</v>
+        <v>3.97</v>
       </c>
       <c r="F75" t="n">
-        <v>10.96</v>
+        <v>11.22</v>
       </c>
       <c r="G75" t="n">
-        <v>107.4</v>
+        <v>120.8</v>
       </c>
       <c r="H75" t="n">
-        <v>8.5</v>
+        <v>9.4</v>
       </c>
       <c r="I75" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-8.640000000000001</v>
+        <v>-24.19</v>
       </c>
       <c r="K75" t="n">
-        <v>123.55</v>
+        <v>84.87</v>
       </c>
       <c r="L75" t="n">
-        <v>123.85</v>
+        <v>88.25</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:51:54</t>
+          <t>07:46:51</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.48</v>
+        <v>4.02</v>
       </c>
       <c r="F76" t="n">
-        <v>10.56</v>
+        <v>10.33</v>
       </c>
       <c r="G76" t="n">
-        <v>131.8</v>
+        <v>110.9</v>
       </c>
       <c r="H76" t="n">
-        <v>4.7</v>
+        <v>10.3</v>
       </c>
       <c r="I76" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>2.23</v>
+        <v>-101.55</v>
       </c>
       <c r="K76" t="n">
-        <v>-54.72</v>
+        <v>-97.69</v>
       </c>
       <c r="L76" t="n">
-        <v>54.76</v>
+        <v>140.91</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:56:14</t>
+          <t>07:51:07</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.42</v>
+        <v>4.35</v>
       </c>
       <c r="F77" t="n">
-        <v>11.57</v>
+        <v>11.48</v>
       </c>
       <c r="G77" t="n">
-        <v>123.3</v>
+        <v>134.7</v>
       </c>
       <c r="H77" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="I77" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-37.18</v>
+        <v>-7.83</v>
       </c>
       <c r="K77" t="n">
-        <v>-45.08</v>
+        <v>-259.89</v>
       </c>
       <c r="L77" t="n">
-        <v>58.43</v>
+        <v>260.01</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:56:56</t>
+          <t>07:52:53</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.68</v>
+        <v>4.14</v>
       </c>
       <c r="F78" t="n">
         <v>10.9</v>
       </c>
       <c r="G78" t="n">
-        <v>125.2</v>
+        <v>129</v>
       </c>
       <c r="H78" t="n">
-        <v>12.3</v>
+        <v>5.1</v>
       </c>
       <c r="I78" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-27</v>
+        <v>21.91</v>
       </c>
       <c r="K78" t="n">
-        <v>-25.32</v>
+        <v>-450.83</v>
       </c>
       <c r="L78" t="n">
-        <v>37.01</v>
+        <v>451.36</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:57:58</t>
+          <t>07:55:22</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.9</v>
+        <v>3.53</v>
       </c>
       <c r="F79" t="n">
-        <v>11.05</v>
+        <v>11.57</v>
       </c>
       <c r="G79" t="n">
-        <v>125.7</v>
+        <v>125.1</v>
       </c>
       <c r="H79" t="n">
-        <v>15.8</v>
+        <v>10.4</v>
       </c>
       <c r="I79" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>21.61</v>
+        <v>230.88</v>
       </c>
       <c r="K79" t="n">
-        <v>11.25</v>
+        <v>208.98</v>
       </c>
       <c r="L79" t="n">
-        <v>24.36</v>
+        <v>311.41</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:02:18</t>
+          <t>08:01:42</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.98</v>
+        <v>4.18</v>
       </c>
       <c r="F80" t="n">
-        <v>10.19</v>
+        <v>11.23</v>
       </c>
       <c r="G80" t="n">
-        <v>127.5</v>
+        <v>111.5</v>
       </c>
       <c r="H80" t="n">
-        <v>0.5</v>
+        <v>7.9</v>
       </c>
       <c r="I80" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>11.07</v>
+        <v>122.51</v>
       </c>
       <c r="K80" t="n">
-        <v>12.89</v>
+        <v>150.01</v>
       </c>
       <c r="L80" t="n">
-        <v>16.99</v>
+        <v>193.68</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:04:27</t>
+          <t>08:02:42</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.35</v>
+        <v>3.97</v>
       </c>
       <c r="F81" t="n">
-        <v>10.6</v>
+        <v>11.42</v>
       </c>
       <c r="G81" t="n">
-        <v>121</v>
+        <v>122.8</v>
       </c>
       <c r="H81" t="n">
-        <v>12.4</v>
+        <v>11.6</v>
       </c>
       <c r="I81" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-46.26</v>
+        <v>-0.76</v>
       </c>
       <c r="K81" t="n">
-        <v>-66.12</v>
+        <v>296.26</v>
       </c>
       <c r="L81" t="n">
-        <v>80.7</v>
+        <v>296.26</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:05:33</t>
+          <t>08:04:25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.12</v>
+        <v>3.58</v>
       </c>
       <c r="F82" t="n">
-        <v>11.16</v>
+        <v>11.13</v>
       </c>
       <c r="G82" t="n">
-        <v>125.2</v>
+        <v>128</v>
       </c>
       <c r="H82" t="n">
-        <v>11.4</v>
+        <v>6.9</v>
       </c>
       <c r="I82" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-272.35</v>
+        <v>-177.87</v>
       </c>
       <c r="K82" t="n">
-        <v>-32.66</v>
+        <v>-21.6</v>
       </c>
       <c r="L82" t="n">
-        <v>274.3</v>
+        <v>179.18</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:09:36</t>
+          <t>08:08:45</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4</v>
+        <v>4.32</v>
       </c>
       <c r="F83" t="n">
-        <v>11.29</v>
+        <v>10.06</v>
       </c>
       <c r="G83" t="n">
-        <v>129.4</v>
+        <v>125.2</v>
       </c>
       <c r="H83" t="n">
-        <v>6.9</v>
+        <v>11.8</v>
       </c>
       <c r="I83" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>89.48</v>
+        <v>300.81</v>
       </c>
       <c r="K83" t="n">
-        <v>-96.48</v>
+        <v>-146.88</v>
       </c>
       <c r="L83" t="n">
-        <v>131.59</v>
+        <v>334.75</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:11:35</t>
+          <t>08:11:15</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.93</v>
+        <v>4.32</v>
       </c>
       <c r="F84" t="n">
-        <v>10.41</v>
+        <v>11.31</v>
       </c>
       <c r="G84" t="n">
-        <v>115.7</v>
+        <v>136.2</v>
       </c>
       <c r="H84" t="n">
-        <v>9</v>
+        <v>10.3</v>
       </c>
       <c r="I84" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-300.28</v>
+        <v>-577.79</v>
       </c>
       <c r="K84" t="n">
-        <v>-26.03</v>
+        <v>122.24</v>
       </c>
       <c r="L84" t="n">
-        <v>301.41</v>
+        <v>590.58</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:13:54</t>
+          <t>08:13:13</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.45</v>
+        <v>4.62</v>
       </c>
       <c r="F85" t="n">
-        <v>10.85</v>
+        <v>12.01</v>
       </c>
       <c r="G85" t="n">
-        <v>121.5</v>
+        <v>122.9</v>
       </c>
       <c r="H85" t="n">
-        <v>10.7</v>
+        <v>18.9</v>
       </c>
       <c r="I85" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-98.29000000000001</v>
+        <v>-197.73</v>
       </c>
       <c r="K85" t="n">
-        <v>148.78</v>
+        <v>-312.34</v>
       </c>
       <c r="L85" t="n">
-        <v>178.31</v>
+        <v>369.66</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:19:21</t>
+          <t>08:16:42</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.73</v>
+        <v>3.77</v>
       </c>
       <c r="F86" t="n">
-        <v>10.45</v>
+        <v>10.71</v>
       </c>
       <c r="G86" t="n">
-        <v>115.9</v>
+        <v>126.2</v>
       </c>
       <c r="H86" t="n">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="I86" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>183.04</v>
+        <v>654.62</v>
       </c>
       <c r="K86" t="n">
-        <v>-31.97</v>
+        <v>353.65</v>
       </c>
       <c r="L86" t="n">
-        <v>185.81</v>
+        <v>744.04</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:20:40</t>
+          <t>08:18:12</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.03</v>
+        <v>4.14</v>
       </c>
       <c r="F87" t="n">
-        <v>10.72</v>
+        <v>10.85</v>
       </c>
       <c r="G87" t="n">
-        <v>107</v>
+        <v>124.5</v>
       </c>
       <c r="H87" t="n">
-        <v>11.7</v>
+        <v>10.5</v>
       </c>
       <c r="I87" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>-6.75</v>
+        <v>17.84</v>
       </c>
       <c r="K87" t="n">
-        <v>447.12</v>
+        <v>-651.66</v>
       </c>
       <c r="L87" t="n">
-        <v>447.17</v>
+        <v>651.91</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:22:49</t>
+          <t>08:20:10</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.95</v>
+        <v>4.82</v>
       </c>
       <c r="F88" t="n">
-        <v>10.76</v>
+        <v>10.02</v>
       </c>
       <c r="G88" t="n">
-        <v>123.7</v>
+        <v>110.9</v>
       </c>
       <c r="H88" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="I88" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-36.05</v>
+        <v>28.39</v>
       </c>
       <c r="K88" t="n">
-        <v>483.64</v>
+        <v>401.03</v>
       </c>
       <c r="L88" t="n">
-        <v>484.98</v>
+        <v>402.03</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-11.xlsx
+++ b/output/2025-07-11.xlsx
@@ -640,13 +640,13 @@
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.75</v>
+        <v>-6.65</v>
       </c>
       <c r="K14" t="n">
-        <v>-116.29</v>
+        <v>-162.83</v>
       </c>
       <c r="L14" t="n">
-        <v>116.39</v>
+        <v>162.97</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-198.73</v>
+        <v>-173.99</v>
       </c>
       <c r="K15" t="n">
-        <v>313.22</v>
+        <v>274.23</v>
       </c>
       <c r="L15" t="n">
-        <v>370.95</v>
+        <v>324.77</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-176.18</v>
+        <v>-162.67</v>
       </c>
       <c r="K16" t="n">
-        <v>316.39</v>
+        <v>292.12</v>
       </c>
       <c r="L16" t="n">
-        <v>362.14</v>
+        <v>334.36</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>-92.45</v>
+        <v>-124.27</v>
       </c>
       <c r="K17" t="n">
-        <v>176.85</v>
+        <v>237.72</v>
       </c>
       <c r="L17" t="n">
-        <v>199.55</v>
+        <v>268.24</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>61.46</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>414.36</v>
+        <v>457.74</v>
       </c>
       <c r="L18" t="n">
-        <v>418.89</v>
+        <v>462.75</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>80.7</v>
+        <v>132.82</v>
       </c>
       <c r="K19" t="n">
-        <v>-31.14</v>
+        <v>-51.25</v>
       </c>
       <c r="L19" t="n">
-        <v>86.5</v>
+        <v>142.36</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.54</v>
+        <v>-11.15</v>
       </c>
       <c r="K20" t="n">
-        <v>-107.38</v>
+        <v>-263.66</v>
       </c>
       <c r="L20" t="n">
-        <v>107.48</v>
+        <v>263.89</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-201.35</v>
+        <v>-198.55</v>
       </c>
       <c r="K21" t="n">
-        <v>-381.81</v>
+        <v>-376.49</v>
       </c>
       <c r="L21" t="n">
-        <v>431.65</v>
+        <v>425.64</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-124.47</v>
+        <v>-232.93</v>
       </c>
       <c r="K22" t="n">
-        <v>-19.14</v>
+        <v>-35.81</v>
       </c>
       <c r="L22" t="n">
-        <v>125.94</v>
+        <v>235.66</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>389.99</v>
+        <v>605.27</v>
       </c>
       <c r="K23" t="n">
-        <v>-166.55</v>
+        <v>-258.49</v>
       </c>
       <c r="L23" t="n">
-        <v>424.06</v>
+        <v>658.16</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-365.69</v>
+        <v>-498.01</v>
       </c>
       <c r="K24" t="n">
-        <v>-210.95</v>
+        <v>-287.28</v>
       </c>
       <c r="L24" t="n">
-        <v>422.17</v>
+        <v>574.9299999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>176.69</v>
+        <v>216.78</v>
       </c>
       <c r="K25" t="n">
-        <v>687.01</v>
+        <v>842.89</v>
       </c>
       <c r="L25" t="n">
-        <v>709.37</v>
+        <v>870.3200000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-927.45</v>
+        <v>-1029.17</v>
       </c>
       <c r="K26" t="n">
-        <v>-129.59</v>
+        <v>-143.8</v>
       </c>
       <c r="L26" t="n">
-        <v>936.46</v>
+        <v>1039.17</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-624.58</v>
+        <v>-838.96</v>
       </c>
       <c r="K27" t="n">
-        <v>-191.56</v>
+        <v>-257.32</v>
       </c>
       <c r="L27" t="n">
-        <v>653.29</v>
+        <v>877.53</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>-117.82</v>
+        <v>-261.44</v>
       </c>
       <c r="K28" t="n">
-        <v>206.97</v>
+        <v>459.27</v>
       </c>
       <c r="L28" t="n">
-        <v>238.15</v>
+        <v>528.46</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>18</v>
       </c>
       <c r="J29" t="n">
-        <v>-299.6</v>
+        <v>-311.89</v>
       </c>
       <c r="K29" t="n">
-        <v>-12.18</v>
+        <v>-12.68</v>
       </c>
       <c r="L29" t="n">
-        <v>299.85</v>
+        <v>312.15</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>-160.76</v>
+        <v>-161.3</v>
       </c>
       <c r="K30" t="n">
-        <v>41.13</v>
+        <v>41.27</v>
       </c>
       <c r="L30" t="n">
-        <v>165.93</v>
+        <v>166.49</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>116.21</v>
+        <v>127.27</v>
       </c>
       <c r="K31" t="n">
-        <v>-65.84999999999999</v>
+        <v>-72.12</v>
       </c>
       <c r="L31" t="n">
-        <v>133.57</v>
+        <v>146.28</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>152.57</v>
+        <v>192.2</v>
       </c>
       <c r="K32" t="n">
-        <v>-125.41</v>
+        <v>-157.99</v>
       </c>
       <c r="L32" t="n">
-        <v>197.5</v>
+        <v>248.8</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-122.2</v>
+        <v>-120.88</v>
       </c>
       <c r="K33" t="n">
-        <v>363.44</v>
+        <v>359.51</v>
       </c>
       <c r="L33" t="n">
-        <v>383.44</v>
+        <v>379.28</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>195.13</v>
+        <v>200.2</v>
       </c>
       <c r="K34" t="n">
-        <v>-196.66</v>
+        <v>-201.77</v>
       </c>
       <c r="L34" t="n">
-        <v>277.04</v>
+        <v>284.24</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-179</v>
+        <v>-228.4</v>
       </c>
       <c r="K35" t="n">
-        <v>-198.79</v>
+        <v>-253.65</v>
       </c>
       <c r="L35" t="n">
-        <v>267.5</v>
+        <v>341.32</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>72.08</v>
+        <v>88.38</v>
       </c>
       <c r="K36" t="n">
-        <v>-267.89</v>
+        <v>-328.45</v>
       </c>
       <c r="L36" t="n">
-        <v>277.42</v>
+        <v>340.13</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>463.21</v>
+        <v>537.12</v>
       </c>
       <c r="K37" t="n">
-        <v>-18.91</v>
+        <v>-21.92</v>
       </c>
       <c r="L37" t="n">
-        <v>463.6</v>
+        <v>537.5700000000001</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>56.8</v>
+        <v>68.55</v>
       </c>
       <c r="K38" t="n">
-        <v>-469.58</v>
+        <v>-566.67</v>
       </c>
       <c r="L38" t="n">
-        <v>473.01</v>
+        <v>570.8</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>288.77</v>
+        <v>438.42</v>
       </c>
       <c r="K39" t="n">
-        <v>22.31</v>
+        <v>33.87</v>
       </c>
       <c r="L39" t="n">
-        <v>289.63</v>
+        <v>439.73</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>322.19</v>
+        <v>494.5</v>
       </c>
       <c r="K40" t="n">
-        <v>222.53</v>
+        <v>341.54</v>
       </c>
       <c r="L40" t="n">
-        <v>391.57</v>
+        <v>600.98</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>-426.86</v>
+        <v>-581.9</v>
       </c>
       <c r="K41" t="n">
-        <v>-519.36</v>
+        <v>-707.98</v>
       </c>
       <c r="L41" t="n">
-        <v>672.26</v>
+        <v>916.4299999999999</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>-38.06</v>
+        <v>-59.16</v>
       </c>
       <c r="K42" t="n">
-        <v>362.29</v>
+        <v>563.12</v>
       </c>
       <c r="L42" t="n">
-        <v>364.28</v>
+        <v>566.22</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>607.13</v>
+        <v>756.84</v>
       </c>
       <c r="K43" t="n">
-        <v>-205.67</v>
+        <v>-256.39</v>
       </c>
       <c r="L43" t="n">
-        <v>641.02</v>
+        <v>799.09</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>53.4</v>
+        <v>79.95</v>
       </c>
       <c r="K44" t="n">
-        <v>91.19</v>
+        <v>136.53</v>
       </c>
       <c r="L44" t="n">
-        <v>105.68</v>
+        <v>158.22</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>1.73</v>
+        <v>2.01</v>
       </c>
       <c r="K45" t="n">
-        <v>179.3</v>
+        <v>207.55</v>
       </c>
       <c r="L45" t="n">
-        <v>179.31</v>
+        <v>207.56</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>-197.75</v>
+        <v>-239.42</v>
       </c>
       <c r="K46" t="n">
-        <v>60.66</v>
+        <v>73.44</v>
       </c>
       <c r="L46" t="n">
-        <v>206.85</v>
+        <v>250.43</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-325.09</v>
+        <v>-350.58</v>
       </c>
       <c r="K47" t="n">
-        <v>-164.4</v>
+        <v>-177.29</v>
       </c>
       <c r="L47" t="n">
-        <v>364.29</v>
+        <v>392.85</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-161.54</v>
+        <v>-165.34</v>
       </c>
       <c r="K48" t="n">
-        <v>158.64</v>
+        <v>162.37</v>
       </c>
       <c r="L48" t="n">
-        <v>226.4</v>
+        <v>231.73</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>29.7</v>
+        <v>52.85</v>
       </c>
       <c r="K49" t="n">
-        <v>41.57</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>51.09</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>300.62</v>
+        <v>390.29</v>
       </c>
       <c r="K50" t="n">
-        <v>263.14</v>
+        <v>341.62</v>
       </c>
       <c r="L50" t="n">
-        <v>399.52</v>
+        <v>518.6799999999999</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-139.98</v>
+        <v>-174.05</v>
       </c>
       <c r="K51" t="n">
-        <v>-392.93</v>
+        <v>-488.56</v>
       </c>
       <c r="L51" t="n">
-        <v>417.12</v>
+        <v>518.64</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>-89.72</v>
+        <v>-107.18</v>
       </c>
       <c r="K52" t="n">
-        <v>-384.96</v>
+        <v>-459.88</v>
       </c>
       <c r="L52" t="n">
-        <v>395.28</v>
+        <v>472.21</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>220.87</v>
+        <v>349.32</v>
       </c>
       <c r="K53" t="n">
-        <v>-275.45</v>
+        <v>-435.64</v>
       </c>
       <c r="L53" t="n">
-        <v>353.07</v>
+        <v>558.39</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-93.13</v>
+        <v>-139.14</v>
       </c>
       <c r="K54" t="n">
-        <v>353.77</v>
+        <v>528.5599999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>365.83</v>
+        <v>546.5599999999999</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>-74.91</v>
+        <v>-161.27</v>
       </c>
       <c r="K55" t="n">
-        <v>143.66</v>
+        <v>309.29</v>
       </c>
       <c r="L55" t="n">
-        <v>162.01</v>
+        <v>348.82</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>55.65</v>
+        <v>85.36</v>
       </c>
       <c r="K56" t="n">
-        <v>480.5</v>
+        <v>736.98</v>
       </c>
       <c r="L56" t="n">
-        <v>483.72</v>
+        <v>741.91</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>303.04</v>
+        <v>639.52</v>
       </c>
       <c r="K57" t="n">
-        <v>-30.3</v>
+        <v>-63.95</v>
       </c>
       <c r="L57" t="n">
-        <v>304.55</v>
+        <v>642.71</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>-96.15000000000001</v>
+        <v>-151.71</v>
       </c>
       <c r="K58" t="n">
-        <v>427.36</v>
+        <v>674.28</v>
       </c>
       <c r="L58" t="n">
-        <v>438.04</v>
+        <v>691.13</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>-68.75</v>
+        <v>-77.98999999999999</v>
       </c>
       <c r="K59" t="n">
-        <v>157.61</v>
+        <v>178.8</v>
       </c>
       <c r="L59" t="n">
-        <v>171.95</v>
+        <v>195.06</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>167.78</v>
+        <v>199.87</v>
       </c>
       <c r="K60" t="n">
-        <v>-65.78</v>
+        <v>-78.36</v>
       </c>
       <c r="L60" t="n">
-        <v>180.21</v>
+        <v>214.68</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>140.87</v>
+        <v>159.69</v>
       </c>
       <c r="K61" t="n">
-        <v>-154.45</v>
+        <v>-175.07</v>
       </c>
       <c r="L61" t="n">
-        <v>209.05</v>
+        <v>236.96</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-9.09</v>
+        <v>-10.42</v>
       </c>
       <c r="K62" t="n">
-        <v>-343.89</v>
+        <v>-394.06</v>
       </c>
       <c r="L62" t="n">
-        <v>344.01</v>
+        <v>394.2</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-165.65</v>
+        <v>-177.2</v>
       </c>
       <c r="K63" t="n">
-        <v>164.99</v>
+        <v>176.5</v>
       </c>
       <c r="L63" t="n">
-        <v>233.79</v>
+        <v>250.1</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>78.09</v>
+        <v>83.59</v>
       </c>
       <c r="K64" t="n">
-        <v>-290.88</v>
+        <v>-311.37</v>
       </c>
       <c r="L64" t="n">
-        <v>301.18</v>
+        <v>322.39</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>-31.4</v>
+        <v>-42.69</v>
       </c>
       <c r="K65" t="n">
-        <v>-352.73</v>
+        <v>-479.59</v>
       </c>
       <c r="L65" t="n">
-        <v>354.13</v>
+        <v>481.48</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-489.57</v>
+        <v>-562.09</v>
       </c>
       <c r="K66" t="n">
-        <v>-95.18000000000001</v>
+        <v>-109.28</v>
       </c>
       <c r="L66" t="n">
-        <v>498.73</v>
+        <v>572.62</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>195.46</v>
+        <v>210.28</v>
       </c>
       <c r="K67" t="n">
-        <v>713.23</v>
+        <v>767.3099999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>739.53</v>
+        <v>795.61</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>594.09</v>
+        <v>826.85</v>
       </c>
       <c r="K68" t="n">
-        <v>196.28</v>
+        <v>273.18</v>
       </c>
       <c r="L68" t="n">
-        <v>625.67</v>
+        <v>870.8099999999999</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>-276.92</v>
+        <v>-447.01</v>
       </c>
       <c r="K69" t="n">
-        <v>146.3</v>
+        <v>236.16</v>
       </c>
       <c r="L69" t="n">
-        <v>313.19</v>
+        <v>505.56</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>-108.83</v>
+        <v>-162.92</v>
       </c>
       <c r="K70" t="n">
-        <v>-395.24</v>
+        <v>-591.71</v>
       </c>
       <c r="L70" t="n">
-        <v>409.95</v>
+        <v>613.73</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>-386.67</v>
+        <v>-478.59</v>
       </c>
       <c r="K71" t="n">
-        <v>851.17</v>
+        <v>1053.5</v>
       </c>
       <c r="L71" t="n">
-        <v>934.88</v>
+        <v>1157.12</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>60.67</v>
+        <v>89.2</v>
       </c>
       <c r="K72" t="n">
-        <v>-371.94</v>
+        <v>-546.8</v>
       </c>
       <c r="L72" t="n">
-        <v>376.86</v>
+        <v>554.02</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-130.97</v>
+        <v>-152.55</v>
       </c>
       <c r="K73" t="n">
-        <v>-741.23</v>
+        <v>-863.33</v>
       </c>
       <c r="L73" t="n">
-        <v>752.71</v>
+        <v>876.7</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>185.41</v>
+        <v>159.1</v>
       </c>
       <c r="K74" t="n">
-        <v>-224.22</v>
+        <v>-192.4</v>
       </c>
       <c r="L74" t="n">
-        <v>290.95</v>
+        <v>249.66</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-24.19</v>
+        <v>-42.01</v>
       </c>
       <c r="K75" t="n">
-        <v>84.87</v>
+        <v>147.4</v>
       </c>
       <c r="L75" t="n">
-        <v>88.25</v>
+        <v>153.27</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-101.55</v>
+        <v>-136.57</v>
       </c>
       <c r="K76" t="n">
-        <v>-97.69</v>
+        <v>-131.39</v>
       </c>
       <c r="L76" t="n">
-        <v>140.91</v>
+        <v>189.51</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-7.83</v>
+        <v>-9.34</v>
       </c>
       <c r="K77" t="n">
-        <v>-259.89</v>
+        <v>-309.98</v>
       </c>
       <c r="L77" t="n">
-        <v>260.01</v>
+        <v>310.12</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>21.91</v>
+        <v>21.1</v>
       </c>
       <c r="K78" t="n">
-        <v>-450.83</v>
+        <v>-434.15</v>
       </c>
       <c r="L78" t="n">
-        <v>451.36</v>
+        <v>434.66</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>230.88</v>
+        <v>244.03</v>
       </c>
       <c r="K79" t="n">
-        <v>208.98</v>
+        <v>220.9</v>
       </c>
       <c r="L79" t="n">
-        <v>311.41</v>
+        <v>329.16</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>122.51</v>
+        <v>220.88</v>
       </c>
       <c r="K80" t="n">
-        <v>150.01</v>
+        <v>270.46</v>
       </c>
       <c r="L80" t="n">
-        <v>193.68</v>
+        <v>349.2</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.76</v>
+        <v>-0.95</v>
       </c>
       <c r="K81" t="n">
-        <v>296.26</v>
+        <v>370.09</v>
       </c>
       <c r="L81" t="n">
-        <v>296.26</v>
+        <v>370.09</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-177.87</v>
+        <v>-275.38</v>
       </c>
       <c r="K82" t="n">
-        <v>-21.6</v>
+        <v>-33.45</v>
       </c>
       <c r="L82" t="n">
-        <v>179.18</v>
+        <v>277.4</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>300.81</v>
+        <v>472.57</v>
       </c>
       <c r="K83" t="n">
-        <v>-146.88</v>
+        <v>-230.75</v>
       </c>
       <c r="L83" t="n">
-        <v>334.75</v>
+        <v>525.89</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-577.79</v>
+        <v>-758.73</v>
       </c>
       <c r="K84" t="n">
-        <v>122.24</v>
+        <v>160.52</v>
       </c>
       <c r="L84" t="n">
-        <v>590.58</v>
+        <v>775.52</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-197.73</v>
+        <v>-290.47</v>
       </c>
       <c r="K85" t="n">
-        <v>-312.34</v>
+        <v>-458.83</v>
       </c>
       <c r="L85" t="n">
-        <v>369.66</v>
+        <v>543.05</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>654.62</v>
+        <v>766.35</v>
       </c>
       <c r="K86" t="n">
-        <v>353.65</v>
+        <v>414.01</v>
       </c>
       <c r="L86" t="n">
-        <v>744.04</v>
+        <v>871.03</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>17.84</v>
+        <v>23.39</v>
       </c>
       <c r="K87" t="n">
-        <v>-651.66</v>
+        <v>-854.23</v>
       </c>
       <c r="L87" t="n">
-        <v>651.91</v>
+        <v>854.55</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>28.39</v>
+        <v>52.86</v>
       </c>
       <c r="K88" t="n">
-        <v>401.03</v>
+        <v>746.8</v>
       </c>
       <c r="L88" t="n">
-        <v>402.03</v>
+        <v>748.66</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-11.xlsx
+++ b/output/2025-07-11.xlsx
@@ -640,13 +640,13 @@
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.65</v>
+        <v>-4.49</v>
       </c>
       <c r="K14" t="n">
-        <v>-162.83</v>
+        <v>-109.93</v>
       </c>
       <c r="L14" t="n">
-        <v>162.97</v>
+        <v>110.02</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-173.99</v>
+        <v>-130.78</v>
       </c>
       <c r="K15" t="n">
-        <v>274.23</v>
+        <v>206.12</v>
       </c>
       <c r="L15" t="n">
-        <v>324.77</v>
+        <v>244.11</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-162.67</v>
+        <v>-120.21</v>
       </c>
       <c r="K16" t="n">
-        <v>292.12</v>
+        <v>215.88</v>
       </c>
       <c r="L16" t="n">
-        <v>334.36</v>
+        <v>247.09</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>-124.27</v>
+        <v>-77.77</v>
       </c>
       <c r="K17" t="n">
-        <v>237.72</v>
+        <v>148.76</v>
       </c>
       <c r="L17" t="n">
-        <v>268.24</v>
+        <v>167.87</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>67.90000000000001</v>
+        <v>41.93</v>
       </c>
       <c r="K18" t="n">
-        <v>457.74</v>
+        <v>282.65</v>
       </c>
       <c r="L18" t="n">
-        <v>462.75</v>
+        <v>285.75</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>132.82</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-51.25</v>
+        <v>-34.48</v>
       </c>
       <c r="L19" t="n">
-        <v>142.36</v>
+        <v>95.77</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-11.15</v>
+        <v>-6.6</v>
       </c>
       <c r="K20" t="n">
-        <v>-263.66</v>
+        <v>-156.23</v>
       </c>
       <c r="L20" t="n">
-        <v>263.89</v>
+        <v>156.37</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-198.55</v>
+        <v>-124.53</v>
       </c>
       <c r="K21" t="n">
-        <v>-376.49</v>
+        <v>-236.14</v>
       </c>
       <c r="L21" t="n">
-        <v>425.64</v>
+        <v>266.97</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-232.93</v>
+        <v>-143.52</v>
       </c>
       <c r="K22" t="n">
-        <v>-35.81</v>
+        <v>-22.07</v>
       </c>
       <c r="L22" t="n">
-        <v>235.66</v>
+        <v>145.21</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>605.27</v>
+        <v>288.96</v>
       </c>
       <c r="K23" t="n">
-        <v>-258.49</v>
+        <v>-123.4</v>
       </c>
       <c r="L23" t="n">
-        <v>658.16</v>
+        <v>314.21</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-498.01</v>
+        <v>-246.62</v>
       </c>
       <c r="K24" t="n">
-        <v>-287.28</v>
+        <v>-142.27</v>
       </c>
       <c r="L24" t="n">
-        <v>574.9299999999999</v>
+        <v>284.72</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>216.78</v>
+        <v>105.53</v>
       </c>
       <c r="K25" t="n">
-        <v>842.89</v>
+        <v>410.32</v>
       </c>
       <c r="L25" t="n">
-        <v>870.3200000000001</v>
+        <v>423.67</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-1029.17</v>
+        <v>-536.4299999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>-143.8</v>
+        <v>-74.95</v>
       </c>
       <c r="L26" t="n">
-        <v>1039.17</v>
+        <v>541.64</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-838.96</v>
+        <v>-389.32</v>
       </c>
       <c r="K27" t="n">
-        <v>-257.32</v>
+        <v>-119.41</v>
       </c>
       <c r="L27" t="n">
-        <v>877.53</v>
+        <v>407.22</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>-261.44</v>
+        <v>-117.53</v>
       </c>
       <c r="K28" t="n">
-        <v>459.27</v>
+        <v>206.47</v>
       </c>
       <c r="L28" t="n">
-        <v>528.46</v>
+        <v>237.58</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>18</v>
       </c>
       <c r="J29" t="n">
-        <v>-311.89</v>
+        <v>-203.46</v>
       </c>
       <c r="K29" t="n">
-        <v>-12.68</v>
+        <v>-8.27</v>
       </c>
       <c r="L29" t="n">
-        <v>312.15</v>
+        <v>203.63</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>-161.3</v>
+        <v>-127.67</v>
       </c>
       <c r="K30" t="n">
-        <v>41.27</v>
+        <v>32.66</v>
       </c>
       <c r="L30" t="n">
-        <v>166.49</v>
+        <v>131.79</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>127.27</v>
+        <v>100.52</v>
       </c>
       <c r="K31" t="n">
-        <v>-72.12</v>
+        <v>-56.97</v>
       </c>
       <c r="L31" t="n">
-        <v>146.28</v>
+        <v>115.54</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>192.2</v>
+        <v>120.24</v>
       </c>
       <c r="K32" t="n">
-        <v>-157.99</v>
+        <v>-98.84</v>
       </c>
       <c r="L32" t="n">
-        <v>248.8</v>
+        <v>155.65</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-120.88</v>
+        <v>-84.59999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>359.51</v>
+        <v>251.61</v>
       </c>
       <c r="L33" t="n">
-        <v>379.28</v>
+        <v>265.46</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>200.2</v>
+        <v>136.41</v>
       </c>
       <c r="K34" t="n">
-        <v>-201.77</v>
+        <v>-137.48</v>
       </c>
       <c r="L34" t="n">
-        <v>284.24</v>
+        <v>193.67</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-228.4</v>
+        <v>-135.13</v>
       </c>
       <c r="K35" t="n">
-        <v>-253.65</v>
+        <v>-150.07</v>
       </c>
       <c r="L35" t="n">
-        <v>341.32</v>
+        <v>201.94</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>88.38</v>
+        <v>53.82</v>
       </c>
       <c r="K36" t="n">
-        <v>-328.45</v>
+        <v>-200.03</v>
       </c>
       <c r="L36" t="n">
-        <v>340.13</v>
+        <v>207.15</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>537.12</v>
+        <v>292.61</v>
       </c>
       <c r="K37" t="n">
-        <v>-21.92</v>
+        <v>-11.94</v>
       </c>
       <c r="L37" t="n">
-        <v>537.5700000000001</v>
+        <v>292.86</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>68.55</v>
+        <v>35.47</v>
       </c>
       <c r="K38" t="n">
-        <v>-566.67</v>
+        <v>-293.26</v>
       </c>
       <c r="L38" t="n">
-        <v>570.8</v>
+        <v>295.4</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>438.42</v>
+        <v>232.93</v>
       </c>
       <c r="K39" t="n">
-        <v>33.87</v>
+        <v>18</v>
       </c>
       <c r="L39" t="n">
-        <v>439.73</v>
+        <v>233.63</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>494.5</v>
+        <v>243.04</v>
       </c>
       <c r="K40" t="n">
-        <v>341.54</v>
+        <v>167.86</v>
       </c>
       <c r="L40" t="n">
-        <v>600.98</v>
+        <v>295.37</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>-581.9</v>
+        <v>-267.72</v>
       </c>
       <c r="K41" t="n">
-        <v>-707.98</v>
+        <v>-325.73</v>
       </c>
       <c r="L41" t="n">
-        <v>916.4299999999999</v>
+        <v>421.64</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>-59.16</v>
+        <v>-30.64</v>
       </c>
       <c r="K42" t="n">
-        <v>563.12</v>
+        <v>291.68</v>
       </c>
       <c r="L42" t="n">
-        <v>566.22</v>
+        <v>293.28</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>756.84</v>
+        <v>392.69</v>
       </c>
       <c r="K43" t="n">
-        <v>-256.39</v>
+        <v>-133.03</v>
       </c>
       <c r="L43" t="n">
-        <v>799.09</v>
+        <v>414.61</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>79.95</v>
+        <v>58.38</v>
       </c>
       <c r="K44" t="n">
-        <v>136.53</v>
+        <v>99.7</v>
       </c>
       <c r="L44" t="n">
-        <v>158.22</v>
+        <v>115.53</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>2.01</v>
+        <v>1.51</v>
       </c>
       <c r="K45" t="n">
-        <v>207.55</v>
+        <v>156.31</v>
       </c>
       <c r="L45" t="n">
-        <v>207.56</v>
+        <v>156.32</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>-239.42</v>
+        <v>-154.42</v>
       </c>
       <c r="K46" t="n">
-        <v>73.44</v>
+        <v>47.37</v>
       </c>
       <c r="L46" t="n">
-        <v>250.43</v>
+        <v>161.52</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-350.58</v>
+        <v>-224.77</v>
       </c>
       <c r="K47" t="n">
-        <v>-177.29</v>
+        <v>-113.66</v>
       </c>
       <c r="L47" t="n">
-        <v>392.85</v>
+        <v>251.87</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-165.34</v>
+        <v>-122.95</v>
       </c>
       <c r="K48" t="n">
-        <v>162.37</v>
+        <v>120.74</v>
       </c>
       <c r="L48" t="n">
-        <v>231.73</v>
+        <v>172.32</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>52.85</v>
+        <v>39.39</v>
       </c>
       <c r="K49" t="n">
-        <v>73.95999999999999</v>
+        <v>55.13</v>
       </c>
       <c r="L49" t="n">
-        <v>90.90000000000001</v>
+        <v>67.76000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>390.29</v>
+        <v>215.87</v>
       </c>
       <c r="K50" t="n">
-        <v>341.62</v>
+        <v>188.95</v>
       </c>
       <c r="L50" t="n">
-        <v>518.6799999999999</v>
+        <v>286.88</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-174.05</v>
+        <v>-97.09999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>-488.56</v>
+        <v>-272.57</v>
       </c>
       <c r="L51" t="n">
-        <v>518.64</v>
+        <v>289.35</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>-107.18</v>
+        <v>-58.73</v>
       </c>
       <c r="K52" t="n">
-        <v>-459.88</v>
+        <v>-252</v>
       </c>
       <c r="L52" t="n">
-        <v>472.21</v>
+        <v>258.75</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>349.32</v>
+        <v>168.89</v>
       </c>
       <c r="K53" t="n">
-        <v>-435.64</v>
+        <v>-210.62</v>
       </c>
       <c r="L53" t="n">
-        <v>558.39</v>
+        <v>269.97</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-139.14</v>
+        <v>-74.19</v>
       </c>
       <c r="K54" t="n">
-        <v>528.5599999999999</v>
+        <v>281.84</v>
       </c>
       <c r="L54" t="n">
-        <v>546.5599999999999</v>
+        <v>291.44</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>-161.27</v>
+        <v>-81.11</v>
       </c>
       <c r="K55" t="n">
-        <v>309.29</v>
+        <v>155.56</v>
       </c>
       <c r="L55" t="n">
-        <v>348.82</v>
+        <v>175.44</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>85.36</v>
+        <v>42.59</v>
       </c>
       <c r="K56" t="n">
-        <v>736.98</v>
+        <v>367.72</v>
       </c>
       <c r="L56" t="n">
-        <v>741.91</v>
+        <v>370.18</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>639.52</v>
+        <v>276.12</v>
       </c>
       <c r="K57" t="n">
-        <v>-63.95</v>
+        <v>-27.61</v>
       </c>
       <c r="L57" t="n">
-        <v>642.71</v>
+        <v>277.5</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>-151.71</v>
+        <v>-74.81999999999999</v>
       </c>
       <c r="K58" t="n">
-        <v>674.28</v>
+        <v>332.54</v>
       </c>
       <c r="L58" t="n">
-        <v>691.13</v>
+        <v>340.85</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>-77.98999999999999</v>
+        <v>-56.55</v>
       </c>
       <c r="K59" t="n">
-        <v>178.8</v>
+        <v>129.64</v>
       </c>
       <c r="L59" t="n">
-        <v>195.06</v>
+        <v>141.44</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>199.87</v>
+        <v>149.33</v>
       </c>
       <c r="K60" t="n">
-        <v>-78.36</v>
+        <v>-58.55</v>
       </c>
       <c r="L60" t="n">
-        <v>214.68</v>
+        <v>160.4</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>159.69</v>
+        <v>108.86</v>
       </c>
       <c r="K61" t="n">
-        <v>-175.07</v>
+        <v>-119.35</v>
       </c>
       <c r="L61" t="n">
-        <v>236.96</v>
+        <v>161.54</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-10.42</v>
+        <v>-6.74</v>
       </c>
       <c r="K62" t="n">
-        <v>-394.06</v>
+        <v>-254.88</v>
       </c>
       <c r="L62" t="n">
-        <v>394.2</v>
+        <v>254.97</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-177.2</v>
+        <v>-129.57</v>
       </c>
       <c r="K63" t="n">
-        <v>176.5</v>
+        <v>129.05</v>
       </c>
       <c r="L63" t="n">
-        <v>250.1</v>
+        <v>182.87</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>83.59</v>
+        <v>52.7</v>
       </c>
       <c r="K64" t="n">
-        <v>-311.37</v>
+        <v>-196.33</v>
       </c>
       <c r="L64" t="n">
-        <v>322.39</v>
+        <v>203.28</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>-42.69</v>
+        <v>-23.58</v>
       </c>
       <c r="K65" t="n">
-        <v>-479.59</v>
+        <v>-264.9</v>
       </c>
       <c r="L65" t="n">
-        <v>481.48</v>
+        <v>265.95</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-562.09</v>
+        <v>-322.72</v>
       </c>
       <c r="K66" t="n">
-        <v>-109.28</v>
+        <v>-62.74</v>
       </c>
       <c r="L66" t="n">
-        <v>572.62</v>
+        <v>328.76</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>210.28</v>
+        <v>122.11</v>
       </c>
       <c r="K67" t="n">
-        <v>767.3099999999999</v>
+        <v>445.57</v>
       </c>
       <c r="L67" t="n">
-        <v>795.61</v>
+        <v>462</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>826.85</v>
+        <v>391.89</v>
       </c>
       <c r="K68" t="n">
-        <v>273.18</v>
+        <v>129.48</v>
       </c>
       <c r="L68" t="n">
-        <v>870.8099999999999</v>
+        <v>412.73</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>-447.01</v>
+        <v>-217.82</v>
       </c>
       <c r="K69" t="n">
-        <v>236.16</v>
+        <v>115.07</v>
       </c>
       <c r="L69" t="n">
-        <v>505.56</v>
+        <v>246.34</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>-162.92</v>
+        <v>-84.84999999999999</v>
       </c>
       <c r="K70" t="n">
-        <v>-591.71</v>
+        <v>-308.16</v>
       </c>
       <c r="L70" t="n">
-        <v>613.73</v>
+        <v>319.63</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>-478.59</v>
+        <v>-224.81</v>
       </c>
       <c r="K71" t="n">
-        <v>1053.5</v>
+        <v>494.87</v>
       </c>
       <c r="L71" t="n">
-        <v>1157.12</v>
+        <v>543.54</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>89.2</v>
+        <v>44.57</v>
       </c>
       <c r="K72" t="n">
-        <v>-546.8</v>
+        <v>-273.21</v>
       </c>
       <c r="L72" t="n">
-        <v>554.02</v>
+        <v>276.82</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-152.55</v>
+        <v>-77.81</v>
       </c>
       <c r="K73" t="n">
-        <v>-863.33</v>
+        <v>-440.35</v>
       </c>
       <c r="L73" t="n">
-        <v>876.7</v>
+        <v>447.17</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>159.1</v>
+        <v>125.75</v>
       </c>
       <c r="K74" t="n">
-        <v>-192.4</v>
+        <v>-152.07</v>
       </c>
       <c r="L74" t="n">
-        <v>249.66</v>
+        <v>197.33</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-42.01</v>
+        <v>-28.37</v>
       </c>
       <c r="K75" t="n">
-        <v>147.4</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>153.27</v>
+        <v>103.5</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-136.57</v>
+        <v>-94.64</v>
       </c>
       <c r="K76" t="n">
-        <v>-131.39</v>
+        <v>-91.05</v>
       </c>
       <c r="L76" t="n">
-        <v>189.51</v>
+        <v>131.33</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-9.34</v>
+        <v>-6.25</v>
       </c>
       <c r="K77" t="n">
-        <v>-309.98</v>
+        <v>-207.52</v>
       </c>
       <c r="L77" t="n">
-        <v>310.12</v>
+        <v>207.62</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>21.1</v>
+        <v>14.72</v>
       </c>
       <c r="K78" t="n">
-        <v>-434.15</v>
+        <v>-302.84</v>
       </c>
       <c r="L78" t="n">
-        <v>434.66</v>
+        <v>303.2</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>244.03</v>
+        <v>156.81</v>
       </c>
       <c r="K79" t="n">
-        <v>220.9</v>
+        <v>141.94</v>
       </c>
       <c r="L79" t="n">
-        <v>329.16</v>
+        <v>211.51</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>220.88</v>
+        <v>116.93</v>
       </c>
       <c r="K80" t="n">
-        <v>270.46</v>
+        <v>143.17</v>
       </c>
       <c r="L80" t="n">
-        <v>349.2</v>
+        <v>184.85</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.95</v>
+        <v>-0.59</v>
       </c>
       <c r="K81" t="n">
-        <v>370.09</v>
+        <v>227.75</v>
       </c>
       <c r="L81" t="n">
-        <v>370.09</v>
+        <v>227.75</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-275.38</v>
+        <v>-162.17</v>
       </c>
       <c r="K82" t="n">
-        <v>-33.45</v>
+        <v>-19.7</v>
       </c>
       <c r="L82" t="n">
-        <v>277.4</v>
+        <v>163.36</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>472.57</v>
+        <v>245.36</v>
       </c>
       <c r="K83" t="n">
-        <v>-230.75</v>
+        <v>-119.8</v>
       </c>
       <c r="L83" t="n">
-        <v>525.89</v>
+        <v>273.05</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-758.73</v>
+        <v>-382.3</v>
       </c>
       <c r="K84" t="n">
-        <v>160.52</v>
+        <v>80.88</v>
       </c>
       <c r="L84" t="n">
-        <v>775.52</v>
+        <v>390.76</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-290.47</v>
+        <v>-159.87</v>
       </c>
       <c r="K85" t="n">
-        <v>-458.83</v>
+        <v>-252.53</v>
       </c>
       <c r="L85" t="n">
-        <v>543.05</v>
+        <v>298.89</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>766.35</v>
+        <v>400.16</v>
       </c>
       <c r="K86" t="n">
-        <v>414.01</v>
+        <v>216.18</v>
       </c>
       <c r="L86" t="n">
-        <v>871.03</v>
+        <v>454.83</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>23.39</v>
+        <v>11.66</v>
       </c>
       <c r="K87" t="n">
-        <v>-854.23</v>
+        <v>-425.76</v>
       </c>
       <c r="L87" t="n">
-        <v>854.55</v>
+        <v>425.91</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>52.86</v>
+        <v>23.93</v>
       </c>
       <c r="K88" t="n">
-        <v>746.8</v>
+        <v>337.99</v>
       </c>
       <c r="L88" t="n">
-        <v>748.66</v>
+        <v>338.83</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-11.xlsx
+++ b/output/2025-07-11.xlsx
@@ -640,13 +640,13 @@
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.49</v>
+        <v>-4.31</v>
       </c>
       <c r="K14" t="n">
-        <v>-109.93</v>
+        <v>-105.52</v>
       </c>
       <c r="L14" t="n">
-        <v>110.02</v>
+        <v>105.61</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-130.78</v>
+        <v>-123.82</v>
       </c>
       <c r="K15" t="n">
-        <v>206.12</v>
+        <v>195.17</v>
       </c>
       <c r="L15" t="n">
-        <v>244.11</v>
+        <v>231.13</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-120.21</v>
+        <v>-115.03</v>
       </c>
       <c r="K16" t="n">
-        <v>215.88</v>
+        <v>206.57</v>
       </c>
       <c r="L16" t="n">
-        <v>247.09</v>
+        <v>236.43</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>-77.77</v>
+        <v>-77.09999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>148.76</v>
+        <v>147.48</v>
       </c>
       <c r="L17" t="n">
-        <v>167.87</v>
+        <v>166.42</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>41.93</v>
+        <v>41.09</v>
       </c>
       <c r="K18" t="n">
-        <v>282.65</v>
+        <v>276.98</v>
       </c>
       <c r="L18" t="n">
-        <v>285.75</v>
+        <v>280.01</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>89.34999999999999</v>
+        <v>88.22</v>
       </c>
       <c r="K19" t="n">
-        <v>-34.48</v>
+        <v>-34.04</v>
       </c>
       <c r="L19" t="n">
-        <v>95.77</v>
+        <v>94.56</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-6.6</v>
+        <v>-6.63</v>
       </c>
       <c r="K20" t="n">
-        <v>-156.23</v>
+        <v>-156.84</v>
       </c>
       <c r="L20" t="n">
-        <v>156.37</v>
+        <v>156.98</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-124.53</v>
+        <v>-126.84</v>
       </c>
       <c r="K21" t="n">
-        <v>-236.14</v>
+        <v>-240.51</v>
       </c>
       <c r="L21" t="n">
-        <v>266.97</v>
+        <v>271.91</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-143.52</v>
+        <v>-142.32</v>
       </c>
       <c r="K22" t="n">
-        <v>-22.07</v>
+        <v>-21.88</v>
       </c>
       <c r="L22" t="n">
-        <v>145.21</v>
+        <v>143.99</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>288.96</v>
+        <v>303.07</v>
       </c>
       <c r="K23" t="n">
-        <v>-123.4</v>
+        <v>-129.43</v>
       </c>
       <c r="L23" t="n">
-        <v>314.21</v>
+        <v>329.55</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-246.62</v>
+        <v>-259.6</v>
       </c>
       <c r="K24" t="n">
-        <v>-142.27</v>
+        <v>-149.76</v>
       </c>
       <c r="L24" t="n">
-        <v>284.72</v>
+        <v>299.7</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>105.53</v>
+        <v>110.91</v>
       </c>
       <c r="K25" t="n">
-        <v>410.32</v>
+        <v>431.23</v>
       </c>
       <c r="L25" t="n">
-        <v>423.67</v>
+        <v>445.27</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-536.4299999999999</v>
+        <v>-558.67</v>
       </c>
       <c r="K26" t="n">
-        <v>-74.95</v>
+        <v>-78.06</v>
       </c>
       <c r="L26" t="n">
-        <v>541.64</v>
+        <v>564.09</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-389.32</v>
+        <v>-415.62</v>
       </c>
       <c r="K27" t="n">
-        <v>-119.41</v>
+        <v>-127.47</v>
       </c>
       <c r="L27" t="n">
-        <v>407.22</v>
+        <v>434.73</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>-117.53</v>
+        <v>-126.39</v>
       </c>
       <c r="K28" t="n">
-        <v>206.47</v>
+        <v>222.03</v>
       </c>
       <c r="L28" t="n">
-        <v>237.58</v>
+        <v>255.49</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>18</v>
       </c>
       <c r="J29" t="n">
-        <v>-203.46</v>
+        <v>-197.48</v>
       </c>
       <c r="K29" t="n">
-        <v>-8.27</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>203.63</v>
+        <v>197.65</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>-127.67</v>
+        <v>-119.65</v>
       </c>
       <c r="K30" t="n">
-        <v>32.66</v>
+        <v>30.61</v>
       </c>
       <c r="L30" t="n">
-        <v>131.79</v>
+        <v>123.5</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>100.52</v>
+        <v>93.58</v>
       </c>
       <c r="K31" t="n">
-        <v>-56.97</v>
+        <v>-53.03</v>
       </c>
       <c r="L31" t="n">
-        <v>115.54</v>
+        <v>107.56</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>120.24</v>
+        <v>118.88</v>
       </c>
       <c r="K32" t="n">
-        <v>-98.84</v>
+        <v>-97.72</v>
       </c>
       <c r="L32" t="n">
-        <v>155.65</v>
+        <v>153.88</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-84.59999999999999</v>
+        <v>-81.97</v>
       </c>
       <c r="K33" t="n">
-        <v>251.61</v>
+        <v>243.78</v>
       </c>
       <c r="L33" t="n">
-        <v>265.46</v>
+        <v>257.2</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>136.41</v>
+        <v>132.93</v>
       </c>
       <c r="K34" t="n">
-        <v>-137.48</v>
+        <v>-133.98</v>
       </c>
       <c r="L34" t="n">
-        <v>193.67</v>
+        <v>188.74</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-135.13</v>
+        <v>-137.98</v>
       </c>
       <c r="K35" t="n">
-        <v>-150.07</v>
+        <v>-153.23</v>
       </c>
       <c r="L35" t="n">
-        <v>201.94</v>
+        <v>206.2</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>53.82</v>
+        <v>54.35</v>
       </c>
       <c r="K36" t="n">
-        <v>-200.03</v>
+        <v>-201.98</v>
       </c>
       <c r="L36" t="n">
-        <v>207.15</v>
+        <v>209.16</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>292.61</v>
+        <v>301.73</v>
       </c>
       <c r="K37" t="n">
-        <v>-11.94</v>
+        <v>-12.32</v>
       </c>
       <c r="L37" t="n">
-        <v>292.86</v>
+        <v>301.98</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>35.47</v>
+        <v>36.99</v>
       </c>
       <c r="K38" t="n">
-        <v>-293.26</v>
+        <v>-305.79</v>
       </c>
       <c r="L38" t="n">
-        <v>295.4</v>
+        <v>308.02</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>232.93</v>
+        <v>239.62</v>
       </c>
       <c r="K39" t="n">
-        <v>18</v>
+        <v>18.51</v>
       </c>
       <c r="L39" t="n">
-        <v>233.63</v>
+        <v>240.33</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>243.04</v>
+        <v>253.53</v>
       </c>
       <c r="K40" t="n">
-        <v>167.86</v>
+        <v>175.11</v>
       </c>
       <c r="L40" t="n">
-        <v>295.37</v>
+        <v>308.12</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>-267.72</v>
+        <v>-285.66</v>
       </c>
       <c r="K41" t="n">
-        <v>-325.73</v>
+        <v>-347.56</v>
       </c>
       <c r="L41" t="n">
-        <v>421.64</v>
+        <v>449.89</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>-30.64</v>
+        <v>-31.95</v>
       </c>
       <c r="K42" t="n">
-        <v>291.68</v>
+        <v>304.14</v>
       </c>
       <c r="L42" t="n">
-        <v>293.28</v>
+        <v>305.81</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>392.69</v>
+        <v>407.64</v>
       </c>
       <c r="K43" t="n">
-        <v>-133.03</v>
+        <v>-138.09</v>
       </c>
       <c r="L43" t="n">
-        <v>414.61</v>
+        <v>430.4</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>58.38</v>
+        <v>56.14</v>
       </c>
       <c r="K44" t="n">
-        <v>99.7</v>
+        <v>95.87</v>
       </c>
       <c r="L44" t="n">
-        <v>115.53</v>
+        <v>111.1</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="K45" t="n">
-        <v>156.31</v>
+        <v>149.32</v>
       </c>
       <c r="L45" t="n">
-        <v>156.32</v>
+        <v>149.32</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>-154.42</v>
+        <v>-148.8</v>
       </c>
       <c r="K46" t="n">
-        <v>47.37</v>
+        <v>45.64</v>
       </c>
       <c r="L46" t="n">
-        <v>161.52</v>
+        <v>155.64</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-224.77</v>
+        <v>-221.98</v>
       </c>
       <c r="K47" t="n">
-        <v>-113.66</v>
+        <v>-112.26</v>
       </c>
       <c r="L47" t="n">
-        <v>251.87</v>
+        <v>248.75</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-122.95</v>
+        <v>-119.33</v>
       </c>
       <c r="K48" t="n">
-        <v>120.74</v>
+        <v>117.19</v>
       </c>
       <c r="L48" t="n">
-        <v>172.32</v>
+        <v>167.25</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>39.39</v>
+        <v>38.57</v>
       </c>
       <c r="K49" t="n">
-        <v>55.13</v>
+        <v>53.99</v>
       </c>
       <c r="L49" t="n">
-        <v>67.76000000000001</v>
+        <v>66.34999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>215.87</v>
+        <v>219.16</v>
       </c>
       <c r="K50" t="n">
-        <v>188.95</v>
+        <v>191.84</v>
       </c>
       <c r="L50" t="n">
-        <v>286.88</v>
+        <v>291.26</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-97.09999999999999</v>
+        <v>-98.61</v>
       </c>
       <c r="K51" t="n">
-        <v>-272.57</v>
+        <v>-276.81</v>
       </c>
       <c r="L51" t="n">
-        <v>289.35</v>
+        <v>293.86</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>-58.73</v>
+        <v>-59.75</v>
       </c>
       <c r="K52" t="n">
-        <v>-252</v>
+        <v>-256.38</v>
       </c>
       <c r="L52" t="n">
-        <v>258.75</v>
+        <v>263.25</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>168.89</v>
+        <v>176.82</v>
       </c>
       <c r="K53" t="n">
-        <v>-210.62</v>
+        <v>-220.51</v>
       </c>
       <c r="L53" t="n">
-        <v>269.97</v>
+        <v>282.65</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-74.19</v>
+        <v>-76.77</v>
       </c>
       <c r="K54" t="n">
-        <v>281.84</v>
+        <v>291.64</v>
       </c>
       <c r="L54" t="n">
-        <v>291.44</v>
+        <v>301.57</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>-81.11</v>
+        <v>-84.88</v>
       </c>
       <c r="K55" t="n">
-        <v>155.56</v>
+        <v>162.79</v>
       </c>
       <c r="L55" t="n">
-        <v>175.44</v>
+        <v>183.59</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>42.59</v>
+        <v>44.56</v>
       </c>
       <c r="K56" t="n">
-        <v>367.72</v>
+        <v>384.67</v>
       </c>
       <c r="L56" t="n">
-        <v>370.18</v>
+        <v>387.25</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>276.12</v>
+        <v>299.3</v>
       </c>
       <c r="K57" t="n">
-        <v>-27.61</v>
+        <v>-29.93</v>
       </c>
       <c r="L57" t="n">
-        <v>277.5</v>
+        <v>300.8</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>-74.81999999999999</v>
+        <v>-79.64</v>
       </c>
       <c r="K58" t="n">
-        <v>332.54</v>
+        <v>353.95</v>
       </c>
       <c r="L58" t="n">
-        <v>340.85</v>
+        <v>362.8</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>-56.55</v>
+        <v>-53.97</v>
       </c>
       <c r="K59" t="n">
-        <v>129.64</v>
+        <v>123.73</v>
       </c>
       <c r="L59" t="n">
-        <v>141.44</v>
+        <v>134.99</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>149.33</v>
+        <v>140.55</v>
       </c>
       <c r="K60" t="n">
-        <v>-58.55</v>
+        <v>-55.1</v>
       </c>
       <c r="L60" t="n">
-        <v>160.4</v>
+        <v>150.96</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>108.86</v>
+        <v>105.07</v>
       </c>
       <c r="K61" t="n">
-        <v>-119.35</v>
+        <v>-115.19</v>
       </c>
       <c r="L61" t="n">
-        <v>161.54</v>
+        <v>155.91</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-6.74</v>
+        <v>-6.56</v>
       </c>
       <c r="K62" t="n">
-        <v>-254.88</v>
+        <v>-248.31</v>
       </c>
       <c r="L62" t="n">
-        <v>254.97</v>
+        <v>248.39</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-129.57</v>
+        <v>-124.96</v>
       </c>
       <c r="K63" t="n">
-        <v>129.05</v>
+        <v>124.46</v>
       </c>
       <c r="L63" t="n">
-        <v>182.87</v>
+        <v>176.36</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>52.7</v>
+        <v>52.38</v>
       </c>
       <c r="K64" t="n">
-        <v>-196.33</v>
+        <v>-195.11</v>
       </c>
       <c r="L64" t="n">
-        <v>203.28</v>
+        <v>202.01</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>-23.58</v>
+        <v>-23.87</v>
       </c>
       <c r="K65" t="n">
-        <v>-264.9</v>
+        <v>-268.19</v>
       </c>
       <c r="L65" t="n">
-        <v>265.95</v>
+        <v>269.25</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-322.72</v>
+        <v>-332.76</v>
       </c>
       <c r="K66" t="n">
-        <v>-62.74</v>
+        <v>-64.69</v>
       </c>
       <c r="L66" t="n">
-        <v>328.76</v>
+        <v>338.99</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>122.11</v>
+        <v>122.95</v>
       </c>
       <c r="K67" t="n">
-        <v>445.57</v>
+        <v>448.64</v>
       </c>
       <c r="L67" t="n">
-        <v>462</v>
+        <v>465.18</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>391.89</v>
+        <v>408.8</v>
       </c>
       <c r="K68" t="n">
-        <v>129.48</v>
+        <v>135.06</v>
       </c>
       <c r="L68" t="n">
-        <v>412.73</v>
+        <v>430.53</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>-217.82</v>
+        <v>-229.55</v>
       </c>
       <c r="K69" t="n">
-        <v>115.07</v>
+        <v>121.27</v>
       </c>
       <c r="L69" t="n">
-        <v>246.34</v>
+        <v>259.62</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>-84.84999999999999</v>
+        <v>-88.63</v>
       </c>
       <c r="K70" t="n">
-        <v>-308.16</v>
+        <v>-321.89</v>
       </c>
       <c r="L70" t="n">
-        <v>319.63</v>
+        <v>333.87</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>-224.81</v>
+        <v>-241.35</v>
       </c>
       <c r="K71" t="n">
-        <v>494.87</v>
+        <v>531.27</v>
       </c>
       <c r="L71" t="n">
-        <v>543.54</v>
+        <v>583.52</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>44.57</v>
+        <v>46.26</v>
       </c>
       <c r="K72" t="n">
-        <v>-273.21</v>
+        <v>-283.61</v>
       </c>
       <c r="L72" t="n">
-        <v>276.82</v>
+        <v>287.36</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-77.81</v>
+        <v>-81</v>
       </c>
       <c r="K73" t="n">
-        <v>-440.35</v>
+        <v>-458.4</v>
       </c>
       <c r="L73" t="n">
-        <v>447.17</v>
+        <v>465.5</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>125.75</v>
+        <v>118.03</v>
       </c>
       <c r="K74" t="n">
-        <v>-152.07</v>
+        <v>-142.74</v>
       </c>
       <c r="L74" t="n">
-        <v>197.33</v>
+        <v>185.22</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-28.37</v>
+        <v>-27.34</v>
       </c>
       <c r="K75" t="n">
-        <v>99.54000000000001</v>
+        <v>95.93000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>103.5</v>
+        <v>99.75</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-94.64</v>
+        <v>-91.01000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>-91.05</v>
+        <v>-87.56</v>
       </c>
       <c r="L76" t="n">
-        <v>131.33</v>
+        <v>126.29</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-6.25</v>
+        <v>-6.14</v>
       </c>
       <c r="K77" t="n">
-        <v>-207.52</v>
+        <v>-203.68</v>
       </c>
       <c r="L77" t="n">
-        <v>207.62</v>
+        <v>203.78</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>14.72</v>
+        <v>14.17</v>
       </c>
       <c r="K78" t="n">
-        <v>-302.84</v>
+        <v>-291.54</v>
       </c>
       <c r="L78" t="n">
-        <v>303.2</v>
+        <v>291.88</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>156.81</v>
+        <v>155.72</v>
       </c>
       <c r="K79" t="n">
-        <v>141.94</v>
+        <v>140.96</v>
       </c>
       <c r="L79" t="n">
-        <v>211.51</v>
+        <v>210.05</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>116.93</v>
+        <v>119.95</v>
       </c>
       <c r="K80" t="n">
-        <v>143.17</v>
+        <v>146.87</v>
       </c>
       <c r="L80" t="n">
-        <v>184.85</v>
+        <v>189.63</v>
       </c>
     </row>
     <row r="81">
@@ -3457,10 +3457,10 @@
         <v>-0.59</v>
       </c>
       <c r="K81" t="n">
-        <v>227.75</v>
+        <v>229.76</v>
       </c>
       <c r="L81" t="n">
-        <v>227.75</v>
+        <v>229.76</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-162.17</v>
+        <v>-163.99</v>
       </c>
       <c r="K82" t="n">
-        <v>-19.7</v>
+        <v>-19.92</v>
       </c>
       <c r="L82" t="n">
-        <v>163.36</v>
+        <v>165.2</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>245.36</v>
+        <v>255.91</v>
       </c>
       <c r="K83" t="n">
-        <v>-119.8</v>
+        <v>-124.95</v>
       </c>
       <c r="L83" t="n">
-        <v>273.05</v>
+        <v>284.78</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-382.3</v>
+        <v>-399.68</v>
       </c>
       <c r="K84" t="n">
-        <v>80.88</v>
+        <v>84.56</v>
       </c>
       <c r="L84" t="n">
-        <v>390.76</v>
+        <v>408.53</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-159.87</v>
+        <v>-167.17</v>
       </c>
       <c r="K85" t="n">
-        <v>-252.53</v>
+        <v>-264.07</v>
       </c>
       <c r="L85" t="n">
-        <v>298.89</v>
+        <v>312.54</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>400.16</v>
+        <v>417.28</v>
       </c>
       <c r="K86" t="n">
-        <v>216.18</v>
+        <v>225.43</v>
       </c>
       <c r="L86" t="n">
-        <v>454.83</v>
+        <v>474.28</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>11.66</v>
+        <v>12.33</v>
       </c>
       <c r="K87" t="n">
-        <v>-425.76</v>
+        <v>-450.46</v>
       </c>
       <c r="L87" t="n">
-        <v>425.91</v>
+        <v>450.62</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>23.93</v>
+        <v>25.66</v>
       </c>
       <c r="K88" t="n">
-        <v>337.99</v>
+        <v>362.52</v>
       </c>
       <c r="L88" t="n">
-        <v>338.83</v>
+        <v>363.43</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-11.xlsx
+++ b/output/2025-07-11.xlsx
@@ -640,13 +640,13 @@
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.31</v>
+        <v>-2.19</v>
       </c>
       <c r="K14" t="n">
-        <v>-105.52</v>
+        <v>-53.72</v>
       </c>
       <c r="L14" t="n">
-        <v>105.61</v>
+        <v>53.77</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-123.82</v>
+        <v>-60.79</v>
       </c>
       <c r="K15" t="n">
-        <v>195.17</v>
+        <v>95.81</v>
       </c>
       <c r="L15" t="n">
-        <v>231.13</v>
+        <v>113.46</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-115.03</v>
+        <v>-52.71</v>
       </c>
       <c r="K16" t="n">
-        <v>206.57</v>
+        <v>94.65000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>236.43</v>
+        <v>108.34</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>-77.09999999999999</v>
+        <v>-35.98</v>
       </c>
       <c r="K17" t="n">
-        <v>147.48</v>
+        <v>68.83</v>
       </c>
       <c r="L17" t="n">
-        <v>166.42</v>
+        <v>77.67</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>41.09</v>
+        <v>18.31</v>
       </c>
       <c r="K18" t="n">
-        <v>276.98</v>
+        <v>123.41</v>
       </c>
       <c r="L18" t="n">
-        <v>280.01</v>
+        <v>124.76</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>88.22</v>
+        <v>47.31</v>
       </c>
       <c r="K19" t="n">
-        <v>-34.04</v>
+        <v>-18.25</v>
       </c>
       <c r="L19" t="n">
-        <v>94.56</v>
+        <v>50.71</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-6.63</v>
+        <v>-2.28</v>
       </c>
       <c r="K20" t="n">
-        <v>-156.84</v>
+        <v>-53.97</v>
       </c>
       <c r="L20" t="n">
-        <v>156.98</v>
+        <v>54.02</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-126.84</v>
+        <v>-68.08</v>
       </c>
       <c r="K21" t="n">
-        <v>-240.51</v>
+        <v>-129.09</v>
       </c>
       <c r="L21" t="n">
-        <v>271.91</v>
+        <v>145.94</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-142.32</v>
+        <v>-70.44</v>
       </c>
       <c r="K22" t="n">
-        <v>-21.88</v>
+        <v>-10.83</v>
       </c>
       <c r="L22" t="n">
-        <v>143.99</v>
+        <v>71.27</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>303.07</v>
+        <v>142.12</v>
       </c>
       <c r="K23" t="n">
-        <v>-129.43</v>
+        <v>-60.69</v>
       </c>
       <c r="L23" t="n">
-        <v>329.55</v>
+        <v>154.54</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-259.6</v>
+        <v>-141.92</v>
       </c>
       <c r="K24" t="n">
-        <v>-149.76</v>
+        <v>-81.87</v>
       </c>
       <c r="L24" t="n">
-        <v>299.7</v>
+        <v>163.84</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>110.91</v>
+        <v>56.62</v>
       </c>
       <c r="K25" t="n">
-        <v>431.23</v>
+        <v>220.16</v>
       </c>
       <c r="L25" t="n">
-        <v>445.27</v>
+        <v>227.33</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-558.67</v>
+        <v>-307</v>
       </c>
       <c r="K26" t="n">
-        <v>-78.06</v>
+        <v>-42.89</v>
       </c>
       <c r="L26" t="n">
-        <v>564.09</v>
+        <v>309.98</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-415.62</v>
+        <v>-230.89</v>
       </c>
       <c r="K27" t="n">
-        <v>-127.47</v>
+        <v>-70.81999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>434.73</v>
+        <v>241.5</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>-126.39</v>
+        <v>-69.73999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>222.03</v>
+        <v>122.51</v>
       </c>
       <c r="L28" t="n">
-        <v>255.49</v>
+        <v>140.97</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>18</v>
       </c>
       <c r="J29" t="n">
-        <v>-197.48</v>
+        <v>-97.18000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>-8.029999999999999</v>
+        <v>-3.95</v>
       </c>
       <c r="L29" t="n">
-        <v>197.65</v>
+        <v>97.26000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>-119.65</v>
+        <v>-62.83</v>
       </c>
       <c r="K30" t="n">
-        <v>30.61</v>
+        <v>16.07</v>
       </c>
       <c r="L30" t="n">
-        <v>123.5</v>
+        <v>64.84999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>93.58</v>
+        <v>48.75</v>
       </c>
       <c r="K31" t="n">
-        <v>-53.03</v>
+        <v>-27.63</v>
       </c>
       <c r="L31" t="n">
-        <v>107.56</v>
+        <v>56.03</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>118.88</v>
+        <v>60.08</v>
       </c>
       <c r="K32" t="n">
-        <v>-97.72</v>
+        <v>-49.39</v>
       </c>
       <c r="L32" t="n">
-        <v>153.88</v>
+        <v>77.78</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-81.97</v>
+        <v>-37.61</v>
       </c>
       <c r="K33" t="n">
-        <v>243.78</v>
+        <v>111.84</v>
       </c>
       <c r="L33" t="n">
-        <v>257.2</v>
+        <v>118</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>132.93</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>-133.98</v>
+        <v>-68.72</v>
       </c>
       <c r="L34" t="n">
-        <v>188.74</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-137.98</v>
+        <v>-70.05</v>
       </c>
       <c r="K35" t="n">
-        <v>-153.23</v>
+        <v>-77.79000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>206.2</v>
+        <v>104.68</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>54.35</v>
+        <v>27.56</v>
       </c>
       <c r="K36" t="n">
-        <v>-201.98</v>
+        <v>-102.41</v>
       </c>
       <c r="L36" t="n">
-        <v>209.16</v>
+        <v>106.05</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>301.73</v>
+        <v>152.81</v>
       </c>
       <c r="K37" t="n">
-        <v>-12.32</v>
+        <v>-6.24</v>
       </c>
       <c r="L37" t="n">
-        <v>301.98</v>
+        <v>152.93</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>36.99</v>
+        <v>21.49</v>
       </c>
       <c r="K38" t="n">
-        <v>-305.79</v>
+        <v>-177.63</v>
       </c>
       <c r="L38" t="n">
-        <v>308.02</v>
+        <v>178.93</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>239.62</v>
+        <v>123.55</v>
       </c>
       <c r="K39" t="n">
-        <v>18.51</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>240.33</v>
+        <v>123.92</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>253.53</v>
+        <v>120.14</v>
       </c>
       <c r="K40" t="n">
-        <v>175.11</v>
+        <v>82.98</v>
       </c>
       <c r="L40" t="n">
-        <v>308.12</v>
+        <v>146.01</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>-285.66</v>
+        <v>-156.82</v>
       </c>
       <c r="K41" t="n">
-        <v>-347.56</v>
+        <v>-190.8</v>
       </c>
       <c r="L41" t="n">
-        <v>449.89</v>
+        <v>246.98</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>-31.95</v>
+        <v>-17.41</v>
       </c>
       <c r="K42" t="n">
-        <v>304.14</v>
+        <v>165.68</v>
       </c>
       <c r="L42" t="n">
-        <v>305.81</v>
+        <v>166.59</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>407.64</v>
+        <v>222.59</v>
       </c>
       <c r="K43" t="n">
-        <v>-138.09</v>
+        <v>-75.40000000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>430.4</v>
+        <v>235.01</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>56.14</v>
+        <v>24.42</v>
       </c>
       <c r="K44" t="n">
-        <v>95.87</v>
+        <v>41.7</v>
       </c>
       <c r="L44" t="n">
-        <v>111.1</v>
+        <v>48.33</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>1.44</v>
+        <v>0.62</v>
       </c>
       <c r="K45" t="n">
-        <v>149.32</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>149.32</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>-148.8</v>
+        <v>-69.95999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>45.64</v>
+        <v>21.46</v>
       </c>
       <c r="L46" t="n">
-        <v>155.64</v>
+        <v>73.18000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-221.98</v>
+        <v>-102.71</v>
       </c>
       <c r="K47" t="n">
-        <v>-112.26</v>
+        <v>-51.94</v>
       </c>
       <c r="L47" t="n">
-        <v>248.75</v>
+        <v>115.1</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-119.33</v>
+        <v>-59.7</v>
       </c>
       <c r="K48" t="n">
-        <v>117.19</v>
+        <v>58.63</v>
       </c>
       <c r="L48" t="n">
-        <v>167.25</v>
+        <v>83.67</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>38.57</v>
+        <v>23</v>
       </c>
       <c r="K49" t="n">
-        <v>53.99</v>
+        <v>32.19</v>
       </c>
       <c r="L49" t="n">
-        <v>66.34999999999999</v>
+        <v>39.56</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>219.16</v>
+        <v>106.08</v>
       </c>
       <c r="K50" t="n">
-        <v>191.84</v>
+        <v>92.84999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>291.26</v>
+        <v>140.97</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-98.61</v>
+        <v>-48.25</v>
       </c>
       <c r="K51" t="n">
-        <v>-276.81</v>
+        <v>-135.45</v>
       </c>
       <c r="L51" t="n">
-        <v>293.86</v>
+        <v>143.79</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>-59.75</v>
+        <v>-30.47</v>
       </c>
       <c r="K52" t="n">
-        <v>-256.38</v>
+        <v>-130.73</v>
       </c>
       <c r="L52" t="n">
-        <v>263.25</v>
+        <v>134.23</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>176.82</v>
+        <v>87.7</v>
       </c>
       <c r="K53" t="n">
-        <v>-220.51</v>
+        <v>-109.37</v>
       </c>
       <c r="L53" t="n">
-        <v>282.65</v>
+        <v>140.19</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-76.77</v>
+        <v>-34.92</v>
       </c>
       <c r="K54" t="n">
-        <v>291.64</v>
+        <v>132.66</v>
       </c>
       <c r="L54" t="n">
-        <v>301.57</v>
+        <v>137.18</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>-84.88</v>
+        <v>-44.39</v>
       </c>
       <c r="K55" t="n">
-        <v>162.79</v>
+        <v>85.14</v>
       </c>
       <c r="L55" t="n">
-        <v>183.59</v>
+        <v>96.02</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>44.56</v>
+        <v>23.52</v>
       </c>
       <c r="K56" t="n">
-        <v>384.67</v>
+        <v>203.1</v>
       </c>
       <c r="L56" t="n">
-        <v>387.25</v>
+        <v>204.45</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>299.3</v>
+        <v>161.7</v>
       </c>
       <c r="K57" t="n">
-        <v>-29.93</v>
+        <v>-16.17</v>
       </c>
       <c r="L57" t="n">
-        <v>300.8</v>
+        <v>162.51</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>-79.64</v>
+        <v>-42.49</v>
       </c>
       <c r="K58" t="n">
-        <v>353.95</v>
+        <v>188.87</v>
       </c>
       <c r="L58" t="n">
-        <v>362.8</v>
+        <v>193.59</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>-53.97</v>
+        <v>-26.07</v>
       </c>
       <c r="K59" t="n">
-        <v>123.73</v>
+        <v>59.76</v>
       </c>
       <c r="L59" t="n">
-        <v>134.99</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>140.55</v>
+        <v>58.19</v>
       </c>
       <c r="K60" t="n">
-        <v>-55.1</v>
+        <v>-22.82</v>
       </c>
       <c r="L60" t="n">
-        <v>150.96</v>
+        <v>62.51</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>105.07</v>
+        <v>50.06</v>
       </c>
       <c r="K61" t="n">
-        <v>-115.19</v>
+        <v>-54.88</v>
       </c>
       <c r="L61" t="n">
-        <v>155.91</v>
+        <v>74.28</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-6.56</v>
+        <v>-2.81</v>
       </c>
       <c r="K62" t="n">
-        <v>-248.31</v>
+        <v>-106.23</v>
       </c>
       <c r="L62" t="n">
-        <v>248.39</v>
+        <v>106.27</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-124.96</v>
+        <v>-59.26</v>
       </c>
       <c r="K63" t="n">
-        <v>124.46</v>
+        <v>59.02</v>
       </c>
       <c r="L63" t="n">
-        <v>176.36</v>
+        <v>83.64</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>52.38</v>
+        <v>27.1</v>
       </c>
       <c r="K64" t="n">
-        <v>-195.11</v>
+        <v>-100.93</v>
       </c>
       <c r="L64" t="n">
-        <v>202.01</v>
+        <v>104.51</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>-23.87</v>
+        <v>-11.54</v>
       </c>
       <c r="K65" t="n">
-        <v>-268.19</v>
+        <v>-129.58</v>
       </c>
       <c r="L65" t="n">
-        <v>269.25</v>
+        <v>130.09</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-332.76</v>
+        <v>-162.91</v>
       </c>
       <c r="K66" t="n">
-        <v>-64.69</v>
+        <v>-31.67</v>
       </c>
       <c r="L66" t="n">
-        <v>338.99</v>
+        <v>165.96</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>122.95</v>
+        <v>58.82</v>
       </c>
       <c r="K67" t="n">
-        <v>448.64</v>
+        <v>214.63</v>
       </c>
       <c r="L67" t="n">
-        <v>465.18</v>
+        <v>222.54</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>408.8</v>
+        <v>184.13</v>
       </c>
       <c r="K68" t="n">
-        <v>135.06</v>
+        <v>60.84</v>
       </c>
       <c r="L68" t="n">
-        <v>430.53</v>
+        <v>193.92</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>-229.55</v>
+        <v>-117.66</v>
       </c>
       <c r="K69" t="n">
-        <v>121.27</v>
+        <v>62.16</v>
       </c>
       <c r="L69" t="n">
-        <v>259.62</v>
+        <v>133.07</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>-88.63</v>
+        <v>-41.93</v>
       </c>
       <c r="K70" t="n">
-        <v>-321.89</v>
+        <v>-152.27</v>
       </c>
       <c r="L70" t="n">
-        <v>333.87</v>
+        <v>157.94</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>-241.35</v>
+        <v>-131.1</v>
       </c>
       <c r="K71" t="n">
-        <v>531.27</v>
+        <v>288.59</v>
       </c>
       <c r="L71" t="n">
-        <v>583.52</v>
+        <v>316.97</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>46.26</v>
+        <v>26.28</v>
       </c>
       <c r="K72" t="n">
-        <v>-283.61</v>
+        <v>-161.09</v>
       </c>
       <c r="L72" t="n">
-        <v>287.36</v>
+        <v>163.22</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-81</v>
+        <v>-45.27</v>
       </c>
       <c r="K73" t="n">
-        <v>-458.4</v>
+        <v>-256.19</v>
       </c>
       <c r="L73" t="n">
-        <v>465.5</v>
+        <v>260.16</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>118.03</v>
+        <v>61.65</v>
       </c>
       <c r="K74" t="n">
-        <v>-142.74</v>
+        <v>-74.56</v>
       </c>
       <c r="L74" t="n">
-        <v>185.22</v>
+        <v>96.75</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-27.34</v>
+        <v>-12.53</v>
       </c>
       <c r="K75" t="n">
-        <v>95.93000000000001</v>
+        <v>43.96</v>
       </c>
       <c r="L75" t="n">
-        <v>99.75</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-91.01000000000001</v>
+        <v>-41.27</v>
       </c>
       <c r="K76" t="n">
-        <v>-87.56</v>
+        <v>-39.71</v>
       </c>
       <c r="L76" t="n">
-        <v>126.29</v>
+        <v>57.27</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-6.14</v>
+        <v>-2.69</v>
       </c>
       <c r="K77" t="n">
-        <v>-203.68</v>
+        <v>-89.36</v>
       </c>
       <c r="L77" t="n">
-        <v>203.78</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>14.17</v>
+        <v>6.42</v>
       </c>
       <c r="K78" t="n">
-        <v>-291.54</v>
+        <v>-132.21</v>
       </c>
       <c r="L78" t="n">
-        <v>291.88</v>
+        <v>132.36</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>155.72</v>
+        <v>79.04000000000001</v>
       </c>
       <c r="K79" t="n">
-        <v>140.96</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>210.05</v>
+        <v>106.61</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>119.95</v>
+        <v>58.67</v>
       </c>
       <c r="K80" t="n">
-        <v>146.87</v>
+        <v>71.84</v>
       </c>
       <c r="L80" t="n">
-        <v>189.63</v>
+        <v>92.75</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.59</v>
+        <v>-0.29</v>
       </c>
       <c r="K81" t="n">
-        <v>229.76</v>
+        <v>113.54</v>
       </c>
       <c r="L81" t="n">
-        <v>229.76</v>
+        <v>113.54</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-163.99</v>
+        <v>-82.8</v>
       </c>
       <c r="K82" t="n">
-        <v>-19.92</v>
+        <v>-10.06</v>
       </c>
       <c r="L82" t="n">
-        <v>165.2</v>
+        <v>83.41</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>255.91</v>
+        <v>119.39</v>
       </c>
       <c r="K83" t="n">
-        <v>-124.95</v>
+        <v>-58.29</v>
       </c>
       <c r="L83" t="n">
-        <v>284.78</v>
+        <v>132.86</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-399.68</v>
+        <v>-186.46</v>
       </c>
       <c r="K84" t="n">
-        <v>84.56</v>
+        <v>39.45</v>
       </c>
       <c r="L84" t="n">
-        <v>408.53</v>
+        <v>190.59</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-167.17</v>
+        <v>-74.22</v>
       </c>
       <c r="K85" t="n">
-        <v>-264.07</v>
+        <v>-117.23</v>
       </c>
       <c r="L85" t="n">
-        <v>312.54</v>
+        <v>138.75</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>417.28</v>
+        <v>229.88</v>
       </c>
       <c r="K86" t="n">
-        <v>225.43</v>
+        <v>124.19</v>
       </c>
       <c r="L86" t="n">
-        <v>474.28</v>
+        <v>261.29</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>12.33</v>
+        <v>6.68</v>
       </c>
       <c r="K87" t="n">
-        <v>-450.46</v>
+        <v>-243.8</v>
       </c>
       <c r="L87" t="n">
-        <v>450.62</v>
+        <v>243.89</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>25.66</v>
+        <v>13.58</v>
       </c>
       <c r="K88" t="n">
-        <v>362.52</v>
+        <v>191.82</v>
       </c>
       <c r="L88" t="n">
-        <v>363.43</v>
+        <v>192.3</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-11.xlsx
+++ b/output/2025-07-11.xlsx
@@ -640,13 +640,13 @@
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.19</v>
+        <v>-2.27</v>
       </c>
       <c r="K14" t="n">
-        <v>-53.72</v>
+        <v>-55.54</v>
       </c>
       <c r="L14" t="n">
-        <v>53.77</v>
+        <v>55.58</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-60.79</v>
+        <v>-57.03</v>
       </c>
       <c r="K15" t="n">
-        <v>95.81</v>
+        <v>89.89</v>
       </c>
       <c r="L15" t="n">
-        <v>113.46</v>
+        <v>106.46</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-52.71</v>
+        <v>-49.28</v>
       </c>
       <c r="K16" t="n">
-        <v>94.65000000000001</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>108.34</v>
+        <v>101.28</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>-35.98</v>
+        <v>-35.81</v>
       </c>
       <c r="K17" t="n">
-        <v>68.83</v>
+        <v>68.5</v>
       </c>
       <c r="L17" t="n">
-        <v>77.67</v>
+        <v>77.29000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>18.31</v>
+        <v>17.15</v>
       </c>
       <c r="K18" t="n">
-        <v>123.41</v>
+        <v>115.64</v>
       </c>
       <c r="L18" t="n">
-        <v>124.76</v>
+        <v>116.91</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>47.31</v>
+        <v>50.71</v>
       </c>
       <c r="K19" t="n">
-        <v>-18.25</v>
+        <v>-19.57</v>
       </c>
       <c r="L19" t="n">
-        <v>50.71</v>
+        <v>54.35</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.28</v>
+        <v>-1.84</v>
       </c>
       <c r="K20" t="n">
-        <v>-53.97</v>
+        <v>-43.53</v>
       </c>
       <c r="L20" t="n">
-        <v>54.02</v>
+        <v>43.57</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-68.08</v>
+        <v>-65.83</v>
       </c>
       <c r="K21" t="n">
-        <v>-129.09</v>
+        <v>-124.83</v>
       </c>
       <c r="L21" t="n">
-        <v>145.94</v>
+        <v>141.12</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-70.44</v>
+        <v>-75.45</v>
       </c>
       <c r="K22" t="n">
-        <v>-10.83</v>
+        <v>-11.6</v>
       </c>
       <c r="L22" t="n">
-        <v>71.27</v>
+        <v>76.34</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>142.12</v>
+        <v>145.32</v>
       </c>
       <c r="K23" t="n">
-        <v>-60.69</v>
+        <v>-62.06</v>
       </c>
       <c r="L23" t="n">
-        <v>154.54</v>
+        <v>158.01</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-141.92</v>
+        <v>-142.33</v>
       </c>
       <c r="K24" t="n">
-        <v>-81.87</v>
+        <v>-82.09999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>163.84</v>
+        <v>164.31</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>56.62</v>
+        <v>55.06</v>
       </c>
       <c r="K25" t="n">
-        <v>220.16</v>
+        <v>214.09</v>
       </c>
       <c r="L25" t="n">
-        <v>227.33</v>
+        <v>221.06</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-307</v>
+        <v>-304.35</v>
       </c>
       <c r="K26" t="n">
-        <v>-42.89</v>
+        <v>-42.53</v>
       </c>
       <c r="L26" t="n">
-        <v>309.98</v>
+        <v>307.31</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-230.89</v>
+        <v>-233.43</v>
       </c>
       <c r="K27" t="n">
-        <v>-70.81999999999999</v>
+        <v>-71.59</v>
       </c>
       <c r="L27" t="n">
-        <v>241.5</v>
+        <v>244.16</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>-69.73999999999999</v>
+        <v>-77.34999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>122.51</v>
+        <v>135.88</v>
       </c>
       <c r="L28" t="n">
-        <v>140.97</v>
+        <v>156.35</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>18</v>
       </c>
       <c r="J29" t="n">
-        <v>-97.18000000000001</v>
+        <v>-92.98</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.95</v>
+        <v>-3.78</v>
       </c>
       <c r="L29" t="n">
-        <v>97.26000000000001</v>
+        <v>93.06</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>-62.83</v>
+        <v>-62.4</v>
       </c>
       <c r="K30" t="n">
-        <v>16.07</v>
+        <v>15.97</v>
       </c>
       <c r="L30" t="n">
-        <v>64.84999999999999</v>
+        <v>64.41</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>48.75</v>
+        <v>49.26</v>
       </c>
       <c r="K31" t="n">
-        <v>-27.63</v>
+        <v>-27.92</v>
       </c>
       <c r="L31" t="n">
-        <v>56.03</v>
+        <v>56.62</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>60.08</v>
+        <v>60.06</v>
       </c>
       <c r="K32" t="n">
-        <v>-49.39</v>
+        <v>-49.37</v>
       </c>
       <c r="L32" t="n">
-        <v>77.78</v>
+        <v>77.75</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-37.61</v>
+        <v>-35.24</v>
       </c>
       <c r="K33" t="n">
-        <v>111.84</v>
+        <v>104.81</v>
       </c>
       <c r="L33" t="n">
-        <v>118</v>
+        <v>110.58</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>68.18000000000001</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>-68.72</v>
+        <v>-66.62</v>
       </c>
       <c r="L34" t="n">
-        <v>96.8</v>
+        <v>93.84999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-70.05</v>
+        <v>-70.48999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>-77.79000000000001</v>
+        <v>-78.29000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>104.68</v>
+        <v>105.35</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>27.56</v>
+        <v>27.6</v>
       </c>
       <c r="K36" t="n">
-        <v>-102.41</v>
+        <v>-102.57</v>
       </c>
       <c r="L36" t="n">
-        <v>106.05</v>
+        <v>106.22</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>152.81</v>
+        <v>148.19</v>
       </c>
       <c r="K37" t="n">
-        <v>-6.24</v>
+        <v>-6.05</v>
       </c>
       <c r="L37" t="n">
-        <v>152.93</v>
+        <v>148.32</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>21.49</v>
+        <v>21.12</v>
       </c>
       <c r="K38" t="n">
-        <v>-177.63</v>
+        <v>-174.6</v>
       </c>
       <c r="L38" t="n">
-        <v>178.93</v>
+        <v>175.88</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>123.55</v>
+        <v>127.68</v>
       </c>
       <c r="K39" t="n">
-        <v>9.550000000000001</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>123.92</v>
+        <v>128.06</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>120.14</v>
+        <v>122.93</v>
       </c>
       <c r="K40" t="n">
-        <v>82.98</v>
+        <v>84.91</v>
       </c>
       <c r="L40" t="n">
-        <v>146.01</v>
+        <v>149.4</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>-156.82</v>
+        <v>-160.15</v>
       </c>
       <c r="K41" t="n">
-        <v>-190.8</v>
+        <v>-194.85</v>
       </c>
       <c r="L41" t="n">
-        <v>246.98</v>
+        <v>252.21</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>-17.41</v>
+        <v>-18.72</v>
       </c>
       <c r="K42" t="n">
-        <v>165.68</v>
+        <v>178.15</v>
       </c>
       <c r="L42" t="n">
-        <v>166.59</v>
+        <v>179.14</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>222.59</v>
+        <v>227.99</v>
       </c>
       <c r="K43" t="n">
-        <v>-75.40000000000001</v>
+        <v>-77.23</v>
       </c>
       <c r="L43" t="n">
-        <v>235.01</v>
+        <v>240.72</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>24.42</v>
+        <v>24.99</v>
       </c>
       <c r="K44" t="n">
-        <v>41.7</v>
+        <v>42.67</v>
       </c>
       <c r="L44" t="n">
-        <v>48.33</v>
+        <v>49.45</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="K45" t="n">
-        <v>64.09999999999999</v>
+        <v>62.59</v>
       </c>
       <c r="L45" t="n">
-        <v>64.09999999999999</v>
+        <v>62.59</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>-69.95999999999999</v>
+        <v>-68.68000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>21.46</v>
+        <v>21.07</v>
       </c>
       <c r="L46" t="n">
-        <v>73.18000000000001</v>
+        <v>71.84</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-102.71</v>
+        <v>-97.16</v>
       </c>
       <c r="K47" t="n">
-        <v>-51.94</v>
+        <v>-49.13</v>
       </c>
       <c r="L47" t="n">
-        <v>115.1</v>
+        <v>108.87</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-59.7</v>
+        <v>-58.38</v>
       </c>
       <c r="K48" t="n">
-        <v>58.63</v>
+        <v>57.33</v>
       </c>
       <c r="L48" t="n">
-        <v>83.67</v>
+        <v>81.81999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>23</v>
+        <v>24.3</v>
       </c>
       <c r="K49" t="n">
-        <v>32.19</v>
+        <v>34.01</v>
       </c>
       <c r="L49" t="n">
-        <v>39.56</v>
+        <v>41.79</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>106.08</v>
+        <v>103.99</v>
       </c>
       <c r="K50" t="n">
-        <v>92.84999999999999</v>
+        <v>91.02</v>
       </c>
       <c r="L50" t="n">
-        <v>140.97</v>
+        <v>138.2</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-48.25</v>
+        <v>-47.11</v>
       </c>
       <c r="K51" t="n">
-        <v>-135.45</v>
+        <v>-132.24</v>
       </c>
       <c r="L51" t="n">
-        <v>143.79</v>
+        <v>140.38</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>-30.47</v>
+        <v>-29.9</v>
       </c>
       <c r="K52" t="n">
-        <v>-130.73</v>
+        <v>-128.29</v>
       </c>
       <c r="L52" t="n">
-        <v>134.23</v>
+        <v>131.73</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>87.7</v>
+        <v>90.16</v>
       </c>
       <c r="K53" t="n">
-        <v>-109.37</v>
+        <v>-112.44</v>
       </c>
       <c r="L53" t="n">
-        <v>140.19</v>
+        <v>144.12</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-34.92</v>
+        <v>-35.94</v>
       </c>
       <c r="K54" t="n">
-        <v>132.66</v>
+        <v>136.54</v>
       </c>
       <c r="L54" t="n">
-        <v>137.18</v>
+        <v>141.19</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>-44.39</v>
+        <v>-48.23</v>
       </c>
       <c r="K55" t="n">
-        <v>85.14</v>
+        <v>92.48999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>96.02</v>
+        <v>104.31</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>23.52</v>
+        <v>27.06</v>
       </c>
       <c r="K56" t="n">
-        <v>203.1</v>
+        <v>233.61</v>
       </c>
       <c r="L56" t="n">
-        <v>204.45</v>
+        <v>235.18</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>161.7</v>
+        <v>180.5</v>
       </c>
       <c r="K57" t="n">
-        <v>-16.17</v>
+        <v>-18.05</v>
       </c>
       <c r="L57" t="n">
-        <v>162.51</v>
+        <v>181.4</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>-42.49</v>
+        <v>-47.17</v>
       </c>
       <c r="K58" t="n">
-        <v>188.87</v>
+        <v>209.63</v>
       </c>
       <c r="L58" t="n">
-        <v>193.59</v>
+        <v>214.87</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>-26.07</v>
+        <v>-25.82</v>
       </c>
       <c r="K59" t="n">
-        <v>59.76</v>
+        <v>59.19</v>
       </c>
       <c r="L59" t="n">
-        <v>65.2</v>
+        <v>64.56999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>58.19</v>
+        <v>56.66</v>
       </c>
       <c r="K60" t="n">
-        <v>-22.82</v>
+        <v>-22.21</v>
       </c>
       <c r="L60" t="n">
-        <v>62.51</v>
+        <v>60.86</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>50.06</v>
+        <v>48.96</v>
       </c>
       <c r="K61" t="n">
-        <v>-54.88</v>
+        <v>-53.68</v>
       </c>
       <c r="L61" t="n">
-        <v>74.28</v>
+        <v>72.65000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-2.81</v>
+        <v>-2.65</v>
       </c>
       <c r="K62" t="n">
-        <v>-106.23</v>
+        <v>-100.11</v>
       </c>
       <c r="L62" t="n">
-        <v>106.27</v>
+        <v>100.14</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-59.26</v>
+        <v>-57.61</v>
       </c>
       <c r="K63" t="n">
-        <v>59.02</v>
+        <v>57.38</v>
       </c>
       <c r="L63" t="n">
-        <v>83.64</v>
+        <v>81.31</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>27.1</v>
+        <v>26.26</v>
       </c>
       <c r="K64" t="n">
-        <v>-100.93</v>
+        <v>-97.81999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>104.51</v>
+        <v>101.28</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>-11.54</v>
+        <v>-11.42</v>
       </c>
       <c r="K65" t="n">
-        <v>-129.58</v>
+        <v>-128.25</v>
       </c>
       <c r="L65" t="n">
-        <v>130.09</v>
+        <v>128.76</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-162.91</v>
+        <v>-156.68</v>
       </c>
       <c r="K66" t="n">
-        <v>-31.67</v>
+        <v>-30.46</v>
       </c>
       <c r="L66" t="n">
-        <v>165.96</v>
+        <v>159.61</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>58.82</v>
+        <v>55.09</v>
       </c>
       <c r="K67" t="n">
-        <v>214.63</v>
+        <v>201.01</v>
       </c>
       <c r="L67" t="n">
-        <v>222.54</v>
+        <v>208.42</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>184.13</v>
+        <v>183.16</v>
       </c>
       <c r="K68" t="n">
-        <v>60.84</v>
+        <v>60.52</v>
       </c>
       <c r="L68" t="n">
-        <v>193.92</v>
+        <v>192.9</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>-117.66</v>
+        <v>-121.63</v>
       </c>
       <c r="K69" t="n">
-        <v>62.16</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="L69" t="n">
-        <v>133.07</v>
+        <v>137.56</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>-41.93</v>
+        <v>-36.16</v>
       </c>
       <c r="K70" t="n">
-        <v>-152.27</v>
+        <v>-131.32</v>
       </c>
       <c r="L70" t="n">
-        <v>157.94</v>
+        <v>136.21</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>-131.1</v>
+        <v>-132.22</v>
       </c>
       <c r="K71" t="n">
-        <v>288.59</v>
+        <v>291.05</v>
       </c>
       <c r="L71" t="n">
-        <v>316.97</v>
+        <v>319.68</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>26.28</v>
+        <v>26.92</v>
       </c>
       <c r="K72" t="n">
-        <v>-161.09</v>
+        <v>-165</v>
       </c>
       <c r="L72" t="n">
-        <v>163.22</v>
+        <v>167.18</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-45.27</v>
+        <v>-44.63</v>
       </c>
       <c r="K73" t="n">
-        <v>-256.19</v>
+        <v>-252.6</v>
       </c>
       <c r="L73" t="n">
-        <v>260.16</v>
+        <v>256.51</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>61.65</v>
+        <v>58.85</v>
       </c>
       <c r="K74" t="n">
-        <v>-74.56</v>
+        <v>-71.16</v>
       </c>
       <c r="L74" t="n">
-        <v>96.75</v>
+        <v>92.34</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-12.53</v>
+        <v>-13.14</v>
       </c>
       <c r="K75" t="n">
-        <v>43.96</v>
+        <v>46.1</v>
       </c>
       <c r="L75" t="n">
-        <v>45.71</v>
+        <v>47.93</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-41.27</v>
+        <v>-41.54</v>
       </c>
       <c r="K76" t="n">
-        <v>-39.71</v>
+        <v>-39.96</v>
       </c>
       <c r="L76" t="n">
-        <v>57.27</v>
+        <v>57.64</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-2.69</v>
+        <v>-2.6</v>
       </c>
       <c r="K77" t="n">
-        <v>-89.36</v>
+        <v>-86.13</v>
       </c>
       <c r="L77" t="n">
-        <v>89.40000000000001</v>
+        <v>86.17</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>6.42</v>
+        <v>5.96</v>
       </c>
       <c r="K78" t="n">
-        <v>-132.21</v>
+        <v>-122.62</v>
       </c>
       <c r="L78" t="n">
-        <v>132.36</v>
+        <v>122.76</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>79.04000000000001</v>
+        <v>76.28</v>
       </c>
       <c r="K79" t="n">
-        <v>71.54000000000001</v>
+        <v>69.05</v>
       </c>
       <c r="L79" t="n">
-        <v>106.61</v>
+        <v>102.89</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>58.67</v>
+        <v>61.26</v>
       </c>
       <c r="K80" t="n">
-        <v>71.84</v>
+        <v>75.01000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>92.75</v>
+        <v>96.84</v>
       </c>
     </row>
     <row r="81">
@@ -3457,10 +3457,10 @@
         <v>-0.29</v>
       </c>
       <c r="K81" t="n">
-        <v>113.54</v>
+        <v>113.26</v>
       </c>
       <c r="L81" t="n">
-        <v>113.54</v>
+        <v>113.26</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-82.8</v>
+        <v>-86.31</v>
       </c>
       <c r="K82" t="n">
-        <v>-10.06</v>
+        <v>-10.48</v>
       </c>
       <c r="L82" t="n">
-        <v>83.41</v>
+        <v>86.94</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>119.39</v>
+        <v>123.73</v>
       </c>
       <c r="K83" t="n">
-        <v>-58.29</v>
+        <v>-60.42</v>
       </c>
       <c r="L83" t="n">
-        <v>132.86</v>
+        <v>137.69</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-186.46</v>
+        <v>-185</v>
       </c>
       <c r="K84" t="n">
-        <v>39.45</v>
+        <v>39.14</v>
       </c>
       <c r="L84" t="n">
-        <v>190.59</v>
+        <v>189.09</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-74.22</v>
+        <v>-77.91</v>
       </c>
       <c r="K85" t="n">
-        <v>-117.23</v>
+        <v>-123.07</v>
       </c>
       <c r="L85" t="n">
-        <v>138.75</v>
+        <v>145.66</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>229.88</v>
+        <v>230.66</v>
       </c>
       <c r="K86" t="n">
-        <v>124.19</v>
+        <v>124.61</v>
       </c>
       <c r="L86" t="n">
-        <v>261.29</v>
+        <v>262.17</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>6.68</v>
+        <v>6.93</v>
       </c>
       <c r="K87" t="n">
-        <v>-243.8</v>
+        <v>-252.99</v>
       </c>
       <c r="L87" t="n">
-        <v>243.89</v>
+        <v>253.09</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>13.58</v>
+        <v>16.03</v>
       </c>
       <c r="K88" t="n">
-        <v>191.82</v>
+        <v>226.5</v>
       </c>
       <c r="L88" t="n">
-        <v>192.3</v>
+        <v>227.07</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-11.xlsx
+++ b/output/2025-07-11.xlsx
@@ -640,13 +640,13 @@
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.27</v>
+        <v>-2.37</v>
       </c>
       <c r="K14" t="n">
-        <v>-55.54</v>
+        <v>-58.08</v>
       </c>
       <c r="L14" t="n">
-        <v>55.58</v>
+        <v>58.13</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-57.03</v>
+        <v>-53.59</v>
       </c>
       <c r="K15" t="n">
-        <v>89.89</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>106.46</v>
+        <v>100.03</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-49.28</v>
+        <v>-46.61</v>
       </c>
       <c r="K16" t="n">
-        <v>88.48999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="L16" t="n">
-        <v>101.28</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>-35.81</v>
+        <v>-36.46</v>
       </c>
       <c r="K17" t="n">
-        <v>68.5</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>77.29000000000001</v>
+        <v>78.69</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>17.15</v>
+        <v>16.43</v>
       </c>
       <c r="K18" t="n">
-        <v>115.64</v>
+        <v>110.74</v>
       </c>
       <c r="L18" t="n">
-        <v>116.91</v>
+        <v>111.95</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>50.71</v>
+        <v>54.64</v>
       </c>
       <c r="K19" t="n">
-        <v>-19.57</v>
+        <v>-21.08</v>
       </c>
       <c r="L19" t="n">
-        <v>54.35</v>
+        <v>58.57</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.84</v>
+        <v>-2.01</v>
       </c>
       <c r="K20" t="n">
-        <v>-43.53</v>
+        <v>-47.47</v>
       </c>
       <c r="L20" t="n">
-        <v>43.57</v>
+        <v>47.51</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-65.83</v>
+        <v>-63.26</v>
       </c>
       <c r="K21" t="n">
-        <v>-124.83</v>
+        <v>-119.95</v>
       </c>
       <c r="L21" t="n">
-        <v>141.12</v>
+        <v>135.61</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-75.45</v>
+        <v>-81.73999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>-11.6</v>
+        <v>-12.57</v>
       </c>
       <c r="L22" t="n">
-        <v>76.34</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>145.32</v>
+        <v>147.78</v>
       </c>
       <c r="K23" t="n">
-        <v>-62.06</v>
+        <v>-63.11</v>
       </c>
       <c r="L23" t="n">
-        <v>158.01</v>
+        <v>160.69</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-142.33</v>
+        <v>-142.5</v>
       </c>
       <c r="K24" t="n">
-        <v>-82.09999999999999</v>
+        <v>-82.2</v>
       </c>
       <c r="L24" t="n">
-        <v>164.31</v>
+        <v>164.5</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>55.06</v>
+        <v>53.01</v>
       </c>
       <c r="K25" t="n">
-        <v>214.09</v>
+        <v>206.1</v>
       </c>
       <c r="L25" t="n">
-        <v>221.06</v>
+        <v>212.8</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-304.35</v>
+        <v>-291.13</v>
       </c>
       <c r="K26" t="n">
-        <v>-42.53</v>
+        <v>-40.68</v>
       </c>
       <c r="L26" t="n">
-        <v>307.31</v>
+        <v>293.96</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-233.43</v>
+        <v>-231.37</v>
       </c>
       <c r="K27" t="n">
-        <v>-71.59</v>
+        <v>-70.95999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>244.16</v>
+        <v>242.01</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>-77.34999999999999</v>
+        <v>-84.08</v>
       </c>
       <c r="K28" t="n">
-        <v>135.88</v>
+        <v>147.7</v>
       </c>
       <c r="L28" t="n">
-        <v>156.35</v>
+        <v>169.96</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>18</v>
       </c>
       <c r="J29" t="n">
-        <v>-92.98</v>
+        <v>-89.51000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.78</v>
+        <v>-3.64</v>
       </c>
       <c r="L29" t="n">
-        <v>93.06</v>
+        <v>89.58</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>-62.4</v>
+        <v>-62.22</v>
       </c>
       <c r="K30" t="n">
-        <v>15.97</v>
+        <v>15.92</v>
       </c>
       <c r="L30" t="n">
-        <v>64.41</v>
+        <v>64.23</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>49.26</v>
+        <v>50.13</v>
       </c>
       <c r="K31" t="n">
-        <v>-27.92</v>
+        <v>-28.41</v>
       </c>
       <c r="L31" t="n">
-        <v>56.62</v>
+        <v>57.62</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>60.06</v>
+        <v>60.66</v>
       </c>
       <c r="K32" t="n">
-        <v>-49.37</v>
+        <v>-49.86</v>
       </c>
       <c r="L32" t="n">
-        <v>77.75</v>
+        <v>78.52</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-35.24</v>
+        <v>-33.55</v>
       </c>
       <c r="K33" t="n">
-        <v>104.81</v>
+        <v>99.78</v>
       </c>
       <c r="L33" t="n">
-        <v>110.58</v>
+        <v>105.27</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>66.09999999999999</v>
+        <v>64.27</v>
       </c>
       <c r="K34" t="n">
-        <v>-66.62</v>
+        <v>-64.77</v>
       </c>
       <c r="L34" t="n">
-        <v>93.84999999999999</v>
+        <v>91.23999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-70.48999999999999</v>
+        <v>-71.22</v>
       </c>
       <c r="K35" t="n">
-        <v>-78.29000000000001</v>
+        <v>-79.09</v>
       </c>
       <c r="L35" t="n">
-        <v>105.35</v>
+        <v>106.43</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>27.6</v>
+        <v>27.74</v>
       </c>
       <c r="K36" t="n">
-        <v>-102.57</v>
+        <v>-103.1</v>
       </c>
       <c r="L36" t="n">
-        <v>106.22</v>
+        <v>106.77</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>148.19</v>
+        <v>143.47</v>
       </c>
       <c r="K37" t="n">
-        <v>-6.05</v>
+        <v>-5.86</v>
       </c>
       <c r="L37" t="n">
-        <v>148.32</v>
+        <v>143.59</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>21.12</v>
+        <v>20.7</v>
       </c>
       <c r="K38" t="n">
-        <v>-174.6</v>
+        <v>-171.15</v>
       </c>
       <c r="L38" t="n">
-        <v>175.88</v>
+        <v>172.39</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>127.68</v>
+        <v>131.86</v>
       </c>
       <c r="K39" t="n">
-        <v>9.859999999999999</v>
+        <v>10.19</v>
       </c>
       <c r="L39" t="n">
-        <v>128.06</v>
+        <v>132.26</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>122.93</v>
+        <v>125.17</v>
       </c>
       <c r="K40" t="n">
-        <v>84.91</v>
+        <v>86.45</v>
       </c>
       <c r="L40" t="n">
-        <v>149.4</v>
+        <v>152.12</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>-160.15</v>
+        <v>-158.6</v>
       </c>
       <c r="K41" t="n">
-        <v>-194.85</v>
+        <v>-192.97</v>
       </c>
       <c r="L41" t="n">
-        <v>252.21</v>
+        <v>249.78</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>-18.72</v>
+        <v>-19.48</v>
       </c>
       <c r="K42" t="n">
-        <v>178.15</v>
+        <v>185.45</v>
       </c>
       <c r="L42" t="n">
-        <v>179.14</v>
+        <v>186.47</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>227.99</v>
+        <v>225.29</v>
       </c>
       <c r="K43" t="n">
-        <v>-77.23</v>
+        <v>-76.31999999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>240.72</v>
+        <v>237.87</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>24.99</v>
+        <v>26.39</v>
       </c>
       <c r="K44" t="n">
-        <v>42.67</v>
+        <v>45.07</v>
       </c>
       <c r="L44" t="n">
-        <v>49.45</v>
+        <v>52.23</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="K45" t="n">
-        <v>62.59</v>
+        <v>63.02</v>
       </c>
       <c r="L45" t="n">
-        <v>62.59</v>
+        <v>63.02</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>-68.68000000000001</v>
+        <v>-68.59999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>21.07</v>
+        <v>21.04</v>
       </c>
       <c r="L46" t="n">
-        <v>71.84</v>
+        <v>71.76000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-97.16</v>
+        <v>-93.41</v>
       </c>
       <c r="K47" t="n">
-        <v>-49.13</v>
+        <v>-47.24</v>
       </c>
       <c r="L47" t="n">
-        <v>108.87</v>
+        <v>104.67</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-58.38</v>
+        <v>-57.58</v>
       </c>
       <c r="K48" t="n">
-        <v>57.33</v>
+        <v>56.55</v>
       </c>
       <c r="L48" t="n">
-        <v>81.81999999999999</v>
+        <v>80.70999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>24.3</v>
+        <v>26.76</v>
       </c>
       <c r="K49" t="n">
-        <v>34.01</v>
+        <v>37.46</v>
       </c>
       <c r="L49" t="n">
-        <v>41.79</v>
+        <v>46.03</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>103.99</v>
+        <v>102.97</v>
       </c>
       <c r="K50" t="n">
-        <v>91.02</v>
+        <v>90.13</v>
       </c>
       <c r="L50" t="n">
-        <v>138.2</v>
+        <v>136.84</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-47.11</v>
+        <v>-46.31</v>
       </c>
       <c r="K51" t="n">
-        <v>-132.24</v>
+        <v>-129.99</v>
       </c>
       <c r="L51" t="n">
-        <v>140.38</v>
+        <v>137.99</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>-29.9</v>
+        <v>-29.32</v>
       </c>
       <c r="K52" t="n">
-        <v>-128.29</v>
+        <v>-125.8</v>
       </c>
       <c r="L52" t="n">
-        <v>131.73</v>
+        <v>129.17</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>90.16</v>
+        <v>92.45</v>
       </c>
       <c r="K53" t="n">
-        <v>-112.44</v>
+        <v>-115.3</v>
       </c>
       <c r="L53" t="n">
-        <v>144.12</v>
+        <v>147.79</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-35.94</v>
+        <v>-36.77</v>
       </c>
       <c r="K54" t="n">
-        <v>136.54</v>
+        <v>139.69</v>
       </c>
       <c r="L54" t="n">
-        <v>141.19</v>
+        <v>144.44</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>-48.23</v>
+        <v>-52.45</v>
       </c>
       <c r="K55" t="n">
-        <v>92.48999999999999</v>
+        <v>100.58</v>
       </c>
       <c r="L55" t="n">
-        <v>104.31</v>
+        <v>113.43</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>27.06</v>
+        <v>27.96</v>
       </c>
       <c r="K56" t="n">
-        <v>233.61</v>
+        <v>241.4</v>
       </c>
       <c r="L56" t="n">
-        <v>235.18</v>
+        <v>243.02</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>180.5</v>
+        <v>193.81</v>
       </c>
       <c r="K57" t="n">
-        <v>-18.05</v>
+        <v>-19.38</v>
       </c>
       <c r="L57" t="n">
-        <v>181.4</v>
+        <v>194.77</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>-47.17</v>
+        <v>-49.03</v>
       </c>
       <c r="K58" t="n">
-        <v>209.63</v>
+        <v>217.92</v>
       </c>
       <c r="L58" t="n">
-        <v>214.87</v>
+        <v>223.37</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>-25.82</v>
+        <v>-25.95</v>
       </c>
       <c r="K59" t="n">
-        <v>59.19</v>
+        <v>59.49</v>
       </c>
       <c r="L59" t="n">
-        <v>64.56999999999999</v>
+        <v>64.91</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>56.66</v>
+        <v>57.19</v>
       </c>
       <c r="K60" t="n">
-        <v>-22.21</v>
+        <v>-22.42</v>
       </c>
       <c r="L60" t="n">
-        <v>60.86</v>
+        <v>61.43</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>48.96</v>
+        <v>48.61</v>
       </c>
       <c r="K61" t="n">
-        <v>-53.68</v>
+        <v>-53.29</v>
       </c>
       <c r="L61" t="n">
-        <v>72.65000000000001</v>
+        <v>72.13</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-2.65</v>
+        <v>-2.57</v>
       </c>
       <c r="K62" t="n">
-        <v>-100.11</v>
+        <v>-97.31</v>
       </c>
       <c r="L62" t="n">
-        <v>100.14</v>
+        <v>97.34999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-57.61</v>
+        <v>-56.96</v>
       </c>
       <c r="K63" t="n">
-        <v>57.38</v>
+        <v>56.73</v>
       </c>
       <c r="L63" t="n">
-        <v>81.31</v>
+        <v>80.39</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>26.26</v>
+        <v>25.48</v>
       </c>
       <c r="K64" t="n">
-        <v>-97.81999999999999</v>
+        <v>-94.92</v>
       </c>
       <c r="L64" t="n">
-        <v>101.28</v>
+        <v>98.28</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>-11.42</v>
+        <v>-11.43</v>
       </c>
       <c r="K65" t="n">
-        <v>-128.25</v>
+        <v>-128.44</v>
       </c>
       <c r="L65" t="n">
-        <v>128.76</v>
+        <v>128.95</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-156.68</v>
+        <v>-151.27</v>
       </c>
       <c r="K66" t="n">
-        <v>-30.46</v>
+        <v>-29.41</v>
       </c>
       <c r="L66" t="n">
-        <v>159.61</v>
+        <v>154.1</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>55.09</v>
+        <v>51.73</v>
       </c>
       <c r="K67" t="n">
-        <v>201.01</v>
+        <v>188.76</v>
       </c>
       <c r="L67" t="n">
-        <v>208.42</v>
+        <v>195.72</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>183.16</v>
+        <v>180.58</v>
       </c>
       <c r="K68" t="n">
-        <v>60.52</v>
+        <v>59.66</v>
       </c>
       <c r="L68" t="n">
-        <v>192.9</v>
+        <v>190.18</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>-121.63</v>
+        <v>-125.63</v>
       </c>
       <c r="K69" t="n">
-        <v>64.26000000000001</v>
+        <v>66.37</v>
       </c>
       <c r="L69" t="n">
-        <v>137.56</v>
+        <v>142.08</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>-36.16</v>
+        <v>-37.27</v>
       </c>
       <c r="K70" t="n">
-        <v>-131.32</v>
+        <v>-135.38</v>
       </c>
       <c r="L70" t="n">
-        <v>136.21</v>
+        <v>140.42</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>-132.22</v>
+        <v>-127.52</v>
       </c>
       <c r="K71" t="n">
-        <v>291.05</v>
+        <v>280.7</v>
       </c>
       <c r="L71" t="n">
-        <v>319.68</v>
+        <v>308.31</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>26.92</v>
+        <v>27.64</v>
       </c>
       <c r="K72" t="n">
-        <v>-165</v>
+        <v>-169.47</v>
       </c>
       <c r="L72" t="n">
-        <v>167.18</v>
+        <v>171.71</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-44.63</v>
+        <v>-43.22</v>
       </c>
       <c r="K73" t="n">
-        <v>-252.6</v>
+        <v>-244.59</v>
       </c>
       <c r="L73" t="n">
-        <v>256.51</v>
+        <v>248.38</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>58.85</v>
+        <v>55.98</v>
       </c>
       <c r="K74" t="n">
-        <v>-71.16</v>
+        <v>-67.7</v>
       </c>
       <c r="L74" t="n">
-        <v>92.34</v>
+        <v>87.84</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-13.14</v>
+        <v>-14.13</v>
       </c>
       <c r="K75" t="n">
-        <v>46.1</v>
+        <v>49.57</v>
       </c>
       <c r="L75" t="n">
-        <v>47.93</v>
+        <v>51.54</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-41.54</v>
+        <v>-42.88</v>
       </c>
       <c r="K76" t="n">
-        <v>-39.96</v>
+        <v>-41.25</v>
       </c>
       <c r="L76" t="n">
-        <v>57.64</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-2.6</v>
+        <v>-2.58</v>
       </c>
       <c r="K77" t="n">
-        <v>-86.13</v>
+        <v>-85.55</v>
       </c>
       <c r="L77" t="n">
-        <v>86.17</v>
+        <v>85.59</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>5.96</v>
+        <v>5.61</v>
       </c>
       <c r="K78" t="n">
-        <v>-122.62</v>
+        <v>-115.49</v>
       </c>
       <c r="L78" t="n">
-        <v>122.76</v>
+        <v>115.63</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>76.28</v>
+        <v>73.89</v>
       </c>
       <c r="K79" t="n">
-        <v>69.05</v>
+        <v>66.89</v>
       </c>
       <c r="L79" t="n">
-        <v>102.89</v>
+        <v>99.67</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>61.26</v>
+        <v>64.83</v>
       </c>
       <c r="K80" t="n">
-        <v>75.01000000000001</v>
+        <v>79.39</v>
       </c>
       <c r="L80" t="n">
-        <v>96.84</v>
+        <v>102.5</v>
       </c>
     </row>
     <row r="81">
@@ -3457,10 +3457,10 @@
         <v>-0.29</v>
       </c>
       <c r="K81" t="n">
-        <v>113.26</v>
+        <v>113.91</v>
       </c>
       <c r="L81" t="n">
-        <v>113.26</v>
+        <v>113.91</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-86.31</v>
+        <v>-90.65000000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>-10.48</v>
+        <v>-11.01</v>
       </c>
       <c r="L82" t="n">
-        <v>86.94</v>
+        <v>91.31999999999999</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>123.73</v>
+        <v>127.67</v>
       </c>
       <c r="K83" t="n">
-        <v>-60.42</v>
+        <v>-62.34</v>
       </c>
       <c r="L83" t="n">
-        <v>137.69</v>
+        <v>142.08</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-185</v>
+        <v>-181.72</v>
       </c>
       <c r="K84" t="n">
-        <v>39.14</v>
+        <v>38.45</v>
       </c>
       <c r="L84" t="n">
-        <v>189.09</v>
+        <v>185.74</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-77.91</v>
+        <v>-80.09999999999999</v>
       </c>
       <c r="K85" t="n">
-        <v>-123.07</v>
+        <v>-126.53</v>
       </c>
       <c r="L85" t="n">
-        <v>145.66</v>
+        <v>149.75</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>230.66</v>
+        <v>224.55</v>
       </c>
       <c r="K86" t="n">
-        <v>124.61</v>
+        <v>121.31</v>
       </c>
       <c r="L86" t="n">
-        <v>262.17</v>
+        <v>255.22</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>6.93</v>
+        <v>6.88</v>
       </c>
       <c r="K87" t="n">
-        <v>-252.99</v>
+        <v>-251.46</v>
       </c>
       <c r="L87" t="n">
-        <v>253.09</v>
+        <v>251.56</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>16.03</v>
+        <v>16.99</v>
       </c>
       <c r="K88" t="n">
-        <v>226.5</v>
+        <v>240.01</v>
       </c>
       <c r="L88" t="n">
-        <v>227.07</v>
+        <v>240.61</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-11.xlsx
+++ b/output/2025-07-11.xlsx
@@ -628,25 +628,25 @@
         <v>3.51</v>
       </c>
       <c r="F14" t="n">
-        <v>11.73</v>
+        <v>9.48</v>
       </c>
       <c r="G14" t="n">
-        <v>113.9</v>
+        <v>139.5</v>
       </c>
       <c r="H14" t="n">
-        <v>10.7</v>
+        <v>3.9</v>
       </c>
       <c r="I14" t="n">
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.37</v>
+        <v>-2.11</v>
       </c>
       <c r="K14" t="n">
-        <v>-58.08</v>
+        <v>-66.77</v>
       </c>
       <c r="L14" t="n">
-        <v>58.13</v>
+        <v>66.81</v>
       </c>
     </row>
     <row r="15">
@@ -670,25 +670,25 @@
         <v>3.66</v>
       </c>
       <c r="F15" t="n">
-        <v>10.96</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>125.5</v>
+        <v>124.2</v>
       </c>
       <c r="H15" t="n">
-        <v>11.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I15" t="n">
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-53.59</v>
+        <v>-54.71</v>
       </c>
       <c r="K15" t="n">
-        <v>84.45999999999999</v>
+        <v>86.83</v>
       </c>
       <c r="L15" t="n">
-        <v>100.03</v>
+        <v>102.63</v>
       </c>
     </row>
     <row r="16">
@@ -712,25 +712,25 @@
         <v>3.97</v>
       </c>
       <c r="F16" t="n">
-        <v>10.86</v>
+        <v>12</v>
       </c>
       <c r="G16" t="n">
-        <v>127.4</v>
+        <v>122.2</v>
       </c>
       <c r="H16" t="n">
-        <v>13.9</v>
+        <v>10.6</v>
       </c>
       <c r="I16" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J16" t="n">
-        <v>-46.61</v>
+        <v>-55.92</v>
       </c>
       <c r="K16" t="n">
-        <v>83.7</v>
+        <v>101.68</v>
       </c>
       <c r="L16" t="n">
-        <v>95.8</v>
+        <v>116.04</v>
       </c>
     </row>
     <row r="17">
@@ -754,25 +754,25 @@
         <v>3.97</v>
       </c>
       <c r="F17" t="n">
-        <v>11.28</v>
+        <v>7.56</v>
       </c>
       <c r="G17" t="n">
-        <v>122.8</v>
+        <v>130.6</v>
       </c>
       <c r="H17" t="n">
-        <v>11.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>-36.46</v>
+        <v>-33.27</v>
       </c>
       <c r="K17" t="n">
-        <v>69.73999999999999</v>
+        <v>65.84</v>
       </c>
       <c r="L17" t="n">
-        <v>78.69</v>
+        <v>73.77</v>
       </c>
     </row>
     <row r="18">
@@ -796,25 +796,25 @@
         <v>4.25</v>
       </c>
       <c r="F18" t="n">
-        <v>10.5</v>
+        <v>9.24</v>
       </c>
       <c r="G18" t="n">
-        <v>133.2</v>
+        <v>114.9</v>
       </c>
       <c r="H18" t="n">
-        <v>5.4</v>
+        <v>13.5</v>
       </c>
       <c r="I18" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>16.43</v>
+        <v>18.72</v>
       </c>
       <c r="K18" t="n">
-        <v>110.74</v>
+        <v>105.49</v>
       </c>
       <c r="L18" t="n">
-        <v>111.95</v>
+        <v>107.14</v>
       </c>
     </row>
     <row r="19">
@@ -838,25 +838,25 @@
         <v>3.28</v>
       </c>
       <c r="F19" t="n">
-        <v>11.32</v>
+        <v>8.6</v>
       </c>
       <c r="G19" t="n">
-        <v>110.9</v>
+        <v>131.4</v>
       </c>
       <c r="H19" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="I19" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>54.64</v>
+        <v>58.86</v>
       </c>
       <c r="K19" t="n">
-        <v>-21.08</v>
+        <v>-26.92</v>
       </c>
       <c r="L19" t="n">
-        <v>58.57</v>
+        <v>64.73</v>
       </c>
     </row>
     <row r="20">
@@ -880,25 +880,25 @@
         <v>4.12</v>
       </c>
       <c r="F20" t="n">
-        <v>10.12</v>
+        <v>8.82</v>
       </c>
       <c r="G20" t="n">
-        <v>138.3</v>
+        <v>107.4</v>
       </c>
       <c r="H20" t="n">
-        <v>5.1</v>
+        <v>16.1</v>
       </c>
       <c r="I20" t="n">
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.01</v>
+        <v>54.64</v>
       </c>
       <c r="K20" t="n">
-        <v>-47.47</v>
+        <v>-62.51</v>
       </c>
       <c r="L20" t="n">
-        <v>47.51</v>
+        <v>83.02</v>
       </c>
     </row>
     <row r="21">
@@ -922,25 +922,25 @@
         <v>3.05</v>
       </c>
       <c r="F21" t="n">
-        <v>10.63</v>
+        <v>9.44</v>
       </c>
       <c r="G21" t="n">
-        <v>121.7</v>
+        <v>117.6</v>
       </c>
       <c r="H21" t="n">
-        <v>14.9</v>
+        <v>7.7</v>
       </c>
       <c r="I21" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>-63.26</v>
+        <v>-68.09999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>-119.95</v>
+        <v>-148.3</v>
       </c>
       <c r="L21" t="n">
-        <v>135.61</v>
+        <v>163.19</v>
       </c>
     </row>
     <row r="22">
@@ -964,25 +964,25 @@
         <v>3.94</v>
       </c>
       <c r="F22" t="n">
-        <v>11.05</v>
+        <v>5.52</v>
       </c>
       <c r="G22" t="n">
-        <v>105.6</v>
+        <v>126.1</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-81.73999999999999</v>
+        <v>-77.54000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-12.57</v>
+        <v>-48.44</v>
       </c>
       <c r="L22" t="n">
-        <v>82.7</v>
+        <v>91.43000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1006,25 +1006,25 @@
         <v>4.29</v>
       </c>
       <c r="F23" t="n">
-        <v>10.25</v>
+        <v>11.07</v>
       </c>
       <c r="G23" t="n">
-        <v>118.9</v>
+        <v>110.1</v>
       </c>
       <c r="H23" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="I23" t="n">
         <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>147.78</v>
+        <v>180.13</v>
       </c>
       <c r="K23" t="n">
-        <v>-63.11</v>
+        <v>-70.77</v>
       </c>
       <c r="L23" t="n">
-        <v>160.69</v>
+        <v>193.53</v>
       </c>
     </row>
     <row r="24">
@@ -1048,25 +1048,25 @@
         <v>3.5</v>
       </c>
       <c r="F24" t="n">
-        <v>11.9</v>
+        <v>10.76</v>
       </c>
       <c r="G24" t="n">
-        <v>138.9</v>
+        <v>143.1</v>
       </c>
       <c r="H24" t="n">
-        <v>13.5</v>
+        <v>16.3</v>
       </c>
       <c r="I24" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-142.5</v>
+        <v>-131.57</v>
       </c>
       <c r="K24" t="n">
-        <v>-82.2</v>
+        <v>-114.01</v>
       </c>
       <c r="L24" t="n">
-        <v>164.5</v>
+        <v>174.09</v>
       </c>
     </row>
     <row r="25">
@@ -1090,25 +1090,25 @@
         <v>3.83</v>
       </c>
       <c r="F25" t="n">
-        <v>10.94</v>
+        <v>8.19</v>
       </c>
       <c r="G25" t="n">
-        <v>118.7</v>
+        <v>123.8</v>
       </c>
       <c r="H25" t="n">
-        <v>10.4</v>
+        <v>6.2</v>
       </c>
       <c r="I25" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>53.01</v>
+        <v>73.09</v>
       </c>
       <c r="K25" t="n">
-        <v>206.1</v>
+        <v>185.58</v>
       </c>
       <c r="L25" t="n">
-        <v>212.8</v>
+        <v>199.45</v>
       </c>
     </row>
     <row r="26">
@@ -1132,25 +1132,25 @@
         <v>3.82</v>
       </c>
       <c r="F26" t="n">
-        <v>10.65</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>123.5</v>
+        <v>118</v>
       </c>
       <c r="H26" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="I26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>-291.13</v>
+        <v>-297.55</v>
       </c>
       <c r="K26" t="n">
-        <v>-40.68</v>
+        <v>-57.68</v>
       </c>
       <c r="L26" t="n">
-        <v>293.96</v>
+        <v>303.09</v>
       </c>
     </row>
     <row r="27">
@@ -1174,25 +1174,25 @@
         <v>3.61</v>
       </c>
       <c r="F27" t="n">
-        <v>10.79</v>
+        <v>8.77</v>
       </c>
       <c r="G27" t="n">
-        <v>134.5</v>
+        <v>120.7</v>
       </c>
       <c r="H27" t="n">
-        <v>13.9</v>
+        <v>14.2</v>
       </c>
       <c r="I27" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>-231.37</v>
+        <v>-237.7</v>
       </c>
       <c r="K27" t="n">
-        <v>-70.95999999999999</v>
+        <v>-103.02</v>
       </c>
       <c r="L27" t="n">
-        <v>242.01</v>
+        <v>259.07</v>
       </c>
     </row>
     <row r="28">
@@ -1216,25 +1216,25 @@
         <v>3.74</v>
       </c>
       <c r="F28" t="n">
-        <v>10.64</v>
+        <v>11.72</v>
       </c>
       <c r="G28" t="n">
-        <v>126.7</v>
+        <v>117.7</v>
       </c>
       <c r="H28" t="n">
-        <v>14.2</v>
+        <v>10.2</v>
       </c>
       <c r="I28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-84.08</v>
+        <v>9.49</v>
       </c>
       <c r="K28" t="n">
-        <v>147.7</v>
+        <v>179.68</v>
       </c>
       <c r="L28" t="n">
-        <v>169.96</v>
+        <v>179.93</v>
       </c>
     </row>
     <row r="29">
@@ -1258,25 +1258,25 @@
         <v>3.65</v>
       </c>
       <c r="F29" t="n">
-        <v>11.23</v>
+        <v>8.56</v>
       </c>
       <c r="G29" t="n">
-        <v>124.3</v>
+        <v>129.6</v>
       </c>
       <c r="H29" t="n">
-        <v>13.1</v>
+        <v>9.1</v>
       </c>
       <c r="I29" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>-89.51000000000001</v>
+        <v>-90.55</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.64</v>
+        <v>-4.39</v>
       </c>
       <c r="L29" t="n">
-        <v>89.58</v>
+        <v>90.66</v>
       </c>
     </row>
     <row r="30">
@@ -1300,25 +1300,25 @@
         <v>3.39</v>
       </c>
       <c r="F30" t="n">
-        <v>10.79</v>
+        <v>10.04</v>
       </c>
       <c r="G30" t="n">
-        <v>121.2</v>
+        <v>120.8</v>
       </c>
       <c r="H30" t="n">
-        <v>12.2</v>
+        <v>7.5</v>
       </c>
       <c r="I30" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>-62.22</v>
+        <v>-78.87</v>
       </c>
       <c r="K30" t="n">
-        <v>15.92</v>
+        <v>19.84</v>
       </c>
       <c r="L30" t="n">
-        <v>64.23</v>
+        <v>81.33</v>
       </c>
     </row>
     <row r="31">
@@ -1342,25 +1342,25 @@
         <v>3.42</v>
       </c>
       <c r="F31" t="n">
-        <v>10.88</v>
+        <v>6.8</v>
       </c>
       <c r="G31" t="n">
-        <v>119</v>
+        <v>122.6</v>
       </c>
       <c r="H31" t="n">
-        <v>7.1</v>
+        <v>6.4</v>
       </c>
       <c r="I31" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>50.13</v>
+        <v>59.75</v>
       </c>
       <c r="K31" t="n">
-        <v>-28.41</v>
+        <v>-34.06</v>
       </c>
       <c r="L31" t="n">
-        <v>57.62</v>
+        <v>68.77</v>
       </c>
     </row>
     <row r="32">
@@ -1384,25 +1384,25 @@
         <v>3.55</v>
       </c>
       <c r="F32" t="n">
-        <v>10.76</v>
+        <v>7.43</v>
       </c>
       <c r="G32" t="n">
-        <v>125.2</v>
+        <v>120.2</v>
       </c>
       <c r="H32" t="n">
-        <v>4.7</v>
+        <v>9.5</v>
       </c>
       <c r="I32" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>60.66</v>
+        <v>62.99</v>
       </c>
       <c r="K32" t="n">
-        <v>-49.86</v>
+        <v>-50.77</v>
       </c>
       <c r="L32" t="n">
-        <v>78.52</v>
+        <v>80.91</v>
       </c>
     </row>
     <row r="33">
@@ -1426,25 +1426,25 @@
         <v>4.07</v>
       </c>
       <c r="F33" t="n">
-        <v>10.56</v>
+        <v>11.73</v>
       </c>
       <c r="G33" t="n">
-        <v>134.3</v>
+        <v>116.1</v>
       </c>
       <c r="H33" t="n">
-        <v>9.1</v>
+        <v>14</v>
       </c>
       <c r="I33" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>-33.55</v>
+        <v>-35.98</v>
       </c>
       <c r="K33" t="n">
-        <v>99.78</v>
+        <v>115.47</v>
       </c>
       <c r="L33" t="n">
-        <v>105.27</v>
+        <v>120.94</v>
       </c>
     </row>
     <row r="34">
@@ -1468,25 +1468,25 @@
         <v>3.48</v>
       </c>
       <c r="F34" t="n">
-        <v>10.57</v>
+        <v>6.6</v>
       </c>
       <c r="G34" t="n">
-        <v>123.3</v>
+        <v>116.4</v>
       </c>
       <c r="H34" t="n">
-        <v>3.2</v>
+        <v>8.5</v>
       </c>
       <c r="I34" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>64.27</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>-64.77</v>
+        <v>-70.44</v>
       </c>
       <c r="L34" t="n">
-        <v>91.23999999999999</v>
+        <v>100.3</v>
       </c>
     </row>
     <row r="35">
@@ -1510,25 +1510,25 @@
         <v>3.49</v>
       </c>
       <c r="F35" t="n">
-        <v>10.69</v>
+        <v>11.12</v>
       </c>
       <c r="G35" t="n">
-        <v>135.2</v>
+        <v>118.7</v>
       </c>
       <c r="H35" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="I35" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-71.22</v>
+        <v>-69.98999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>-79.09</v>
+        <v>-98.98</v>
       </c>
       <c r="L35" t="n">
-        <v>106.43</v>
+        <v>121.23</v>
       </c>
     </row>
     <row r="36">
@@ -1552,25 +1552,25 @@
         <v>3.51</v>
       </c>
       <c r="F36" t="n">
-        <v>11.09</v>
+        <v>9.15</v>
       </c>
       <c r="G36" t="n">
-        <v>118.3</v>
+        <v>126.9</v>
       </c>
       <c r="H36" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I36" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>27.74</v>
+        <v>40.46</v>
       </c>
       <c r="K36" t="n">
-        <v>-103.1</v>
+        <v>-123.08</v>
       </c>
       <c r="L36" t="n">
-        <v>106.77</v>
+        <v>129.56</v>
       </c>
     </row>
     <row r="37">
@@ -1594,25 +1594,25 @@
         <v>3.53</v>
       </c>
       <c r="F37" t="n">
-        <v>10.71</v>
+        <v>10.93</v>
       </c>
       <c r="G37" t="n">
-        <v>123.7</v>
+        <v>119.3</v>
       </c>
       <c r="H37" t="n">
-        <v>11.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I37" t="n">
         <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>143.47</v>
+        <v>166.97</v>
       </c>
       <c r="K37" t="n">
-        <v>-5.86</v>
+        <v>-11.3</v>
       </c>
       <c r="L37" t="n">
-        <v>143.59</v>
+        <v>167.35</v>
       </c>
     </row>
     <row r="38">
@@ -1636,25 +1636,25 @@
         <v>3.22</v>
       </c>
       <c r="F38" t="n">
-        <v>10.66</v>
+        <v>9.49</v>
       </c>
       <c r="G38" t="n">
-        <v>121.5</v>
+        <v>118.1</v>
       </c>
       <c r="H38" t="n">
-        <v>11.6</v>
+        <v>7.6</v>
       </c>
       <c r="I38" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>20.7</v>
+        <v>43.93</v>
       </c>
       <c r="K38" t="n">
-        <v>-171.15</v>
+        <v>-191.66</v>
       </c>
       <c r="L38" t="n">
-        <v>172.39</v>
+        <v>196.63</v>
       </c>
     </row>
     <row r="39">
@@ -1678,25 +1678,25 @@
         <v>3.78</v>
       </c>
       <c r="F39" t="n">
-        <v>10.47</v>
+        <v>9.33</v>
       </c>
       <c r="G39" t="n">
-        <v>133.1</v>
+        <v>114.3</v>
       </c>
       <c r="H39" t="n">
-        <v>5.2</v>
+        <v>13.5</v>
       </c>
       <c r="I39" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>131.86</v>
+        <v>159.46</v>
       </c>
       <c r="K39" t="n">
-        <v>10.19</v>
+        <v>-0.4</v>
       </c>
       <c r="L39" t="n">
-        <v>132.26</v>
+        <v>159.46</v>
       </c>
     </row>
     <row r="40">
@@ -1720,25 +1720,25 @@
         <v>4.23</v>
       </c>
       <c r="F40" t="n">
-        <v>12.32</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="G40" t="n">
-        <v>121.3</v>
+        <v>151.3</v>
       </c>
       <c r="H40" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="I40" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>125.17</v>
+        <v>149.08</v>
       </c>
       <c r="K40" t="n">
-        <v>86.45</v>
+        <v>50.84</v>
       </c>
       <c r="L40" t="n">
-        <v>152.12</v>
+        <v>157.51</v>
       </c>
     </row>
     <row r="41">
@@ -1762,25 +1762,25 @@
         <v>3.84</v>
       </c>
       <c r="F41" t="n">
-        <v>11.41</v>
+        <v>7.18</v>
       </c>
       <c r="G41" t="n">
-        <v>128.4</v>
+        <v>133.1</v>
       </c>
       <c r="H41" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="I41" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>-158.6</v>
+        <v>-138.27</v>
       </c>
       <c r="K41" t="n">
-        <v>-192.97</v>
+        <v>-226.16</v>
       </c>
       <c r="L41" t="n">
-        <v>249.78</v>
+        <v>265.08</v>
       </c>
     </row>
     <row r="42">
@@ -1804,25 +1804,25 @@
         <v>4</v>
       </c>
       <c r="F42" t="n">
-        <v>11.11</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>140.3</v>
+        <v>127.3</v>
       </c>
       <c r="H42" t="n">
-        <v>5.6</v>
+        <v>17.1</v>
       </c>
       <c r="I42" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-19.48</v>
+        <v>36.05</v>
       </c>
       <c r="K42" t="n">
-        <v>185.45</v>
+        <v>224.34</v>
       </c>
       <c r="L42" t="n">
-        <v>186.47</v>
+        <v>227.21</v>
       </c>
     </row>
     <row r="43">
@@ -1846,25 +1846,25 @@
         <v>3.95</v>
       </c>
       <c r="F43" t="n">
-        <v>11.22</v>
+        <v>8.57</v>
       </c>
       <c r="G43" t="n">
-        <v>119.1</v>
+        <v>129.4</v>
       </c>
       <c r="H43" t="n">
-        <v>3.2</v>
+        <v>6.4</v>
       </c>
       <c r="I43" t="n">
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>225.29</v>
+        <v>245.56</v>
       </c>
       <c r="K43" t="n">
-        <v>-76.31999999999999</v>
+        <v>-100.62</v>
       </c>
       <c r="L43" t="n">
-        <v>237.87</v>
+        <v>265.37</v>
       </c>
     </row>
     <row r="44">
@@ -1888,25 +1888,25 @@
         <v>4.23</v>
       </c>
       <c r="F44" t="n">
-        <v>10.77</v>
+        <v>12.65</v>
       </c>
       <c r="G44" t="n">
-        <v>136</v>
+        <v>120.5</v>
       </c>
       <c r="H44" t="n">
-        <v>14.1</v>
+        <v>14.9</v>
       </c>
       <c r="I44" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>26.39</v>
+        <v>34.42</v>
       </c>
       <c r="K44" t="n">
-        <v>45.07</v>
+        <v>53.51</v>
       </c>
       <c r="L44" t="n">
-        <v>52.23</v>
+        <v>63.63</v>
       </c>
     </row>
     <row r="45">
@@ -1930,25 +1930,25 @@
         <v>4.3</v>
       </c>
       <c r="F45" t="n">
-        <v>10.98</v>
+        <v>12.43</v>
       </c>
       <c r="G45" t="n">
-        <v>114.8</v>
+        <v>124.7</v>
       </c>
       <c r="H45" t="n">
-        <v>12.1</v>
+        <v>4.3</v>
       </c>
       <c r="I45" t="n">
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>0.61</v>
+        <v>1.79</v>
       </c>
       <c r="K45" t="n">
-        <v>63.02</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>63.02</v>
+        <v>71.01000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1972,25 +1972,25 @@
         <v>3.85</v>
       </c>
       <c r="F46" t="n">
-        <v>10.78</v>
+        <v>8.65</v>
       </c>
       <c r="G46" t="n">
-        <v>129.6</v>
+        <v>120.7</v>
       </c>
       <c r="H46" t="n">
-        <v>5.2</v>
+        <v>11.7</v>
       </c>
       <c r="I46" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>-68.59999999999999</v>
+        <v>-71.37</v>
       </c>
       <c r="K46" t="n">
-        <v>21.04</v>
+        <v>21.84</v>
       </c>
       <c r="L46" t="n">
-        <v>71.76000000000001</v>
+        <v>74.64</v>
       </c>
     </row>
     <row r="47">
@@ -2014,25 +2014,25 @@
         <v>4.02</v>
       </c>
       <c r="F47" t="n">
-        <v>10.09</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>137.1</v>
+        <v>106.8</v>
       </c>
       <c r="H47" t="n">
-        <v>12.5</v>
+        <v>15.4</v>
       </c>
       <c r="I47" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>-93.41</v>
+        <v>-101.78</v>
       </c>
       <c r="K47" t="n">
-        <v>-47.24</v>
+        <v>-52.92</v>
       </c>
       <c r="L47" t="n">
-        <v>104.67</v>
+        <v>114.72</v>
       </c>
     </row>
     <row r="48">
@@ -2056,25 +2056,25 @@
         <v>3.6</v>
       </c>
       <c r="F48" t="n">
-        <v>11.11</v>
+        <v>10.37</v>
       </c>
       <c r="G48" t="n">
-        <v>132.2</v>
+        <v>127.1</v>
       </c>
       <c r="H48" t="n">
-        <v>10.9</v>
+        <v>13</v>
       </c>
       <c r="I48" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-57.58</v>
+        <v>-71.64</v>
       </c>
       <c r="K48" t="n">
-        <v>56.55</v>
+        <v>71.33</v>
       </c>
       <c r="L48" t="n">
-        <v>80.70999999999999</v>
+        <v>101.09</v>
       </c>
     </row>
     <row r="49">
@@ -2098,25 +2098,25 @@
         <v>2.72</v>
       </c>
       <c r="F49" t="n">
-        <v>10.28</v>
+        <v>9.59</v>
       </c>
       <c r="G49" t="n">
-        <v>142.8</v>
+        <v>110.6</v>
       </c>
       <c r="H49" t="n">
-        <v>12.4</v>
+        <v>18.3</v>
       </c>
       <c r="I49" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>26.76</v>
+        <v>42.64</v>
       </c>
       <c r="K49" t="n">
-        <v>37.46</v>
+        <v>47.24</v>
       </c>
       <c r="L49" t="n">
-        <v>46.03</v>
+        <v>63.63</v>
       </c>
     </row>
     <row r="50">
@@ -2140,25 +2140,25 @@
         <v>4.41</v>
       </c>
       <c r="F50" t="n">
-        <v>10.47</v>
+        <v>10.82</v>
       </c>
       <c r="G50" t="n">
-        <v>124.5</v>
+        <v>114.5</v>
       </c>
       <c r="H50" t="n">
-        <v>6.6</v>
+        <v>9.1</v>
       </c>
       <c r="I50" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>102.97</v>
+        <v>122.34</v>
       </c>
       <c r="K50" t="n">
-        <v>90.13</v>
+        <v>87.95</v>
       </c>
       <c r="L50" t="n">
-        <v>136.84</v>
+        <v>150.67</v>
       </c>
     </row>
     <row r="51">
@@ -2182,25 +2182,25 @@
         <v>4.17</v>
       </c>
       <c r="F51" t="n">
-        <v>11.43</v>
+        <v>12.65</v>
       </c>
       <c r="G51" t="n">
-        <v>127.7</v>
+        <v>133.7</v>
       </c>
       <c r="H51" t="n">
-        <v>6.8</v>
+        <v>10.8</v>
       </c>
       <c r="I51" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-46.31</v>
+        <v>-39.66</v>
       </c>
       <c r="K51" t="n">
-        <v>-129.99</v>
+        <v>-150.76</v>
       </c>
       <c r="L51" t="n">
-        <v>137.99</v>
+        <v>155.89</v>
       </c>
     </row>
     <row r="52">
@@ -2224,25 +2224,25 @@
         <v>3.42</v>
       </c>
       <c r="F52" t="n">
-        <v>10.79</v>
+        <v>6.34</v>
       </c>
       <c r="G52" t="n">
-        <v>116.6</v>
+        <v>120.8</v>
       </c>
       <c r="H52" t="n">
-        <v>2.3</v>
+        <v>5.2</v>
       </c>
       <c r="I52" t="n">
         <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>-29.32</v>
+        <v>-20.98</v>
       </c>
       <c r="K52" t="n">
-        <v>-125.8</v>
+        <v>-132.75</v>
       </c>
       <c r="L52" t="n">
-        <v>129.17</v>
+        <v>134.4</v>
       </c>
     </row>
     <row r="53">
@@ -2266,25 +2266,25 @@
         <v>3.98</v>
       </c>
       <c r="F53" t="n">
-        <v>10.44</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="G53" t="n">
-        <v>133.5</v>
+        <v>113.7</v>
       </c>
       <c r="H53" t="n">
-        <v>7</v>
+        <v>13.7</v>
       </c>
       <c r="I53" t="n">
         <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>92.45</v>
+        <v>129.69</v>
       </c>
       <c r="K53" t="n">
-        <v>-115.3</v>
+        <v>-120.61</v>
       </c>
       <c r="L53" t="n">
-        <v>147.79</v>
+        <v>177.11</v>
       </c>
     </row>
     <row r="54">
@@ -2308,25 +2308,25 @@
         <v>4.47</v>
       </c>
       <c r="F54" t="n">
-        <v>10.33</v>
+        <v>12.03</v>
       </c>
       <c r="G54" t="n">
-        <v>131.3</v>
+        <v>111.6</v>
       </c>
       <c r="H54" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="I54" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-36.77</v>
+        <v>1.17</v>
       </c>
       <c r="K54" t="n">
-        <v>139.69</v>
+        <v>164.12</v>
       </c>
       <c r="L54" t="n">
-        <v>144.44</v>
+        <v>164.13</v>
       </c>
     </row>
     <row r="55">
@@ -2350,25 +2350,25 @@
         <v>3.71</v>
       </c>
       <c r="F55" t="n">
-        <v>11.1</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>123</v>
+        <v>127.1</v>
       </c>
       <c r="H55" t="n">
-        <v>11.1</v>
+        <v>8.4</v>
       </c>
       <c r="I55" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-52.45</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="K55" t="n">
-        <v>100.58</v>
+        <v>63.11</v>
       </c>
       <c r="L55" t="n">
-        <v>113.43</v>
+        <v>63.66</v>
       </c>
     </row>
     <row r="56">
@@ -2392,25 +2392,25 @@
         <v>4.76</v>
       </c>
       <c r="F56" t="n">
-        <v>10.52</v>
+        <v>9.01</v>
       </c>
       <c r="G56" t="n">
-        <v>119.7</v>
+        <v>115.4</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="I56" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J56" t="n">
-        <v>27.96</v>
+        <v>81.09</v>
       </c>
       <c r="K56" t="n">
-        <v>241.4</v>
+        <v>270.37</v>
       </c>
       <c r="L56" t="n">
-        <v>243.02</v>
+        <v>282.26</v>
       </c>
     </row>
     <row r="57">
@@ -2434,25 +2434,25 @@
         <v>4.18</v>
       </c>
       <c r="F57" t="n">
-        <v>10.42</v>
+        <v>9.44</v>
       </c>
       <c r="G57" t="n">
-        <v>135.9</v>
+        <v>113.4</v>
       </c>
       <c r="H57" t="n">
-        <v>11.4</v>
+        <v>14.9</v>
       </c>
       <c r="I57" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>193.81</v>
+        <v>232.65</v>
       </c>
       <c r="K57" t="n">
-        <v>-19.38</v>
+        <v>-19.62</v>
       </c>
       <c r="L57" t="n">
-        <v>194.77</v>
+        <v>233.48</v>
       </c>
     </row>
     <row r="58">
@@ -2476,25 +2476,25 @@
         <v>4.47</v>
       </c>
       <c r="F58" t="n">
-        <v>11.31</v>
+        <v>12.65</v>
       </c>
       <c r="G58" t="n">
-        <v>131.5</v>
+        <v>131.1</v>
       </c>
       <c r="H58" t="n">
-        <v>11</v>
+        <v>12.7</v>
       </c>
       <c r="I58" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J58" t="n">
-        <v>-49.03</v>
+        <v>-19.46</v>
       </c>
       <c r="K58" t="n">
-        <v>217.92</v>
+        <v>265.1</v>
       </c>
       <c r="L58" t="n">
-        <v>223.37</v>
+        <v>265.82</v>
       </c>
     </row>
     <row r="59">
@@ -2518,25 +2518,25 @@
         <v>3.73</v>
       </c>
       <c r="F59" t="n">
-        <v>10.63</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G59" t="n">
-        <v>134.9</v>
+        <v>117.5</v>
       </c>
       <c r="H59" t="n">
-        <v>12.3</v>
+        <v>14.3</v>
       </c>
       <c r="I59" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-25.95</v>
+        <v>-27.37</v>
       </c>
       <c r="K59" t="n">
-        <v>59.49</v>
+        <v>65.89</v>
       </c>
       <c r="L59" t="n">
-        <v>64.91</v>
+        <v>71.34999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2560,25 +2560,25 @@
         <v>4.5</v>
       </c>
       <c r="F60" t="n">
-        <v>11.02</v>
+        <v>7.32</v>
       </c>
       <c r="G60" t="n">
-        <v>134.2</v>
+        <v>125.4</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I60" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>57.19</v>
+        <v>62.47</v>
       </c>
       <c r="K60" t="n">
-        <v>-22.42</v>
+        <v>-24.57</v>
       </c>
       <c r="L60" t="n">
-        <v>61.43</v>
+        <v>67.13</v>
       </c>
     </row>
     <row r="61">
@@ -2602,25 +2602,25 @@
         <v>3.79</v>
       </c>
       <c r="F61" t="n">
-        <v>11.16</v>
+        <v>11.29</v>
       </c>
       <c r="G61" t="n">
-        <v>138.1</v>
+        <v>128.2</v>
       </c>
       <c r="H61" t="n">
-        <v>12.9</v>
+        <v>15.9</v>
       </c>
       <c r="I61" t="n">
         <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>48.61</v>
+        <v>56.54</v>
       </c>
       <c r="K61" t="n">
-        <v>-53.29</v>
+        <v>-61.24</v>
       </c>
       <c r="L61" t="n">
-        <v>72.13</v>
+        <v>83.34999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2644,25 +2644,25 @@
         <v>4.52</v>
       </c>
       <c r="F62" t="n">
-        <v>11.25</v>
+        <v>12.16</v>
       </c>
       <c r="G62" t="n">
-        <v>117.3</v>
+        <v>130</v>
       </c>
       <c r="H62" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="I62" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-2.57</v>
+        <v>-0.47</v>
       </c>
       <c r="K62" t="n">
-        <v>-97.31</v>
+        <v>-106.03</v>
       </c>
       <c r="L62" t="n">
-        <v>97.34999999999999</v>
+        <v>106.03</v>
       </c>
     </row>
     <row r="63">
@@ -2686,25 +2686,25 @@
         <v>3.88</v>
       </c>
       <c r="F63" t="n">
-        <v>10.83</v>
+        <v>11.46</v>
       </c>
       <c r="G63" t="n">
-        <v>103.8</v>
+        <v>121.7</v>
       </c>
       <c r="H63" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-56.96</v>
+        <v>-63.21</v>
       </c>
       <c r="K63" t="n">
-        <v>56.73</v>
+        <v>62.73</v>
       </c>
       <c r="L63" t="n">
-        <v>80.39</v>
+        <v>89.05</v>
       </c>
     </row>
     <row r="64">
@@ -2728,25 +2728,25 @@
         <v>3.44</v>
       </c>
       <c r="F64" t="n">
-        <v>10.61</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="G64" t="n">
-        <v>119.4</v>
+        <v>117.2</v>
       </c>
       <c r="H64" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="I64" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>25.48</v>
+        <v>28.05</v>
       </c>
       <c r="K64" t="n">
-        <v>-94.92</v>
+        <v>-97.37</v>
       </c>
       <c r="L64" t="n">
-        <v>98.28</v>
+        <v>101.33</v>
       </c>
     </row>
     <row r="65">
@@ -2770,25 +2770,25 @@
         <v>4.45</v>
       </c>
       <c r="F65" t="n">
-        <v>10.49</v>
+        <v>12.65</v>
       </c>
       <c r="G65" t="n">
-        <v>121.3</v>
+        <v>114.8</v>
       </c>
       <c r="H65" t="n">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="I65" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-11.43</v>
+        <v>5.73</v>
       </c>
       <c r="K65" t="n">
-        <v>-128.44</v>
+        <v>-152.18</v>
       </c>
       <c r="L65" t="n">
-        <v>128.95</v>
+        <v>152.29</v>
       </c>
     </row>
     <row r="66">
@@ -2812,25 +2812,25 @@
         <v>4.16</v>
       </c>
       <c r="F66" t="n">
-        <v>11.47</v>
+        <v>12.65</v>
       </c>
       <c r="G66" t="n">
-        <v>132.4</v>
+        <v>134.4</v>
       </c>
       <c r="H66" t="n">
-        <v>20.2</v>
+        <v>13.1</v>
       </c>
       <c r="I66" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-151.27</v>
+        <v>-156.89</v>
       </c>
       <c r="K66" t="n">
-        <v>-29.41</v>
+        <v>-42.07</v>
       </c>
       <c r="L66" t="n">
-        <v>154.1</v>
+        <v>162.43</v>
       </c>
     </row>
     <row r="67">
@@ -2854,25 +2854,25 @@
         <v>4.69</v>
       </c>
       <c r="F67" t="n">
-        <v>10.92</v>
+        <v>11.94</v>
       </c>
       <c r="G67" t="n">
-        <v>129.4</v>
+        <v>123.4</v>
       </c>
       <c r="H67" t="n">
-        <v>7.1</v>
+        <v>11.6</v>
       </c>
       <c r="I67" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>51.73</v>
+        <v>69.81</v>
       </c>
       <c r="K67" t="n">
-        <v>188.76</v>
+        <v>203.77</v>
       </c>
       <c r="L67" t="n">
-        <v>195.72</v>
+        <v>215.4</v>
       </c>
     </row>
     <row r="68">
@@ -2896,25 +2896,25 @@
         <v>4.53</v>
       </c>
       <c r="F68" t="n">
-        <v>10.62</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="G68" t="n">
-        <v>133.6</v>
+        <v>117.4</v>
       </c>
       <c r="H68" t="n">
-        <v>2</v>
+        <v>13.7</v>
       </c>
       <c r="I68" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>180.58</v>
+        <v>200.87</v>
       </c>
       <c r="K68" t="n">
-        <v>59.66</v>
+        <v>49.24</v>
       </c>
       <c r="L68" t="n">
-        <v>190.18</v>
+        <v>206.82</v>
       </c>
     </row>
     <row r="69">
@@ -2938,25 +2938,25 @@
         <v>3.81</v>
       </c>
       <c r="F69" t="n">
-        <v>11.57</v>
+        <v>9.99</v>
       </c>
       <c r="G69" t="n">
-        <v>128.2</v>
+        <v>136.4</v>
       </c>
       <c r="H69" t="n">
-        <v>12.4</v>
+        <v>11</v>
       </c>
       <c r="I69" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-125.63</v>
+        <v>-133.26</v>
       </c>
       <c r="K69" t="n">
-        <v>66.37</v>
+        <v>43.74</v>
       </c>
       <c r="L69" t="n">
-        <v>142.08</v>
+        <v>140.25</v>
       </c>
     </row>
     <row r="70">
@@ -2980,25 +2980,25 @@
         <v>4.24</v>
       </c>
       <c r="F70" t="n">
-        <v>10.77</v>
+        <v>12.65</v>
       </c>
       <c r="G70" t="n">
-        <v>128.9</v>
+        <v>120.4</v>
       </c>
       <c r="H70" t="n">
-        <v>13.2</v>
+        <v>11.4</v>
       </c>
       <c r="I70" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-37.27</v>
+        <v>-0.79</v>
       </c>
       <c r="K70" t="n">
-        <v>-135.38</v>
+        <v>-174.22</v>
       </c>
       <c r="L70" t="n">
-        <v>140.42</v>
+        <v>174.23</v>
       </c>
     </row>
     <row r="71">
@@ -3022,25 +3022,25 @@
         <v>4.06</v>
       </c>
       <c r="F71" t="n">
-        <v>11.38</v>
+        <v>12.17</v>
       </c>
       <c r="G71" t="n">
-        <v>125.4</v>
+        <v>132.6</v>
       </c>
       <c r="H71" t="n">
-        <v>15</v>
+        <v>9.6</v>
       </c>
       <c r="I71" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-127.52</v>
+        <v>-123.92</v>
       </c>
       <c r="K71" t="n">
-        <v>280.7</v>
+        <v>295.69</v>
       </c>
       <c r="L71" t="n">
-        <v>308.31</v>
+        <v>320.61</v>
       </c>
     </row>
     <row r="72">
@@ -3064,25 +3064,25 @@
         <v>3.24</v>
       </c>
       <c r="F72" t="n">
-        <v>11.09</v>
+        <v>7.82</v>
       </c>
       <c r="G72" t="n">
-        <v>137.7</v>
+        <v>126.7</v>
       </c>
       <c r="H72" t="n">
-        <v>6.3</v>
+        <v>15.7</v>
       </c>
       <c r="I72" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>27.64</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="K72" t="n">
-        <v>-169.47</v>
+        <v>-199.61</v>
       </c>
       <c r="L72" t="n">
-        <v>171.71</v>
+        <v>211.93</v>
       </c>
     </row>
     <row r="73">
@@ -3106,25 +3106,25 @@
         <v>3.5</v>
       </c>
       <c r="F73" t="n">
-        <v>11.42</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="G73" t="n">
-        <v>134.8</v>
+        <v>133.4</v>
       </c>
       <c r="H73" t="n">
-        <v>7.7</v>
+        <v>14.3</v>
       </c>
       <c r="I73" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J73" t="n">
-        <v>-43.22</v>
+        <v>-24.35</v>
       </c>
       <c r="K73" t="n">
-        <v>-244.59</v>
+        <v>-302.71</v>
       </c>
       <c r="L73" t="n">
-        <v>248.38</v>
+        <v>303.68</v>
       </c>
     </row>
     <row r="74">
@@ -3151,22 +3151,22 @@
         <v>11.07</v>
       </c>
       <c r="G74" t="n">
-        <v>127.9</v>
+        <v>126.5</v>
       </c>
       <c r="H74" t="n">
-        <v>12.9</v>
+        <v>10.8</v>
       </c>
       <c r="I74" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>55.98</v>
+        <v>66.45</v>
       </c>
       <c r="K74" t="n">
-        <v>-67.7</v>
+        <v>-80.01000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>87.84</v>
+        <v>104.01</v>
       </c>
     </row>
     <row r="75">
@@ -3190,25 +3190,25 @@
         <v>3.97</v>
       </c>
       <c r="F75" t="n">
-        <v>11.22</v>
+        <v>11.21</v>
       </c>
       <c r="G75" t="n">
-        <v>120.8</v>
+        <v>129.3</v>
       </c>
       <c r="H75" t="n">
-        <v>9.4</v>
+        <v>7.3</v>
       </c>
       <c r="I75" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-14.13</v>
+        <v>-14.7</v>
       </c>
       <c r="K75" t="n">
-        <v>49.57</v>
+        <v>56.2</v>
       </c>
       <c r="L75" t="n">
-        <v>51.54</v>
+        <v>58.09</v>
       </c>
     </row>
     <row r="76">
@@ -3232,25 +3232,25 @@
         <v>4.02</v>
       </c>
       <c r="F76" t="n">
-        <v>10.33</v>
+        <v>11.72</v>
       </c>
       <c r="G76" t="n">
-        <v>110.9</v>
+        <v>111.7</v>
       </c>
       <c r="H76" t="n">
-        <v>10.3</v>
+        <v>2.4</v>
       </c>
       <c r="I76" t="n">
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-42.88</v>
+        <v>-48.03</v>
       </c>
       <c r="K76" t="n">
-        <v>-41.25</v>
+        <v>-48.62</v>
       </c>
       <c r="L76" t="n">
-        <v>59.5</v>
+        <v>68.34</v>
       </c>
     </row>
     <row r="77">
@@ -3274,25 +3274,25 @@
         <v>4.35</v>
       </c>
       <c r="F77" t="n">
-        <v>11.48</v>
+        <v>8.33</v>
       </c>
       <c r="G77" t="n">
-        <v>134.7</v>
+        <v>134.6</v>
       </c>
       <c r="H77" t="n">
-        <v>16</v>
+        <v>14.2</v>
       </c>
       <c r="I77" t="n">
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-2.58</v>
+        <v>-0</v>
       </c>
       <c r="K77" t="n">
-        <v>-85.55</v>
+        <v>-89.7</v>
       </c>
       <c r="L77" t="n">
-        <v>85.59</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="78">
@@ -3316,25 +3316,25 @@
         <v>4.14</v>
       </c>
       <c r="F78" t="n">
-        <v>10.9</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>129</v>
+        <v>122.9</v>
       </c>
       <c r="H78" t="n">
-        <v>5.1</v>
+        <v>11.4</v>
       </c>
       <c r="I78" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>5.61</v>
+        <v>8</v>
       </c>
       <c r="K78" t="n">
-        <v>-115.49</v>
+        <v>-120.6</v>
       </c>
       <c r="L78" t="n">
-        <v>115.63</v>
+        <v>120.87</v>
       </c>
     </row>
     <row r="79">
@@ -3358,25 +3358,25 @@
         <v>3.53</v>
       </c>
       <c r="F79" t="n">
-        <v>11.57</v>
+        <v>9.42</v>
       </c>
       <c r="G79" t="n">
-        <v>125.1</v>
+        <v>136.3</v>
       </c>
       <c r="H79" t="n">
-        <v>10.4</v>
+        <v>9.4</v>
       </c>
       <c r="I79" t="n">
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>73.89</v>
+        <v>82.45</v>
       </c>
       <c r="K79" t="n">
-        <v>66.89</v>
+        <v>70.97</v>
       </c>
       <c r="L79" t="n">
-        <v>99.67</v>
+        <v>108.79</v>
       </c>
     </row>
     <row r="80">
@@ -3400,25 +3400,25 @@
         <v>4.18</v>
       </c>
       <c r="F80" t="n">
-        <v>11.23</v>
+        <v>11.28</v>
       </c>
       <c r="G80" t="n">
-        <v>111.5</v>
+        <v>129.6</v>
       </c>
       <c r="H80" t="n">
-        <v>7.9</v>
+        <v>2.7</v>
       </c>
       <c r="I80" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>64.83</v>
+        <v>93.5</v>
       </c>
       <c r="K80" t="n">
-        <v>79.39</v>
+        <v>63.93</v>
       </c>
       <c r="L80" t="n">
-        <v>102.5</v>
+        <v>113.26</v>
       </c>
     </row>
     <row r="81">
@@ -3442,25 +3442,25 @@
         <v>3.97</v>
       </c>
       <c r="F81" t="n">
-        <v>11.42</v>
+        <v>11.32</v>
       </c>
       <c r="G81" t="n">
-        <v>122.8</v>
+        <v>133.4</v>
       </c>
       <c r="H81" t="n">
-        <v>11.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.29</v>
+        <v>11.49</v>
       </c>
       <c r="K81" t="n">
-        <v>113.91</v>
+        <v>129.24</v>
       </c>
       <c r="L81" t="n">
-        <v>113.91</v>
+        <v>129.74</v>
       </c>
     </row>
     <row r="82">
@@ -3484,25 +3484,25 @@
         <v>3.58</v>
       </c>
       <c r="F82" t="n">
-        <v>11.13</v>
+        <v>9.19</v>
       </c>
       <c r="G82" t="n">
-        <v>128</v>
+        <v>127.5</v>
       </c>
       <c r="H82" t="n">
-        <v>6.9</v>
+        <v>10.9</v>
       </c>
       <c r="I82" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>-90.65000000000001</v>
+        <v>-101.02</v>
       </c>
       <c r="K82" t="n">
-        <v>-11.01</v>
+        <v>-29.63</v>
       </c>
       <c r="L82" t="n">
-        <v>91.31999999999999</v>
+        <v>105.28</v>
       </c>
     </row>
     <row r="83">
@@ -3526,25 +3526,25 @@
         <v>4.32</v>
       </c>
       <c r="F83" t="n">
-        <v>10.06</v>
+        <v>12.65</v>
       </c>
       <c r="G83" t="n">
-        <v>125.2</v>
+        <v>106.2</v>
       </c>
       <c r="H83" t="n">
-        <v>11.8</v>
+        <v>9.5</v>
       </c>
       <c r="I83" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>127.67</v>
+        <v>159.86</v>
       </c>
       <c r="K83" t="n">
-        <v>-62.34</v>
+        <v>-61.62</v>
       </c>
       <c r="L83" t="n">
-        <v>142.08</v>
+        <v>171.33</v>
       </c>
     </row>
     <row r="84">
@@ -3568,25 +3568,25 @@
         <v>4.32</v>
       </c>
       <c r="F84" t="n">
-        <v>11.31</v>
+        <v>12.65</v>
       </c>
       <c r="G84" t="n">
-        <v>136.2</v>
+        <v>131.3</v>
       </c>
       <c r="H84" t="n">
-        <v>10.3</v>
+        <v>15</v>
       </c>
       <c r="I84" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>-181.72</v>
+        <v>-189.98</v>
       </c>
       <c r="K84" t="n">
-        <v>38.45</v>
+        <v>24.99</v>
       </c>
       <c r="L84" t="n">
-        <v>185.74</v>
+        <v>191.61</v>
       </c>
     </row>
     <row r="85">
@@ -3610,25 +3610,25 @@
         <v>4.62</v>
       </c>
       <c r="F85" t="n">
-        <v>12.01</v>
+        <v>12.65</v>
       </c>
       <c r="G85" t="n">
-        <v>122.9</v>
+        <v>145.2</v>
       </c>
       <c r="H85" t="n">
-        <v>18.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I85" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J85" t="n">
-        <v>-80.09999999999999</v>
+        <v>-74.7</v>
       </c>
       <c r="K85" t="n">
-        <v>-126.53</v>
+        <v>-184.05</v>
       </c>
       <c r="L85" t="n">
-        <v>149.75</v>
+        <v>198.64</v>
       </c>
     </row>
     <row r="86">
@@ -3652,25 +3652,25 @@
         <v>3.77</v>
       </c>
       <c r="F86" t="n">
-        <v>10.71</v>
+        <v>10.43</v>
       </c>
       <c r="G86" t="n">
-        <v>126.2</v>
+        <v>119.3</v>
       </c>
       <c r="H86" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="I86" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>224.55</v>
+        <v>274.23</v>
       </c>
       <c r="K86" t="n">
-        <v>121.31</v>
+        <v>118.56</v>
       </c>
       <c r="L86" t="n">
-        <v>255.22</v>
+        <v>298.76</v>
       </c>
     </row>
     <row r="87">
@@ -3694,25 +3694,25 @@
         <v>4.14</v>
       </c>
       <c r="F87" t="n">
-        <v>10.85</v>
+        <v>9.16</v>
       </c>
       <c r="G87" t="n">
-        <v>124.5</v>
+        <v>122</v>
       </c>
       <c r="H87" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I87" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>6.88</v>
+        <v>41.32</v>
       </c>
       <c r="K87" t="n">
-        <v>-251.46</v>
+        <v>-299.63</v>
       </c>
       <c r="L87" t="n">
-        <v>251.56</v>
+        <v>302.46</v>
       </c>
     </row>
     <row r="88">
@@ -3736,25 +3736,25 @@
         <v>4.82</v>
       </c>
       <c r="F88" t="n">
-        <v>10.02</v>
+        <v>12.65</v>
       </c>
       <c r="G88" t="n">
-        <v>110.9</v>
+        <v>105.3</v>
       </c>
       <c r="H88" t="n">
-        <v>7.8</v>
+        <v>2.4</v>
       </c>
       <c r="I88" t="n">
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>16.99</v>
+        <v>84.18000000000001</v>
       </c>
       <c r="K88" t="n">
-        <v>240.01</v>
+        <v>260.85</v>
       </c>
       <c r="L88" t="n">
-        <v>240.61</v>
+        <v>274.09</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-11.xlsx
+++ b/output/2025-07-11.xlsx
@@ -640,13 +640,13 @@
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.11</v>
+        <v>-2.3</v>
       </c>
       <c r="K14" t="n">
-        <v>-66.77</v>
+        <v>-72.75</v>
       </c>
       <c r="L14" t="n">
-        <v>66.81</v>
+        <v>72.78</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-54.71</v>
+        <v>-55.67</v>
       </c>
       <c r="K15" t="n">
-        <v>86.83</v>
+        <v>88.36</v>
       </c>
       <c r="L15" t="n">
-        <v>102.63</v>
+        <v>104.43</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>18</v>
       </c>
       <c r="J16" t="n">
-        <v>-55.92</v>
+        <v>-61.7</v>
       </c>
       <c r="K16" t="n">
-        <v>101.68</v>
+        <v>112.18</v>
       </c>
       <c r="L16" t="n">
-        <v>116.04</v>
+        <v>128.03</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>-33.27</v>
+        <v>-33.15</v>
       </c>
       <c r="K17" t="n">
-        <v>65.84</v>
+        <v>65.61</v>
       </c>
       <c r="L17" t="n">
-        <v>73.77</v>
+        <v>73.51000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>18.72</v>
+        <v>18.64</v>
       </c>
       <c r="K18" t="n">
-        <v>105.49</v>
+        <v>104.99</v>
       </c>
       <c r="L18" t="n">
-        <v>107.14</v>
+        <v>106.63</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>58.86</v>
+        <v>60.01</v>
       </c>
       <c r="K19" t="n">
-        <v>-26.92</v>
+        <v>-27.45</v>
       </c>
       <c r="L19" t="n">
-        <v>64.73</v>
+        <v>65.98999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>54.64</v>
+        <v>56.66</v>
       </c>
       <c r="K20" t="n">
-        <v>-62.51</v>
+        <v>-64.81</v>
       </c>
       <c r="L20" t="n">
-        <v>83.02</v>
+        <v>86.09</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>-68.09999999999999</v>
+        <v>-75.40000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-148.3</v>
+        <v>-164.19</v>
       </c>
       <c r="L21" t="n">
-        <v>163.19</v>
+        <v>180.67</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-77.54000000000001</v>
+        <v>-84.48999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>-48.44</v>
+        <v>-52.78</v>
       </c>
       <c r="L22" t="n">
-        <v>91.43000000000001</v>
+        <v>99.62</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>180.13</v>
+        <v>196.74</v>
       </c>
       <c r="K23" t="n">
-        <v>-70.77</v>
+        <v>-77.29000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>193.53</v>
+        <v>211.38</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-131.57</v>
+        <v>-131.61</v>
       </c>
       <c r="K24" t="n">
-        <v>-114.01</v>
+        <v>-114.05</v>
       </c>
       <c r="L24" t="n">
-        <v>174.09</v>
+        <v>174.15</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>73.09</v>
+        <v>74.58</v>
       </c>
       <c r="K25" t="n">
-        <v>185.58</v>
+        <v>189.35</v>
       </c>
       <c r="L25" t="n">
-        <v>199.45</v>
+        <v>203.5</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>-297.55</v>
+        <v>-304.77</v>
       </c>
       <c r="K26" t="n">
-        <v>-57.68</v>
+        <v>-59.08</v>
       </c>
       <c r="L26" t="n">
-        <v>303.09</v>
+        <v>310.45</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>-237.7</v>
+        <v>-263.97</v>
       </c>
       <c r="K27" t="n">
-        <v>-103.02</v>
+        <v>-114.4</v>
       </c>
       <c r="L27" t="n">
-        <v>259.07</v>
+        <v>287.69</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>9.49</v>
+        <v>10.24</v>
       </c>
       <c r="K28" t="n">
-        <v>179.68</v>
+        <v>193.76</v>
       </c>
       <c r="L28" t="n">
-        <v>179.93</v>
+        <v>194.03</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>-90.55</v>
+        <v>-97.06999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>-4.39</v>
+        <v>-4.7</v>
       </c>
       <c r="L29" t="n">
-        <v>90.66</v>
+        <v>97.18000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>-78.87</v>
+        <v>-87.26000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>19.84</v>
+        <v>21.95</v>
       </c>
       <c r="L30" t="n">
-        <v>81.33</v>
+        <v>89.98</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>59.75</v>
+        <v>66.09</v>
       </c>
       <c r="K31" t="n">
-        <v>-34.06</v>
+        <v>-37.68</v>
       </c>
       <c r="L31" t="n">
-        <v>68.77</v>
+        <v>76.08</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>62.99</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>-50.77</v>
+        <v>-53.56</v>
       </c>
       <c r="L32" t="n">
-        <v>80.91</v>
+        <v>85.36</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>-35.98</v>
+        <v>-37.87</v>
       </c>
       <c r="K33" t="n">
-        <v>115.47</v>
+        <v>121.52</v>
       </c>
       <c r="L33" t="n">
-        <v>120.94</v>
+        <v>127.29</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>71.40000000000001</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>-70.44</v>
+        <v>-77.90000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>100.3</v>
+        <v>110.92</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-69.98999999999999</v>
+        <v>-72.65000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>-98.98</v>
+        <v>-102.74</v>
       </c>
       <c r="L35" t="n">
-        <v>121.23</v>
+        <v>125.83</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>40.46</v>
+        <v>44.12</v>
       </c>
       <c r="K36" t="n">
-        <v>-123.08</v>
+        <v>-134.21</v>
       </c>
       <c r="L36" t="n">
-        <v>129.56</v>
+        <v>141.27</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>166.97</v>
+        <v>184.76</v>
       </c>
       <c r="K37" t="n">
-        <v>-11.3</v>
+        <v>-12.51</v>
       </c>
       <c r="L37" t="n">
-        <v>167.35</v>
+        <v>185.19</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>43.93</v>
+        <v>46.41</v>
       </c>
       <c r="K38" t="n">
-        <v>-191.66</v>
+        <v>-202.51</v>
       </c>
       <c r="L38" t="n">
-        <v>196.63</v>
+        <v>207.76</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>159.46</v>
+        <v>162.69</v>
       </c>
       <c r="K39" t="n">
         <v>-0.4</v>
       </c>
       <c r="L39" t="n">
-        <v>159.46</v>
+        <v>162.69</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>149.08</v>
+        <v>154.99</v>
       </c>
       <c r="K40" t="n">
-        <v>50.84</v>
+        <v>52.85</v>
       </c>
       <c r="L40" t="n">
-        <v>157.51</v>
+        <v>163.76</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>-138.27</v>
+        <v>-151.56</v>
       </c>
       <c r="K41" t="n">
-        <v>-226.16</v>
+        <v>-247.89</v>
       </c>
       <c r="L41" t="n">
-        <v>265.08</v>
+        <v>290.55</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>36.05</v>
+        <v>40.14</v>
       </c>
       <c r="K42" t="n">
-        <v>224.34</v>
+        <v>249.82</v>
       </c>
       <c r="L42" t="n">
-        <v>227.21</v>
+        <v>253.03</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>245.56</v>
+        <v>246.9</v>
       </c>
       <c r="K43" t="n">
-        <v>-100.62</v>
+        <v>-101.17</v>
       </c>
       <c r="L43" t="n">
-        <v>265.37</v>
+        <v>266.83</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>34.42</v>
+        <v>35.58</v>
       </c>
       <c r="K44" t="n">
-        <v>53.51</v>
+        <v>55.31</v>
       </c>
       <c r="L44" t="n">
-        <v>63.63</v>
+        <v>65.77</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="K45" t="n">
-        <v>70.98999999999999</v>
+        <v>70.63</v>
       </c>
       <c r="L45" t="n">
-        <v>71.01000000000001</v>
+        <v>70.66</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>-71.37</v>
+        <v>-76.43000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>21.84</v>
+        <v>23.39</v>
       </c>
       <c r="L46" t="n">
-        <v>74.64</v>
+        <v>79.93000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>-101.78</v>
+        <v>-112.27</v>
       </c>
       <c r="K47" t="n">
-        <v>-52.92</v>
+        <v>-58.38</v>
       </c>
       <c r="L47" t="n">
-        <v>114.72</v>
+        <v>126.54</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-71.64</v>
+        <v>-79.18000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>71.33</v>
+        <v>78.83</v>
       </c>
       <c r="L48" t="n">
-        <v>101.09</v>
+        <v>111.73</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>42.64</v>
+        <v>45.05</v>
       </c>
       <c r="K49" t="n">
-        <v>47.24</v>
+        <v>49.91</v>
       </c>
       <c r="L49" t="n">
-        <v>63.63</v>
+        <v>67.23999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>122.34</v>
+        <v>129.02</v>
       </c>
       <c r="K50" t="n">
-        <v>87.95</v>
+        <v>92.75</v>
       </c>
       <c r="L50" t="n">
-        <v>150.67</v>
+        <v>158.9</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-39.66</v>
+        <v>-41.12</v>
       </c>
       <c r="K51" t="n">
-        <v>-150.76</v>
+        <v>-156.32</v>
       </c>
       <c r="L51" t="n">
-        <v>155.89</v>
+        <v>161.63</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>-20.98</v>
+        <v>-23.22</v>
       </c>
       <c r="K52" t="n">
-        <v>-132.75</v>
+        <v>-146.93</v>
       </c>
       <c r="L52" t="n">
-        <v>134.4</v>
+        <v>148.75</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>129.69</v>
+        <v>141.61</v>
       </c>
       <c r="K53" t="n">
-        <v>-120.61</v>
+        <v>-131.69</v>
       </c>
       <c r="L53" t="n">
-        <v>177.11</v>
+        <v>193.37</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="K54" t="n">
-        <v>164.12</v>
+        <v>170.67</v>
       </c>
       <c r="L54" t="n">
-        <v>164.13</v>
+        <v>170.67</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>8.369999999999999</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="K55" t="n">
-        <v>63.11</v>
+        <v>69.91</v>
       </c>
       <c r="L55" t="n">
-        <v>63.66</v>
+        <v>70.52</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>19</v>
       </c>
       <c r="J56" t="n">
-        <v>81.09</v>
+        <v>89.95</v>
       </c>
       <c r="K56" t="n">
-        <v>270.37</v>
+        <v>299.92</v>
       </c>
       <c r="L56" t="n">
-        <v>282.26</v>
+        <v>313.12</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>232.65</v>
+        <v>255.57</v>
       </c>
       <c r="K57" t="n">
-        <v>-19.62</v>
+        <v>-21.55</v>
       </c>
       <c r="L57" t="n">
-        <v>233.48</v>
+        <v>256.48</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>19</v>
       </c>
       <c r="J58" t="n">
-        <v>-19.46</v>
+        <v>-21.54</v>
       </c>
       <c r="K58" t="n">
-        <v>265.1</v>
+        <v>293.48</v>
       </c>
       <c r="L58" t="n">
-        <v>265.82</v>
+        <v>294.27</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-27.37</v>
+        <v>-28.85</v>
       </c>
       <c r="K59" t="n">
-        <v>65.89</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>71.34999999999999</v>
+        <v>75.20999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>62.47</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>-24.57</v>
+        <v>-25.36</v>
       </c>
       <c r="L60" t="n">
-        <v>67.13</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>56.54</v>
+        <v>60.57</v>
       </c>
       <c r="K61" t="n">
-        <v>-61.24</v>
+        <v>-65.61</v>
       </c>
       <c r="L61" t="n">
-        <v>83.34999999999999</v>
+        <v>89.29000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.47</v>
+        <v>-0.49</v>
       </c>
       <c r="K62" t="n">
-        <v>-106.03</v>
+        <v>-109.46</v>
       </c>
       <c r="L62" t="n">
-        <v>106.03</v>
+        <v>109.46</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-63.21</v>
+        <v>-63.02</v>
       </c>
       <c r="K63" t="n">
-        <v>62.73</v>
+        <v>62.53</v>
       </c>
       <c r="L63" t="n">
-        <v>89.05</v>
+        <v>88.78</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>28.05</v>
+        <v>29.61</v>
       </c>
       <c r="K64" t="n">
-        <v>-97.37</v>
+        <v>-102.79</v>
       </c>
       <c r="L64" t="n">
-        <v>101.33</v>
+        <v>106.97</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>5.73</v>
+        <v>6.24</v>
       </c>
       <c r="K65" t="n">
-        <v>-152.18</v>
+        <v>-165.7</v>
       </c>
       <c r="L65" t="n">
-        <v>152.29</v>
+        <v>165.82</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-156.89</v>
+        <v>-159.72</v>
       </c>
       <c r="K66" t="n">
-        <v>-42.07</v>
+        <v>-42.83</v>
       </c>
       <c r="L66" t="n">
-        <v>162.43</v>
+        <v>165.36</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>69.81</v>
+        <v>74.81</v>
       </c>
       <c r="K67" t="n">
-        <v>203.77</v>
+        <v>218.38</v>
       </c>
       <c r="L67" t="n">
-        <v>215.4</v>
+        <v>230.84</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>200.87</v>
+        <v>213.84</v>
       </c>
       <c r="K68" t="n">
-        <v>49.24</v>
+        <v>52.41</v>
       </c>
       <c r="L68" t="n">
-        <v>206.82</v>
+        <v>220.17</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-133.26</v>
+        <v>-138.47</v>
       </c>
       <c r="K69" t="n">
-        <v>43.74</v>
+        <v>45.45</v>
       </c>
       <c r="L69" t="n">
-        <v>140.25</v>
+        <v>145.74</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.79</v>
+        <v>-0.85</v>
       </c>
       <c r="K70" t="n">
-        <v>-174.22</v>
+        <v>-187.34</v>
       </c>
       <c r="L70" t="n">
-        <v>174.23</v>
+        <v>187.34</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-123.92</v>
+        <v>-129.49</v>
       </c>
       <c r="K71" t="n">
-        <v>295.69</v>
+        <v>308.97</v>
       </c>
       <c r="L71" t="n">
-        <v>320.61</v>
+        <v>335.01</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>71.20999999999999</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="K72" t="n">
-        <v>-199.61</v>
+        <v>-214.39</v>
       </c>
       <c r="L72" t="n">
-        <v>211.93</v>
+        <v>227.63</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>18</v>
       </c>
       <c r="J73" t="n">
-        <v>-24.35</v>
+        <v>-27.02</v>
       </c>
       <c r="K73" t="n">
-        <v>-302.71</v>
+        <v>-335.86</v>
       </c>
       <c r="L73" t="n">
-        <v>303.68</v>
+        <v>336.94</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>66.45</v>
+        <v>68.95</v>
       </c>
       <c r="K74" t="n">
-        <v>-80.01000000000001</v>
+        <v>-83.02</v>
       </c>
       <c r="L74" t="n">
-        <v>104.01</v>
+        <v>107.92</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-14.7</v>
+        <v>-15.21</v>
       </c>
       <c r="K75" t="n">
-        <v>56.2</v>
+        <v>58.16</v>
       </c>
       <c r="L75" t="n">
-        <v>58.09</v>
+        <v>60.11</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-48.03</v>
+        <v>-50.56</v>
       </c>
       <c r="K76" t="n">
-        <v>-48.62</v>
+        <v>-51.18</v>
       </c>
       <c r="L76" t="n">
-        <v>68.34</v>
+        <v>71.94</v>
       </c>
     </row>
     <row r="77">
@@ -3289,10 +3289,10 @@
         <v>-0</v>
       </c>
       <c r="K77" t="n">
-        <v>-89.7</v>
+        <v>-92.66</v>
       </c>
       <c r="L77" t="n">
-        <v>89.7</v>
+        <v>92.66</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>8</v>
+        <v>7.96</v>
       </c>
       <c r="K78" t="n">
-        <v>-120.6</v>
+        <v>-120.09</v>
       </c>
       <c r="L78" t="n">
-        <v>120.87</v>
+        <v>120.35</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>82.45</v>
+        <v>89.81999999999999</v>
       </c>
       <c r="K79" t="n">
-        <v>70.97</v>
+        <v>77.31</v>
       </c>
       <c r="L79" t="n">
-        <v>108.79</v>
+        <v>118.51</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>93.5</v>
+        <v>100.27</v>
       </c>
       <c r="K80" t="n">
-        <v>63.93</v>
+        <v>68.56</v>
       </c>
       <c r="L80" t="n">
-        <v>113.26</v>
+        <v>121.46</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>11.49</v>
+        <v>12.12</v>
       </c>
       <c r="K81" t="n">
-        <v>129.24</v>
+        <v>136.38</v>
       </c>
       <c r="L81" t="n">
-        <v>129.74</v>
+        <v>136.92</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>-101.02</v>
+        <v>-110.14</v>
       </c>
       <c r="K82" t="n">
-        <v>-29.63</v>
+        <v>-32.3</v>
       </c>
       <c r="L82" t="n">
-        <v>105.28</v>
+        <v>114.78</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>159.86</v>
+        <v>160.06</v>
       </c>
       <c r="K83" t="n">
-        <v>-61.62</v>
+        <v>-61.7</v>
       </c>
       <c r="L83" t="n">
-        <v>171.33</v>
+        <v>171.54</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>-189.98</v>
+        <v>-193.94</v>
       </c>
       <c r="K84" t="n">
-        <v>24.99</v>
+        <v>25.51</v>
       </c>
       <c r="L84" t="n">
-        <v>191.61</v>
+        <v>195.61</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>18</v>
       </c>
       <c r="J85" t="n">
-        <v>-74.7</v>
+        <v>-83.34999999999999</v>
       </c>
       <c r="K85" t="n">
-        <v>-184.05</v>
+        <v>-205.37</v>
       </c>
       <c r="L85" t="n">
-        <v>198.64</v>
+        <v>221.64</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>274.23</v>
+        <v>280.79</v>
       </c>
       <c r="K86" t="n">
-        <v>118.56</v>
+        <v>121.39</v>
       </c>
       <c r="L86" t="n">
-        <v>298.76</v>
+        <v>305.9</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>41.32</v>
+        <v>46.05</v>
       </c>
       <c r="K87" t="n">
-        <v>-299.63</v>
+        <v>-333.97</v>
       </c>
       <c r="L87" t="n">
-        <v>302.46</v>
+        <v>337.13</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>84.18000000000001</v>
+        <v>90.48</v>
       </c>
       <c r="K88" t="n">
-        <v>260.85</v>
+        <v>280.37</v>
       </c>
       <c r="L88" t="n">
-        <v>274.09</v>
+        <v>294.61</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-11.xlsx
+++ b/output/2025-07-11.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.51</v>
+        <v>3.7</v>
       </c>
       <c r="F14" t="n">
-        <v>9.48</v>
+        <v>10.51</v>
       </c>
       <c r="G14" t="n">
-        <v>139.5</v>
+        <v>120.8</v>
       </c>
       <c r="H14" t="n">
-        <v>3.9</v>
+        <v>56.9</v>
       </c>
       <c r="I14" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.3</v>
+        <v>63.81</v>
       </c>
       <c r="K14" t="n">
-        <v>-72.75</v>
+        <v>-12.56</v>
       </c>
       <c r="L14" t="n">
-        <v>72.78</v>
+        <v>65.03</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:45:53</t>
+          <t>04:46:24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.66</v>
+        <v>3.22</v>
       </c>
       <c r="F15" t="n">
-        <v>8.210000000000001</v>
+        <v>7.95</v>
       </c>
       <c r="G15" t="n">
-        <v>124.2</v>
+        <v>127.2</v>
       </c>
       <c r="H15" t="n">
-        <v>9.699999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="I15" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>-55.67</v>
+        <v>19.1</v>
       </c>
       <c r="K15" t="n">
-        <v>88.36</v>
+        <v>-48.7</v>
       </c>
       <c r="L15" t="n">
-        <v>104.43</v>
+        <v>52.31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:48:29</t>
+          <t>04:48:06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.97</v>
+        <v>3.4</v>
       </c>
       <c r="F16" t="n">
-        <v>12</v>
+        <v>6.58</v>
       </c>
       <c r="G16" t="n">
-        <v>122.2</v>
+        <v>114.1</v>
       </c>
       <c r="H16" t="n">
-        <v>10.6</v>
+        <v>36.5</v>
       </c>
       <c r="I16" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>-61.7</v>
+        <v>20.08</v>
       </c>
       <c r="K16" t="n">
-        <v>112.18</v>
+        <v>-53.4</v>
       </c>
       <c r="L16" t="n">
-        <v>128.03</v>
+        <v>57.05</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:52:28</t>
+          <t>04:51:45</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.97</v>
+        <v>4.35</v>
       </c>
       <c r="F17" t="n">
-        <v>7.56</v>
+        <v>12.18</v>
       </c>
       <c r="G17" t="n">
-        <v>130.6</v>
+        <v>127.4</v>
       </c>
       <c r="H17" t="n">
-        <v>8.300000000000001</v>
+        <v>34.6</v>
       </c>
       <c r="I17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-33.15</v>
+        <v>-69.59</v>
       </c>
       <c r="K17" t="n">
-        <v>65.61</v>
+        <v>71.09</v>
       </c>
       <c r="L17" t="n">
-        <v>73.51000000000001</v>
+        <v>99.48</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:54:18</t>
+          <t>04:52:43</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>4.25</v>
+        <v>3.26</v>
       </c>
       <c r="F18" t="n">
-        <v>9.24</v>
+        <v>10.07</v>
       </c>
       <c r="G18" t="n">
-        <v>114.9</v>
+        <v>126.7</v>
       </c>
       <c r="H18" t="n">
-        <v>13.5</v>
+        <v>41.1</v>
       </c>
       <c r="I18" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J18" t="n">
-        <v>18.64</v>
+        <v>73.16</v>
       </c>
       <c r="K18" t="n">
-        <v>104.99</v>
+        <v>-63.12</v>
       </c>
       <c r="L18" t="n">
-        <v>106.63</v>
+        <v>96.62</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:55:50</t>
+          <t>04:54:46</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.28</v>
+        <v>3.87</v>
       </c>
       <c r="F19" t="n">
-        <v>8.6</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>131.4</v>
+        <v>135.5</v>
       </c>
       <c r="H19" t="n">
-        <v>2.3</v>
+        <v>53.3</v>
       </c>
       <c r="I19" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J19" t="n">
-        <v>60.01</v>
+        <v>25.96</v>
       </c>
       <c r="K19" t="n">
-        <v>-27.45</v>
+        <v>-102.37</v>
       </c>
       <c r="L19" t="n">
-        <v>65.98999999999999</v>
+        <v>105.61</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:00:12</t>
+          <t>04:58:55</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>4.12</v>
+        <v>4.05</v>
       </c>
       <c r="F20" t="n">
-        <v>8.82</v>
+        <v>11.33</v>
       </c>
       <c r="G20" t="n">
-        <v>107.4</v>
+        <v>122.2</v>
       </c>
       <c r="H20" t="n">
-        <v>16.1</v>
+        <v>35</v>
       </c>
       <c r="I20" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J20" t="n">
-        <v>56.66</v>
+        <v>-52.9</v>
       </c>
       <c r="K20" t="n">
-        <v>-64.81</v>
+        <v>-156.38</v>
       </c>
       <c r="L20" t="n">
-        <v>86.09</v>
+        <v>165.09</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:02:21</t>
+          <t>05:01:22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.05</v>
+        <v>4.48</v>
       </c>
       <c r="F21" t="n">
-        <v>9.44</v>
+        <v>11.61</v>
       </c>
       <c r="G21" t="n">
-        <v>117.6</v>
+        <v>118.5</v>
       </c>
       <c r="H21" t="n">
-        <v>7.7</v>
+        <v>74.2</v>
       </c>
       <c r="I21" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J21" t="n">
-        <v>-75.40000000000001</v>
+        <v>178.62</v>
       </c>
       <c r="K21" t="n">
-        <v>-164.19</v>
+        <v>109.52</v>
       </c>
       <c r="L21" t="n">
-        <v>180.67</v>
+        <v>209.52</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:04:45</t>
+          <t>05:02:29</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.94</v>
+        <v>4.37</v>
       </c>
       <c r="F22" t="n">
-        <v>5.52</v>
+        <v>10.58</v>
       </c>
       <c r="G22" t="n">
-        <v>126.1</v>
+        <v>116.2</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>44.3</v>
       </c>
       <c r="I22" t="n">
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-84.48999999999999</v>
+        <v>-31.85</v>
       </c>
       <c r="K22" t="n">
-        <v>-52.78</v>
+        <v>168.33</v>
       </c>
       <c r="L22" t="n">
-        <v>99.62</v>
+        <v>171.31</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:07:46</t>
+          <t>05:07:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.29</v>
+        <v>3.37</v>
       </c>
       <c r="F23" t="n">
-        <v>11.07</v>
+        <v>10.31</v>
       </c>
       <c r="G23" t="n">
-        <v>110.1</v>
+        <v>125.8</v>
       </c>
       <c r="H23" t="n">
-        <v>6.4</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I23" t="n">
         <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>196.74</v>
+        <v>116.52</v>
       </c>
       <c r="K23" t="n">
-        <v>-77.29000000000001</v>
+        <v>-158.3</v>
       </c>
       <c r="L23" t="n">
-        <v>211.38</v>
+        <v>196.55</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:09:58</t>
+          <t>05:08:24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="F24" t="n">
-        <v>10.76</v>
+        <v>4.84</v>
       </c>
       <c r="G24" t="n">
-        <v>143.1</v>
+        <v>124.6</v>
       </c>
       <c r="H24" t="n">
-        <v>16.3</v>
+        <v>37</v>
       </c>
       <c r="I24" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-131.61</v>
+        <v>192.43</v>
       </c>
       <c r="K24" t="n">
-        <v>-114.05</v>
+        <v>-66.08</v>
       </c>
       <c r="L24" t="n">
-        <v>174.15</v>
+        <v>203.46</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:10:26</t>
+          <t>05:10:38</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.83</v>
+        <v>4.1</v>
       </c>
       <c r="F25" t="n">
-        <v>8.19</v>
+        <v>9.58</v>
       </c>
       <c r="G25" t="n">
-        <v>123.8</v>
+        <v>114.8</v>
       </c>
       <c r="H25" t="n">
-        <v>6.2</v>
+        <v>16.4</v>
       </c>
       <c r="I25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>74.58</v>
+        <v>214.07</v>
       </c>
       <c r="K25" t="n">
-        <v>189.35</v>
+        <v>-42.52</v>
       </c>
       <c r="L25" t="n">
-        <v>203.5</v>
+        <v>218.25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:16:33</t>
+          <t>05:15:21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.82</v>
+        <v>4.15</v>
       </c>
       <c r="F26" t="n">
-        <v>8.949999999999999</v>
+        <v>11.52</v>
       </c>
       <c r="G26" t="n">
-        <v>118</v>
+        <v>125.8</v>
       </c>
       <c r="H26" t="n">
-        <v>8.6</v>
+        <v>35.7</v>
       </c>
       <c r="I26" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>-304.77</v>
+        <v>-225.52</v>
       </c>
       <c r="K26" t="n">
-        <v>-59.08</v>
+        <v>-172.94</v>
       </c>
       <c r="L26" t="n">
-        <v>310.45</v>
+        <v>284.19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:18:23</t>
+          <t>05:16:11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.61</v>
+        <v>3.64</v>
       </c>
       <c r="F27" t="n">
-        <v>8.77</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>120.7</v>
+        <v>130.2</v>
       </c>
       <c r="H27" t="n">
-        <v>14.2</v>
+        <v>32.4</v>
       </c>
       <c r="I27" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-263.97</v>
+        <v>148.21</v>
       </c>
       <c r="K27" t="n">
-        <v>-114.4</v>
+        <v>-119.58</v>
       </c>
       <c r="L27" t="n">
-        <v>287.69</v>
+        <v>190.44</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:19:57</t>
+          <t>05:18:24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.74</v>
+        <v>2.96</v>
       </c>
       <c r="F28" t="n">
-        <v>11.72</v>
+        <v>7.01</v>
       </c>
       <c r="G28" t="n">
-        <v>117.7</v>
+        <v>120.9</v>
       </c>
       <c r="H28" t="n">
-        <v>10.2</v>
+        <v>55.9</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>10.24</v>
+        <v>162.23</v>
       </c>
       <c r="K28" t="n">
-        <v>193.76</v>
+        <v>-148.94</v>
       </c>
       <c r="L28" t="n">
-        <v>194.03</v>
+        <v>220.23</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:29:35</t>
+          <t>05:28:39</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.65</v>
+        <v>3.36</v>
       </c>
       <c r="F29" t="n">
-        <v>8.56</v>
+        <v>6.91</v>
       </c>
       <c r="G29" t="n">
-        <v>129.6</v>
+        <v>119.1</v>
       </c>
       <c r="H29" t="n">
-        <v>9.1</v>
+        <v>36.9</v>
       </c>
       <c r="I29" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J29" t="n">
-        <v>-97.06999999999999</v>
+        <v>-51.01</v>
       </c>
       <c r="K29" t="n">
-        <v>-4.7</v>
+        <v>12.05</v>
       </c>
       <c r="L29" t="n">
-        <v>97.18000000000001</v>
+        <v>52.42</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:30:39</t>
+          <t>05:30:48</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.39</v>
+        <v>3.45</v>
       </c>
       <c r="F30" t="n">
-        <v>10.04</v>
+        <v>10.61</v>
       </c>
       <c r="G30" t="n">
-        <v>120.8</v>
+        <v>135.3</v>
       </c>
       <c r="H30" t="n">
-        <v>7.5</v>
+        <v>22.3</v>
       </c>
       <c r="I30" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-87.26000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="K30" t="n">
-        <v>21.95</v>
+        <v>-58.26</v>
       </c>
       <c r="L30" t="n">
-        <v>89.98</v>
+        <v>58.27</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:32:38</t>
+          <t>05:33:08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.42</v>
+        <v>4.01</v>
       </c>
       <c r="F31" t="n">
-        <v>6.8</v>
+        <v>8.9</v>
       </c>
       <c r="G31" t="n">
-        <v>122.6</v>
+        <v>124.7</v>
       </c>
       <c r="H31" t="n">
-        <v>6.4</v>
+        <v>3.7</v>
       </c>
       <c r="I31" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J31" t="n">
-        <v>66.09</v>
+        <v>49.96</v>
       </c>
       <c r="K31" t="n">
-        <v>-37.68</v>
+        <v>39.84</v>
       </c>
       <c r="L31" t="n">
-        <v>76.08</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:37:08</t>
+          <t>05:38:03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.55</v>
+        <v>3.76</v>
       </c>
       <c r="F32" t="n">
-        <v>7.43</v>
+        <v>11.51</v>
       </c>
       <c r="G32" t="n">
-        <v>120.2</v>
+        <v>126.4</v>
       </c>
       <c r="H32" t="n">
-        <v>9.5</v>
+        <v>42.4</v>
       </c>
       <c r="I32" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>66.45999999999999</v>
+        <v>9.35</v>
       </c>
       <c r="K32" t="n">
-        <v>-53.56</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>85.36</v>
+        <v>82.84999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:38:10</t>
+          <t>05:38:41</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.07</v>
+        <v>3.3</v>
       </c>
       <c r="F33" t="n">
-        <v>11.73</v>
+        <v>8.09</v>
       </c>
       <c r="G33" t="n">
-        <v>116.1</v>
+        <v>121.7</v>
       </c>
       <c r="H33" t="n">
-        <v>14</v>
+        <v>73.8</v>
       </c>
       <c r="I33" t="n">
         <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>-37.87</v>
+        <v>-46.57</v>
       </c>
       <c r="K33" t="n">
-        <v>121.52</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>127.29</v>
+        <v>87.01000000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:40:12</t>
+          <t>05:40:33</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="F34" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>116.4</v>
+        <v>118.6</v>
       </c>
       <c r="H34" t="n">
-        <v>8.5</v>
+        <v>64.7</v>
       </c>
       <c r="I34" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>78.95999999999999</v>
+        <v>13.79</v>
       </c>
       <c r="K34" t="n">
-        <v>-77.90000000000001</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>110.92</v>
+        <v>70.65000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:45:13</t>
+          <t>05:46:41</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.49</v>
+        <v>3.8</v>
       </c>
       <c r="F35" t="n">
-        <v>11.12</v>
+        <v>12.65</v>
       </c>
       <c r="G35" t="n">
-        <v>118.7</v>
+        <v>113.2</v>
       </c>
       <c r="H35" t="n">
-        <v>14.5</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I35" t="n">
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-72.65000000000001</v>
+        <v>-17.76</v>
       </c>
       <c r="K35" t="n">
-        <v>-102.74</v>
+        <v>137.14</v>
       </c>
       <c r="L35" t="n">
-        <v>125.83</v>
+        <v>138.28</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:46:51</t>
+          <t>05:48:43</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.51</v>
+        <v>3.44</v>
       </c>
       <c r="F36" t="n">
-        <v>9.15</v>
+        <v>9.51</v>
       </c>
       <c r="G36" t="n">
-        <v>126.9</v>
+        <v>103.7</v>
       </c>
       <c r="H36" t="n">
-        <v>6</v>
+        <v>27.1</v>
       </c>
       <c r="I36" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>44.12</v>
+        <v>102.26</v>
       </c>
       <c r="K36" t="n">
-        <v>-134.21</v>
+        <v>63.47</v>
       </c>
       <c r="L36" t="n">
-        <v>141.27</v>
+        <v>120.35</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:49:07</t>
+          <t>05:51:04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.53</v>
+        <v>4.12</v>
       </c>
       <c r="F37" t="n">
-        <v>10.93</v>
+        <v>12.65</v>
       </c>
       <c r="G37" t="n">
-        <v>119.3</v>
+        <v>132.4</v>
       </c>
       <c r="H37" t="n">
-        <v>8.699999999999999</v>
+        <v>44.6</v>
       </c>
       <c r="I37" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J37" t="n">
-        <v>184.76</v>
+        <v>19.73</v>
       </c>
       <c r="K37" t="n">
-        <v>-12.51</v>
+        <v>82.06999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>185.19</v>
+        <v>84.41</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:54:06</t>
+          <t>05:55:22</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.22</v>
+        <v>3.92</v>
       </c>
       <c r="F38" t="n">
-        <v>9.49</v>
+        <v>7.99</v>
       </c>
       <c r="G38" t="n">
-        <v>118.1</v>
+        <v>127.2</v>
       </c>
       <c r="H38" t="n">
-        <v>7.6</v>
+        <v>13.3</v>
       </c>
       <c r="I38" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>46.41</v>
+        <v>186.98</v>
       </c>
       <c r="K38" t="n">
-        <v>-202.51</v>
+        <v>-196.43</v>
       </c>
       <c r="L38" t="n">
-        <v>207.76</v>
+        <v>271.19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:56:16</t>
+          <t>05:57:16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.78</v>
+        <v>3.24</v>
       </c>
       <c r="F39" t="n">
-        <v>9.33</v>
+        <v>7.16</v>
       </c>
       <c r="G39" t="n">
-        <v>114.3</v>
+        <v>128.6</v>
       </c>
       <c r="H39" t="n">
-        <v>13.5</v>
+        <v>26.8</v>
       </c>
       <c r="I39" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J39" t="n">
-        <v>162.69</v>
+        <v>-142.56</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.4</v>
+        <v>-125.85</v>
       </c>
       <c r="L39" t="n">
-        <v>162.69</v>
+        <v>190.16</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:57:05</t>
+          <t>05:59:26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.23</v>
+        <v>3.95</v>
       </c>
       <c r="F40" t="n">
-        <v>9.970000000000001</v>
+        <v>12.65</v>
       </c>
       <c r="G40" t="n">
-        <v>151.3</v>
+        <v>119.5</v>
       </c>
       <c r="H40" t="n">
-        <v>7.6</v>
+        <v>54.5</v>
       </c>
       <c r="I40" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>154.99</v>
+        <v>172.5</v>
       </c>
       <c r="K40" t="n">
-        <v>52.85</v>
+        <v>-73.12</v>
       </c>
       <c r="L40" t="n">
-        <v>163.76</v>
+        <v>187.36</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:02:19</t>
+          <t>06:04:06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.84</v>
+        <v>3.45</v>
       </c>
       <c r="F41" t="n">
-        <v>7.18</v>
+        <v>10.02</v>
       </c>
       <c r="G41" t="n">
-        <v>133.1</v>
+        <v>118.6</v>
       </c>
       <c r="H41" t="n">
-        <v>11.1</v>
+        <v>29.8</v>
       </c>
       <c r="I41" t="n">
         <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>-151.56</v>
+        <v>137.03</v>
       </c>
       <c r="K41" t="n">
-        <v>-247.89</v>
+        <v>-167.24</v>
       </c>
       <c r="L41" t="n">
-        <v>290.55</v>
+        <v>216.21</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:03:14</t>
+          <t>06:06:22</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="F42" t="n">
-        <v>9.130000000000001</v>
+        <v>10.02</v>
       </c>
       <c r="G42" t="n">
-        <v>127.3</v>
+        <v>124.6</v>
       </c>
       <c r="H42" t="n">
-        <v>17.1</v>
+        <v>26.7</v>
       </c>
       <c r="I42" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>40.14</v>
+        <v>96.27</v>
       </c>
       <c r="K42" t="n">
-        <v>249.82</v>
+        <v>-273.49</v>
       </c>
       <c r="L42" t="n">
-        <v>253.03</v>
+        <v>289.94</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:04:21</t>
+          <t>06:07:50</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.95</v>
+        <v>3.18</v>
       </c>
       <c r="F43" t="n">
-        <v>8.57</v>
+        <v>7.98</v>
       </c>
       <c r="G43" t="n">
-        <v>129.4</v>
+        <v>131.1</v>
       </c>
       <c r="H43" t="n">
-        <v>6.4</v>
+        <v>63.2</v>
       </c>
       <c r="I43" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>246.9</v>
+        <v>-188.86</v>
       </c>
       <c r="K43" t="n">
-        <v>-101.17</v>
+        <v>-56.5</v>
       </c>
       <c r="L43" t="n">
-        <v>266.83</v>
+        <v>197.13</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:13:29</t>
+          <t>06:16:14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.23</v>
+        <v>3.55</v>
       </c>
       <c r="F44" t="n">
-        <v>12.65</v>
+        <v>11.79</v>
       </c>
       <c r="G44" t="n">
-        <v>120.5</v>
+        <v>128.7</v>
       </c>
       <c r="H44" t="n">
-        <v>14.9</v>
+        <v>41.1</v>
       </c>
       <c r="I44" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>35.58</v>
+        <v>56.71</v>
       </c>
       <c r="K44" t="n">
-        <v>55.31</v>
+        <v>-15.82</v>
       </c>
       <c r="L44" t="n">
-        <v>65.77</v>
+        <v>58.87</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:14:07</t>
+          <t>06:18:28</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.3</v>
+        <v>4.13</v>
       </c>
       <c r="F45" t="n">
-        <v>12.43</v>
+        <v>9.26</v>
       </c>
       <c r="G45" t="n">
-        <v>124.7</v>
+        <v>133.2</v>
       </c>
       <c r="H45" t="n">
-        <v>4.3</v>
+        <v>27.6</v>
       </c>
       <c r="I45" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>1.78</v>
+        <v>-0.27</v>
       </c>
       <c r="K45" t="n">
-        <v>70.63</v>
+        <v>-89</v>
       </c>
       <c r="L45" t="n">
-        <v>70.66</v>
+        <v>89</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:15:44</t>
+          <t>06:20:34</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.85</v>
+        <v>3.92</v>
       </c>
       <c r="F46" t="n">
-        <v>8.65</v>
+        <v>9.99</v>
       </c>
       <c r="G46" t="n">
-        <v>120.7</v>
+        <v>129</v>
       </c>
       <c r="H46" t="n">
-        <v>11.7</v>
+        <v>44.4</v>
       </c>
       <c r="I46" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>-76.43000000000001</v>
+        <v>58.28</v>
       </c>
       <c r="K46" t="n">
-        <v>23.39</v>
+        <v>-12.58</v>
       </c>
       <c r="L46" t="n">
-        <v>79.93000000000001</v>
+        <v>59.62</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:20:11</t>
+          <t>06:24:42</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.02</v>
+        <v>4.04</v>
       </c>
       <c r="F47" t="n">
-        <v>9.779999999999999</v>
+        <v>11.02</v>
       </c>
       <c r="G47" t="n">
-        <v>106.8</v>
+        <v>119</v>
       </c>
       <c r="H47" t="n">
-        <v>15.4</v>
+        <v>57.9</v>
       </c>
       <c r="I47" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>-112.27</v>
+        <v>92.20999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>-58.38</v>
+        <v>55.6</v>
       </c>
       <c r="L47" t="n">
-        <v>126.54</v>
+        <v>107.67</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:22:29</t>
+          <t>06:26:41</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="F48" t="n">
-        <v>10.37</v>
+        <v>8.35</v>
       </c>
       <c r="G48" t="n">
-        <v>127.1</v>
+        <v>118.5</v>
       </c>
       <c r="H48" t="n">
-        <v>13</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>-79.18000000000001</v>
+        <v>120.03</v>
       </c>
       <c r="K48" t="n">
-        <v>78.83</v>
+        <v>-30.59</v>
       </c>
       <c r="L48" t="n">
-        <v>111.73</v>
+        <v>123.86</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:23:17</t>
+          <t>06:28:10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.72</v>
+        <v>3.94</v>
       </c>
       <c r="F49" t="n">
-        <v>9.59</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>110.6</v>
+        <v>126.6</v>
       </c>
       <c r="H49" t="n">
-        <v>18.3</v>
+        <v>66.2</v>
       </c>
       <c r="I49" t="n">
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>45.05</v>
+        <v>132.09</v>
       </c>
       <c r="K49" t="n">
-        <v>49.91</v>
+        <v>-30.41</v>
       </c>
       <c r="L49" t="n">
-        <v>67.23999999999999</v>
+        <v>135.54</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:27:18</t>
+          <t>06:33:27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.41</v>
+        <v>3.9</v>
       </c>
       <c r="F50" t="n">
-        <v>10.82</v>
+        <v>10.85</v>
       </c>
       <c r="G50" t="n">
-        <v>114.5</v>
+        <v>117.2</v>
       </c>
       <c r="H50" t="n">
-        <v>9.1</v>
+        <v>50.2</v>
       </c>
       <c r="I50" t="n">
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>129.02</v>
+        <v>-61.48</v>
       </c>
       <c r="K50" t="n">
-        <v>92.75</v>
+        <v>-132.77</v>
       </c>
       <c r="L50" t="n">
-        <v>158.9</v>
+        <v>146.31</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:27:54</t>
+          <t>06:34:49</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.17</v>
+        <v>3.54</v>
       </c>
       <c r="F51" t="n">
-        <v>12.65</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G51" t="n">
-        <v>133.7</v>
+        <v>118.2</v>
       </c>
       <c r="H51" t="n">
-        <v>10.8</v>
+        <v>50</v>
       </c>
       <c r="I51" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>-41.12</v>
+        <v>-60.03</v>
       </c>
       <c r="K51" t="n">
-        <v>-156.32</v>
+        <v>126.72</v>
       </c>
       <c r="L51" t="n">
-        <v>161.63</v>
+        <v>140.22</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:30:11</t>
+          <t>06:35:44</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.42</v>
+        <v>4.45</v>
       </c>
       <c r="F52" t="n">
-        <v>6.34</v>
+        <v>12.45</v>
       </c>
       <c r="G52" t="n">
-        <v>120.8</v>
+        <v>120.5</v>
       </c>
       <c r="H52" t="n">
-        <v>5.2</v>
+        <v>40.7</v>
       </c>
       <c r="I52" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-23.22</v>
+        <v>-185.15</v>
       </c>
       <c r="K52" t="n">
-        <v>-146.93</v>
+        <v>-104.06</v>
       </c>
       <c r="L52" t="n">
-        <v>148.75</v>
+        <v>212.39</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:35:11</t>
+          <t>06:39:43</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.98</v>
+        <v>3.73</v>
       </c>
       <c r="F53" t="n">
-        <v>9.550000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="G53" t="n">
-        <v>113.7</v>
+        <v>124.4</v>
       </c>
       <c r="H53" t="n">
-        <v>13.7</v>
+        <v>25.9</v>
       </c>
       <c r="I53" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>141.61</v>
+        <v>156.21</v>
       </c>
       <c r="K53" t="n">
-        <v>-131.69</v>
+        <v>50.84</v>
       </c>
       <c r="L53" t="n">
-        <v>193.37</v>
+        <v>164.27</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:37:21</t>
+          <t>06:41:55</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.47</v>
+        <v>3.81</v>
       </c>
       <c r="F54" t="n">
-        <v>12.03</v>
+        <v>9.81</v>
       </c>
       <c r="G54" t="n">
-        <v>111.6</v>
+        <v>116.7</v>
       </c>
       <c r="H54" t="n">
-        <v>12.5</v>
+        <v>40.6</v>
       </c>
       <c r="I54" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J54" t="n">
-        <v>1.22</v>
+        <v>-217.03</v>
       </c>
       <c r="K54" t="n">
-        <v>170.67</v>
+        <v>71.8</v>
       </c>
       <c r="L54" t="n">
-        <v>170.67</v>
+        <v>228.6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:40:05</t>
+          <t>06:44:35</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="F55" t="n">
-        <v>9.539999999999999</v>
+        <v>10.86</v>
       </c>
       <c r="G55" t="n">
-        <v>127.1</v>
+        <v>116.7</v>
       </c>
       <c r="H55" t="n">
-        <v>8.4</v>
+        <v>53.5</v>
       </c>
       <c r="I55" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>9.279999999999999</v>
+        <v>-49.85</v>
       </c>
       <c r="K55" t="n">
-        <v>69.91</v>
+        <v>-104.21</v>
       </c>
       <c r="L55" t="n">
-        <v>70.52</v>
+        <v>115.52</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:45:01</t>
+          <t>06:49:18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.76</v>
+        <v>4.18</v>
       </c>
       <c r="F56" t="n">
-        <v>9.01</v>
+        <v>11.51</v>
       </c>
       <c r="G56" t="n">
-        <v>115.4</v>
+        <v>123.6</v>
       </c>
       <c r="H56" t="n">
-        <v>6.7</v>
+        <v>41.1</v>
       </c>
       <c r="I56" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>89.95</v>
+        <v>334.13</v>
       </c>
       <c r="K56" t="n">
-        <v>299.92</v>
+        <v>25.67</v>
       </c>
       <c r="L56" t="n">
-        <v>313.12</v>
+        <v>335.11</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:47:34</t>
+          <t>06:50:43</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.18</v>
+        <v>3.69</v>
       </c>
       <c r="F57" t="n">
-        <v>9.44</v>
+        <v>9.66</v>
       </c>
       <c r="G57" t="n">
-        <v>113.4</v>
+        <v>120.9</v>
       </c>
       <c r="H57" t="n">
-        <v>14.9</v>
+        <v>59.9</v>
       </c>
       <c r="I57" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>255.57</v>
+        <v>-63.17</v>
       </c>
       <c r="K57" t="n">
-        <v>-21.55</v>
+        <v>-287.86</v>
       </c>
       <c r="L57" t="n">
-        <v>256.48</v>
+        <v>294.71</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:48:37</t>
+          <t>06:53:15</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.47</v>
+        <v>3.91</v>
       </c>
       <c r="F58" t="n">
-        <v>12.65</v>
+        <v>10.3</v>
       </c>
       <c r="G58" t="n">
-        <v>131.1</v>
+        <v>124.3</v>
       </c>
       <c r="H58" t="n">
-        <v>12.7</v>
+        <v>28.4</v>
       </c>
       <c r="I58" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>-21.54</v>
+        <v>161.94</v>
       </c>
       <c r="K58" t="n">
-        <v>293.48</v>
+        <v>-223.85</v>
       </c>
       <c r="L58" t="n">
-        <v>294.27</v>
+        <v>276.29</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:58:36</t>
+          <t>07:03:49</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.73</v>
+        <v>5.28</v>
       </c>
       <c r="F59" t="n">
-        <v>8.380000000000001</v>
+        <v>12.65</v>
       </c>
       <c r="G59" t="n">
-        <v>117.5</v>
+        <v>136.6</v>
       </c>
       <c r="H59" t="n">
-        <v>14.3</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J59" t="n">
-        <v>-28.85</v>
+        <v>133.35</v>
       </c>
       <c r="K59" t="n">
-        <v>69.45999999999999</v>
+        <v>-12.37</v>
       </c>
       <c r="L59" t="n">
-        <v>75.20999999999999</v>
+        <v>133.92</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:01:04</t>
+          <t>07:05:35</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.5</v>
+        <v>3.96</v>
       </c>
       <c r="F60" t="n">
-        <v>7.32</v>
+        <v>12.39</v>
       </c>
       <c r="G60" t="n">
-        <v>125.4</v>
+        <v>143.7</v>
       </c>
       <c r="H60" t="n">
-        <v>14</v>
+        <v>18.6</v>
       </c>
       <c r="I60" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J60" t="n">
-        <v>64.48999999999999</v>
+        <v>53.33</v>
       </c>
       <c r="K60" t="n">
-        <v>-25.36</v>
+        <v>-26.21</v>
       </c>
       <c r="L60" t="n">
-        <v>69.3</v>
+        <v>59.43</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:02:40</t>
+          <t>07:07:24</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.79</v>
+        <v>3.73</v>
       </c>
       <c r="F61" t="n">
-        <v>11.29</v>
+        <v>9.84</v>
       </c>
       <c r="G61" t="n">
-        <v>128.2</v>
+        <v>116.4</v>
       </c>
       <c r="H61" t="n">
-        <v>15.9</v>
+        <v>7</v>
       </c>
       <c r="I61" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>60.57</v>
+        <v>72.31</v>
       </c>
       <c r="K61" t="n">
-        <v>-65.61</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>89.29000000000001</v>
+        <v>72.81999999999999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:07:50</t>
+          <t>07:12:13</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.52</v>
+        <v>4.47</v>
       </c>
       <c r="F62" t="n">
-        <v>12.16</v>
+        <v>12.65</v>
       </c>
       <c r="G62" t="n">
-        <v>130</v>
+        <v>134.3</v>
       </c>
       <c r="H62" t="n">
-        <v>5.5</v>
+        <v>24.8</v>
       </c>
       <c r="I62" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.49</v>
+        <v>81.06</v>
       </c>
       <c r="K62" t="n">
-        <v>-109.46</v>
+        <v>-21.9</v>
       </c>
       <c r="L62" t="n">
-        <v>109.46</v>
+        <v>83.95999999999999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:10:12</t>
+          <t>07:13:30</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.88</v>
+        <v>3.71</v>
       </c>
       <c r="F63" t="n">
-        <v>11.46</v>
+        <v>12.14</v>
       </c>
       <c r="G63" t="n">
-        <v>121.7</v>
+        <v>117</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>26.8</v>
       </c>
       <c r="I63" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J63" t="n">
-        <v>-63.02</v>
+        <v>-5.39</v>
       </c>
       <c r="K63" t="n">
-        <v>62.53</v>
+        <v>-87.5</v>
       </c>
       <c r="L63" t="n">
-        <v>88.78</v>
+        <v>87.66</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:11:18</t>
+          <t>07:15:11</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.44</v>
+        <v>4.41</v>
       </c>
       <c r="F64" t="n">
-        <v>8.720000000000001</v>
+        <v>12.65</v>
       </c>
       <c r="G64" t="n">
-        <v>117.2</v>
+        <v>128.1</v>
       </c>
       <c r="H64" t="n">
-        <v>6.6</v>
+        <v>21.2</v>
       </c>
       <c r="I64" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J64" t="n">
-        <v>29.61</v>
+        <v>-38.38</v>
       </c>
       <c r="K64" t="n">
-        <v>-102.79</v>
+        <v>-103.24</v>
       </c>
       <c r="L64" t="n">
-        <v>106.97</v>
+        <v>110.14</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:15:19</t>
+          <t>07:19:17</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.45</v>
+        <v>4.25</v>
       </c>
       <c r="F65" t="n">
         <v>12.65</v>
       </c>
       <c r="G65" t="n">
-        <v>114.8</v>
+        <v>129.9</v>
       </c>
       <c r="H65" t="n">
-        <v>7.6</v>
+        <v>43.7</v>
       </c>
       <c r="I65" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J65" t="n">
-        <v>6.24</v>
+        <v>91.09</v>
       </c>
       <c r="K65" t="n">
-        <v>-165.7</v>
+        <v>204.63</v>
       </c>
       <c r="L65" t="n">
-        <v>165.82</v>
+        <v>223.99</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:16:51</t>
+          <t>07:21:39</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.16</v>
+        <v>3.38</v>
       </c>
       <c r="F66" t="n">
-        <v>12.65</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="G66" t="n">
-        <v>134.4</v>
+        <v>129.8</v>
       </c>
       <c r="H66" t="n">
-        <v>13.1</v>
+        <v>35.1</v>
       </c>
       <c r="I66" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>-159.72</v>
+        <v>67.62</v>
       </c>
       <c r="K66" t="n">
-        <v>-42.83</v>
+        <v>-112.68</v>
       </c>
       <c r="L66" t="n">
-        <v>165.36</v>
+        <v>131.41</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:18:29</t>
+          <t>07:23:22</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.69</v>
+        <v>4</v>
       </c>
       <c r="F67" t="n">
-        <v>11.94</v>
+        <v>12.65</v>
       </c>
       <c r="G67" t="n">
-        <v>123.4</v>
+        <v>114.1</v>
       </c>
       <c r="H67" t="n">
-        <v>11.6</v>
+        <v>3.6</v>
       </c>
       <c r="I67" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>74.81</v>
+        <v>-127.38</v>
       </c>
       <c r="K67" t="n">
-        <v>218.38</v>
+        <v>-56.75</v>
       </c>
       <c r="L67" t="n">
-        <v>230.84</v>
+        <v>139.45</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:23:10</t>
+          <t>07:27:34</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.53</v>
+        <v>4.7</v>
       </c>
       <c r="F68" t="n">
-        <v>9.609999999999999</v>
+        <v>12.65</v>
       </c>
       <c r="G68" t="n">
-        <v>117.4</v>
+        <v>121.9</v>
       </c>
       <c r="H68" t="n">
-        <v>13.7</v>
+        <v>36.9</v>
       </c>
       <c r="I68" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J68" t="n">
-        <v>213.84</v>
+        <v>-186.22</v>
       </c>
       <c r="K68" t="n">
-        <v>52.41</v>
+        <v>-191.53</v>
       </c>
       <c r="L68" t="n">
-        <v>220.17</v>
+        <v>267.13</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:24:39</t>
+          <t>07:29:34</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.81</v>
+        <v>4.37</v>
       </c>
       <c r="F69" t="n">
-        <v>9.99</v>
+        <v>12.65</v>
       </c>
       <c r="G69" t="n">
-        <v>136.4</v>
+        <v>137</v>
       </c>
       <c r="H69" t="n">
-        <v>11</v>
+        <v>24.4</v>
       </c>
       <c r="I69" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>-138.47</v>
+        <v>150.04</v>
       </c>
       <c r="K69" t="n">
-        <v>45.45</v>
+        <v>130.02</v>
       </c>
       <c r="L69" t="n">
-        <v>145.74</v>
+        <v>198.54</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:26:05</t>
+          <t>07:31:12</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.24</v>
+        <v>3.79</v>
       </c>
       <c r="F70" t="n">
-        <v>12.65</v>
+        <v>11.1</v>
       </c>
       <c r="G70" t="n">
-        <v>120.4</v>
+        <v>119.4</v>
       </c>
       <c r="H70" t="n">
-        <v>11.4</v>
+        <v>1.1</v>
       </c>
       <c r="I70" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.85</v>
+        <v>226.81</v>
       </c>
       <c r="K70" t="n">
-        <v>-187.34</v>
+        <v>74.72</v>
       </c>
       <c r="L70" t="n">
-        <v>187.34</v>
+        <v>238.8</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:29:39</t>
+          <t>07:36:28</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.06</v>
+        <v>3.01</v>
       </c>
       <c r="F71" t="n">
-        <v>12.17</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="G71" t="n">
-        <v>132.6</v>
+        <v>127.4</v>
       </c>
       <c r="H71" t="n">
-        <v>9.6</v>
+        <v>40</v>
       </c>
       <c r="I71" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>-129.49</v>
+        <v>181.21</v>
       </c>
       <c r="K71" t="n">
-        <v>308.97</v>
+        <v>45.17</v>
       </c>
       <c r="L71" t="n">
-        <v>335.01</v>
+        <v>186.75</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:31:44</t>
+          <t>07:37:21</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.24</v>
+        <v>4.21</v>
       </c>
       <c r="F72" t="n">
-        <v>7.82</v>
+        <v>10.53</v>
       </c>
       <c r="G72" t="n">
-        <v>126.7</v>
+        <v>111.4</v>
       </c>
       <c r="H72" t="n">
-        <v>15.7</v>
+        <v>27.4</v>
       </c>
       <c r="I72" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J72" t="n">
-        <v>76.48999999999999</v>
+        <v>-118.53</v>
       </c>
       <c r="K72" t="n">
-        <v>-214.39</v>
+        <v>-332.38</v>
       </c>
       <c r="L72" t="n">
-        <v>227.63</v>
+        <v>352.88</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:33:02</t>
+          <t>07:38:54</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.5</v>
+        <v>4.11</v>
       </c>
       <c r="F73" t="n">
-        <v>8.449999999999999</v>
+        <v>12.65</v>
       </c>
       <c r="G73" t="n">
-        <v>133.4</v>
+        <v>109.2</v>
       </c>
       <c r="H73" t="n">
-        <v>14.3</v>
+        <v>26.4</v>
       </c>
       <c r="I73" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-27.02</v>
+        <v>208.09</v>
       </c>
       <c r="K73" t="n">
-        <v>-335.86</v>
+        <v>39.15</v>
       </c>
       <c r="L73" t="n">
-        <v>336.94</v>
+        <v>211.74</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:42:44</t>
+          <t>07:52:15</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.41</v>
+        <v>4.23</v>
       </c>
       <c r="F74" t="n">
-        <v>11.07</v>
+        <v>12.65</v>
       </c>
       <c r="G74" t="n">
-        <v>126.5</v>
+        <v>126</v>
       </c>
       <c r="H74" t="n">
-        <v>10.8</v>
+        <v>23.5</v>
       </c>
       <c r="I74" t="n">
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>68.95</v>
+        <v>-60.06</v>
       </c>
       <c r="K74" t="n">
-        <v>-83.02</v>
+        <v>61.05</v>
       </c>
       <c r="L74" t="n">
-        <v>107.92</v>
+        <v>85.64</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:44:55</t>
+          <t>07:53:26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.97</v>
+        <v>4.79</v>
       </c>
       <c r="F75" t="n">
-        <v>11.21</v>
+        <v>12.65</v>
       </c>
       <c r="G75" t="n">
-        <v>129.3</v>
+        <v>127.3</v>
       </c>
       <c r="H75" t="n">
-        <v>7.3</v>
+        <v>83</v>
       </c>
       <c r="I75" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-15.21</v>
+        <v>74.06</v>
       </c>
       <c r="K75" t="n">
-        <v>58.16</v>
+        <v>51.79</v>
       </c>
       <c r="L75" t="n">
-        <v>60.11</v>
+        <v>90.37</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:46:51</t>
+          <t>07:55:33</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.02</v>
+        <v>5.33</v>
       </c>
       <c r="F76" t="n">
-        <v>11.72</v>
+        <v>12.65</v>
       </c>
       <c r="G76" t="n">
-        <v>111.7</v>
+        <v>123.6</v>
       </c>
       <c r="H76" t="n">
-        <v>2.4</v>
+        <v>25.6</v>
       </c>
       <c r="I76" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>-50.56</v>
+        <v>106.94</v>
       </c>
       <c r="K76" t="n">
-        <v>-51.18</v>
+        <v>52.09</v>
       </c>
       <c r="L76" t="n">
-        <v>71.94</v>
+        <v>118.95</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:51:07</t>
+          <t>07:59:46</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.35</v>
+        <v>3.93</v>
       </c>
       <c r="F77" t="n">
-        <v>8.33</v>
+        <v>12.65</v>
       </c>
       <c r="G77" t="n">
-        <v>134.6</v>
+        <v>128.9</v>
       </c>
       <c r="H77" t="n">
-        <v>14.2</v>
+        <v>40.8</v>
       </c>
       <c r="I77" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>-0</v>
+        <v>34.62</v>
       </c>
       <c r="K77" t="n">
-        <v>-92.66</v>
+        <v>102.26</v>
       </c>
       <c r="L77" t="n">
-        <v>92.66</v>
+        <v>107.96</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:52:53</t>
+          <t>08:00:26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="F78" t="n">
-        <v>9.949999999999999</v>
+        <v>9.34</v>
       </c>
       <c r="G78" t="n">
-        <v>122.9</v>
+        <v>124.8</v>
       </c>
       <c r="H78" t="n">
-        <v>11.4</v>
+        <v>47.4</v>
       </c>
       <c r="I78" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J78" t="n">
-        <v>7.96</v>
+        <v>81.39</v>
       </c>
       <c r="K78" t="n">
-        <v>-120.09</v>
+        <v>-70.45999999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>120.35</v>
+        <v>107.65</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:55:22</t>
+          <t>08:02:09</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.53</v>
+        <v>4.53</v>
       </c>
       <c r="F79" t="n">
-        <v>9.42</v>
+        <v>12.64</v>
       </c>
       <c r="G79" t="n">
-        <v>136.3</v>
+        <v>124.8</v>
       </c>
       <c r="H79" t="n">
-        <v>9.4</v>
+        <v>64.3</v>
       </c>
       <c r="I79" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>89.81999999999999</v>
+        <v>-108.87</v>
       </c>
       <c r="K79" t="n">
-        <v>77.31</v>
+        <v>10.94</v>
       </c>
       <c r="L79" t="n">
-        <v>118.51</v>
+        <v>109.42</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:01:42</t>
+          <t>08:07:32</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.18</v>
+        <v>3.91</v>
       </c>
       <c r="F80" t="n">
-        <v>11.28</v>
+        <v>8.27</v>
       </c>
       <c r="G80" t="n">
-        <v>129.6</v>
+        <v>106.8</v>
       </c>
       <c r="H80" t="n">
-        <v>2.7</v>
+        <v>9.1</v>
       </c>
       <c r="I80" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>100.27</v>
+        <v>-162.39</v>
       </c>
       <c r="K80" t="n">
-        <v>68.56</v>
+        <v>-50.8</v>
       </c>
       <c r="L80" t="n">
-        <v>121.46</v>
+        <v>170.15</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:02:42</t>
+          <t>08:09:34</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.97</v>
+        <v>3.2</v>
       </c>
       <c r="F81" t="n">
-        <v>11.32</v>
+        <v>9.66</v>
       </c>
       <c r="G81" t="n">
-        <v>133.4</v>
+        <v>120.4</v>
       </c>
       <c r="H81" t="n">
-        <v>8.300000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="I81" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>12.12</v>
+        <v>-87.48</v>
       </c>
       <c r="K81" t="n">
-        <v>136.38</v>
+        <v>-131.43</v>
       </c>
       <c r="L81" t="n">
-        <v>136.92</v>
+        <v>157.88</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:04:25</t>
+          <t>08:11:58</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="F82" t="n">
-        <v>9.19</v>
+        <v>10.68</v>
       </c>
       <c r="G82" t="n">
-        <v>127.5</v>
+        <v>127.6</v>
       </c>
       <c r="H82" t="n">
-        <v>10.9</v>
+        <v>47.8</v>
       </c>
       <c r="I82" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J82" t="n">
-        <v>-110.14</v>
+        <v>-92.61</v>
       </c>
       <c r="K82" t="n">
-        <v>-32.3</v>
+        <v>119.66</v>
       </c>
       <c r="L82" t="n">
-        <v>114.78</v>
+        <v>151.31</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:08:45</t>
+          <t>08:16:52</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.32</v>
+        <v>3.67</v>
       </c>
       <c r="F83" t="n">
-        <v>12.65</v>
+        <v>8.24</v>
       </c>
       <c r="G83" t="n">
-        <v>106.2</v>
+        <v>120.6</v>
       </c>
       <c r="H83" t="n">
-        <v>9.5</v>
+        <v>41.8</v>
       </c>
       <c r="I83" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>160.06</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="K83" t="n">
-        <v>-61.7</v>
+        <v>-211.55</v>
       </c>
       <c r="L83" t="n">
-        <v>171.54</v>
+        <v>222.23</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:11:15</t>
+          <t>08:19:16</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.32</v>
+        <v>4.43</v>
       </c>
       <c r="F84" t="n">
         <v>12.65</v>
       </c>
       <c r="G84" t="n">
-        <v>131.3</v>
+        <v>120.7</v>
       </c>
       <c r="H84" t="n">
-        <v>15</v>
+        <v>45.2</v>
       </c>
       <c r="I84" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-193.94</v>
+        <v>263.01</v>
       </c>
       <c r="K84" t="n">
-        <v>25.51</v>
+        <v>-56.46</v>
       </c>
       <c r="L84" t="n">
-        <v>195.61</v>
+        <v>269</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:13:13</t>
+          <t>08:21:14</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.62</v>
+        <v>5.08</v>
       </c>
       <c r="F85" t="n">
         <v>12.65</v>
       </c>
       <c r="G85" t="n">
-        <v>145.2</v>
+        <v>133.3</v>
       </c>
       <c r="H85" t="n">
-        <v>8.300000000000001</v>
+        <v>46.9</v>
       </c>
       <c r="I85" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>-83.34999999999999</v>
+        <v>282.87</v>
       </c>
       <c r="K85" t="n">
-        <v>-205.37</v>
+        <v>-118.31</v>
       </c>
       <c r="L85" t="n">
-        <v>221.64</v>
+        <v>306.62</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:16:42</t>
+          <t>08:26:46</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.77</v>
+        <v>4.57</v>
       </c>
       <c r="F86" t="n">
-        <v>10.43</v>
+        <v>11.71</v>
       </c>
       <c r="G86" t="n">
-        <v>119.3</v>
+        <v>125.2</v>
       </c>
       <c r="H86" t="n">
-        <v>10</v>
+        <v>25.3</v>
       </c>
       <c r="I86" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J86" t="n">
-        <v>280.79</v>
+        <v>-44.9</v>
       </c>
       <c r="K86" t="n">
-        <v>121.39</v>
+        <v>-363.13</v>
       </c>
       <c r="L86" t="n">
-        <v>305.9</v>
+        <v>365.89</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:18:12</t>
+          <t>08:28:45</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.14</v>
+        <v>4.74</v>
       </c>
       <c r="F87" t="n">
-        <v>9.16</v>
+        <v>12.65</v>
       </c>
       <c r="G87" t="n">
-        <v>122</v>
+        <v>110.9</v>
       </c>
       <c r="H87" t="n">
-        <v>9.199999999999999</v>
+        <v>37.7</v>
       </c>
       <c r="I87" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J87" t="n">
-        <v>46.05</v>
+        <v>134.27</v>
       </c>
       <c r="K87" t="n">
-        <v>-333.97</v>
+        <v>-79.45999999999999</v>
       </c>
       <c r="L87" t="n">
-        <v>337.13</v>
+        <v>156.02</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:20:10</t>
+          <t>08:29:59</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.82</v>
+        <v>4.85</v>
       </c>
       <c r="F88" t="n">
         <v>12.65</v>
       </c>
       <c r="G88" t="n">
-        <v>105.3</v>
+        <v>113.8</v>
       </c>
       <c r="H88" t="n">
-        <v>2.4</v>
+        <v>40.9</v>
       </c>
       <c r="I88" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>90.48</v>
+        <v>22.62</v>
       </c>
       <c r="K88" t="n">
-        <v>280.37</v>
+        <v>387.37</v>
       </c>
       <c r="L88" t="n">
-        <v>294.61</v>
+        <v>388.03</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-11.xlsx
+++ b/output/2025-07-11.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7</v>
+        <v>3.52</v>
       </c>
       <c r="F14" t="n">
-        <v>10.51</v>
+        <v>7.94</v>
       </c>
       <c r="G14" t="n">
-        <v>120.8</v>
+        <v>120.5</v>
       </c>
       <c r="H14" t="n">
-        <v>56.9</v>
+        <v>56.5</v>
       </c>
       <c r="I14" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>63.81</v>
+        <v>57.55</v>
       </c>
       <c r="K14" t="n">
-        <v>-12.56</v>
+        <v>-47.46</v>
       </c>
       <c r="L14" t="n">
-        <v>65.03</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:46:24</t>
+          <t>04:45:58</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.22</v>
+        <v>3.41</v>
       </c>
       <c r="F15" t="n">
-        <v>7.95</v>
+        <v>10.23</v>
       </c>
       <c r="G15" t="n">
-        <v>127.2</v>
+        <v>133.2</v>
       </c>
       <c r="H15" t="n">
-        <v>77.5</v>
+        <v>62.8</v>
       </c>
       <c r="I15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>19.1</v>
+        <v>-3.21</v>
       </c>
       <c r="K15" t="n">
-        <v>-48.7</v>
+        <v>-66.14</v>
       </c>
       <c r="L15" t="n">
-        <v>52.31</v>
+        <v>66.22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:48:06</t>
+          <t>04:47:26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,28 +709,28 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.4</v>
+        <v>4.01</v>
       </c>
       <c r="F16" t="n">
-        <v>6.58</v>
+        <v>12.2</v>
       </c>
       <c r="G16" t="n">
-        <v>114.1</v>
+        <v>114</v>
       </c>
       <c r="H16" t="n">
-        <v>36.5</v>
+        <v>53.1</v>
       </c>
       <c r="I16" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>20.08</v>
+        <v>50.9</v>
       </c>
       <c r="K16" t="n">
-        <v>-53.4</v>
+        <v>48.86</v>
       </c>
       <c r="L16" t="n">
-        <v>57.05</v>
+        <v>70.56</v>
       </c>
     </row>
     <row r="17">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4.35</v>
+        <v>3.71</v>
       </c>
       <c r="F17" t="n">
-        <v>12.18</v>
+        <v>10.64</v>
       </c>
       <c r="G17" t="n">
-        <v>127.4</v>
+        <v>121.3</v>
       </c>
       <c r="H17" t="n">
-        <v>34.6</v>
+        <v>18.1</v>
       </c>
       <c r="I17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-69.59</v>
+        <v>-123.07</v>
       </c>
       <c r="K17" t="n">
-        <v>71.09</v>
+        <v>-7.12</v>
       </c>
       <c r="L17" t="n">
-        <v>99.48</v>
+        <v>123.27</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:52:43</t>
+          <t>04:52:50</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.26</v>
+        <v>3.65</v>
       </c>
       <c r="F18" t="n">
-        <v>10.07</v>
+        <v>8.32</v>
       </c>
       <c r="G18" t="n">
-        <v>126.7</v>
+        <v>132.8</v>
       </c>
       <c r="H18" t="n">
-        <v>41.1</v>
+        <v>34.9</v>
       </c>
       <c r="I18" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>73.16</v>
+        <v>26.14</v>
       </c>
       <c r="K18" t="n">
-        <v>-63.12</v>
+        <v>-99.43000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>96.62</v>
+        <v>102.81</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:54:46</t>
+          <t>04:53:43</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.87</v>
+        <v>3.75</v>
       </c>
       <c r="F19" t="n">
-        <v>9.880000000000001</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>135.5</v>
+        <v>123.5</v>
       </c>
       <c r="H19" t="n">
-        <v>53.3</v>
+        <v>43.2</v>
       </c>
       <c r="I19" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>25.96</v>
+        <v>28.51</v>
       </c>
       <c r="K19" t="n">
-        <v>-102.37</v>
+        <v>-68.09</v>
       </c>
       <c r="L19" t="n">
-        <v>105.61</v>
+        <v>73.81999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:58:55</t>
+          <t>04:58:46</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>4.05</v>
+        <v>3.53</v>
       </c>
       <c r="F20" t="n">
-        <v>11.33</v>
+        <v>10.5</v>
       </c>
       <c r="G20" t="n">
-        <v>122.2</v>
+        <v>107.2</v>
       </c>
       <c r="H20" t="n">
-        <v>35</v>
+        <v>15.2</v>
       </c>
       <c r="I20" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-52.9</v>
+        <v>-64.58</v>
       </c>
       <c r="K20" t="n">
-        <v>-156.38</v>
+        <v>-113.44</v>
       </c>
       <c r="L20" t="n">
-        <v>165.09</v>
+        <v>130.53</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:01:22</t>
+          <t>04:59:30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>4.48</v>
+        <v>3.6</v>
       </c>
       <c r="F21" t="n">
-        <v>11.61</v>
+        <v>9.43</v>
       </c>
       <c r="G21" t="n">
-        <v>118.5</v>
+        <v>143.6</v>
       </c>
       <c r="H21" t="n">
-        <v>74.2</v>
+        <v>27.2</v>
       </c>
       <c r="I21" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>178.62</v>
+        <v>-156.08</v>
       </c>
       <c r="K21" t="n">
-        <v>109.52</v>
+        <v>-18.55</v>
       </c>
       <c r="L21" t="n">
-        <v>209.52</v>
+        <v>157.17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:02:29</t>
+          <t>05:00:21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>4.37</v>
+        <v>3.76</v>
       </c>
       <c r="F22" t="n">
-        <v>10.58</v>
+        <v>10.46</v>
       </c>
       <c r="G22" t="n">
-        <v>116.2</v>
+        <v>122.1</v>
       </c>
       <c r="H22" t="n">
-        <v>44.3</v>
+        <v>49</v>
       </c>
       <c r="I22" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-31.85</v>
+        <v>-23.75</v>
       </c>
       <c r="K22" t="n">
-        <v>168.33</v>
+        <v>-69.3</v>
       </c>
       <c r="L22" t="n">
-        <v>171.31</v>
+        <v>73.26000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:07:00</t>
+          <t>05:05:03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.37</v>
+        <v>3.69</v>
       </c>
       <c r="F23" t="n">
-        <v>10.31</v>
+        <v>7.53</v>
       </c>
       <c r="G23" t="n">
-        <v>125.8</v>
+        <v>139.1</v>
       </c>
       <c r="H23" t="n">
-        <v>71.09999999999999</v>
+        <v>43.1</v>
       </c>
       <c r="I23" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>116.52</v>
+        <v>-94.59</v>
       </c>
       <c r="K23" t="n">
-        <v>-158.3</v>
+        <v>-179.24</v>
       </c>
       <c r="L23" t="n">
-        <v>196.55</v>
+        <v>202.67</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:08:24</t>
+          <t>05:07:15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.41</v>
+        <v>3.97</v>
       </c>
       <c r="F24" t="n">
-        <v>4.84</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>124.6</v>
+        <v>107.7</v>
       </c>
       <c r="H24" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="I24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J24" t="n">
-        <v>192.43</v>
+        <v>220.32</v>
       </c>
       <c r="K24" t="n">
-        <v>-66.08</v>
+        <v>194.85</v>
       </c>
       <c r="L24" t="n">
-        <v>203.46</v>
+        <v>294.12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:10:38</t>
+          <t>05:08:34</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>4.1</v>
+        <v>4.13</v>
       </c>
       <c r="F25" t="n">
-        <v>9.58</v>
+        <v>11.96</v>
       </c>
       <c r="G25" t="n">
-        <v>114.8</v>
+        <v>128.4</v>
       </c>
       <c r="H25" t="n">
-        <v>16.4</v>
+        <v>55</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J25" t="n">
-        <v>214.07</v>
+        <v>-76.06999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>-42.52</v>
+        <v>321.91</v>
       </c>
       <c r="L25" t="n">
-        <v>218.25</v>
+        <v>330.78</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:15:21</t>
+          <t>05:14:25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.15</v>
+        <v>3.42</v>
       </c>
       <c r="F26" t="n">
-        <v>11.52</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>125.8</v>
+        <v>124.2</v>
       </c>
       <c r="H26" t="n">
-        <v>35.7</v>
+        <v>55.9</v>
       </c>
       <c r="I26" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>-225.52</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>-172.94</v>
+        <v>-229.42</v>
       </c>
       <c r="L26" t="n">
-        <v>284.19</v>
+        <v>241.31</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:16:11</t>
+          <t>05:16:13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.64</v>
+        <v>3.35</v>
       </c>
       <c r="F27" t="n">
-        <v>9.390000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="G27" t="n">
-        <v>130.2</v>
+        <v>124</v>
       </c>
       <c r="H27" t="n">
-        <v>32.4</v>
+        <v>33.7</v>
       </c>
       <c r="I27" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>148.21</v>
+        <v>139.58</v>
       </c>
       <c r="K27" t="n">
-        <v>-119.58</v>
+        <v>-170.76</v>
       </c>
       <c r="L27" t="n">
-        <v>190.44</v>
+        <v>220.55</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:18:24</t>
+          <t>05:17:33</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.96</v>
+        <v>3.89</v>
       </c>
       <c r="F28" t="n">
-        <v>7.01</v>
+        <v>9.52</v>
       </c>
       <c r="G28" t="n">
-        <v>120.9</v>
+        <v>138.4</v>
       </c>
       <c r="H28" t="n">
-        <v>55.9</v>
+        <v>39.8</v>
       </c>
       <c r="I28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>162.23</v>
+        <v>-336.86</v>
       </c>
       <c r="K28" t="n">
-        <v>-148.94</v>
+        <v>4.22</v>
       </c>
       <c r="L28" t="n">
-        <v>220.23</v>
+        <v>336.89</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:28:39</t>
+          <t>05:26:28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.36</v>
+        <v>4.1</v>
       </c>
       <c r="F29" t="n">
-        <v>6.91</v>
+        <v>12.17</v>
       </c>
       <c r="G29" t="n">
-        <v>119.1</v>
+        <v>139.2</v>
       </c>
       <c r="H29" t="n">
-        <v>36.9</v>
+        <v>23.9</v>
       </c>
       <c r="I29" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-51.01</v>
+        <v>8.26</v>
       </c>
       <c r="K29" t="n">
-        <v>12.05</v>
+        <v>86.76000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>52.42</v>
+        <v>87.16</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:30:48</t>
+          <t>05:27:49</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.45</v>
+        <v>3.24</v>
       </c>
       <c r="F30" t="n">
-        <v>10.61</v>
+        <v>9.35</v>
       </c>
       <c r="G30" t="n">
-        <v>135.3</v>
+        <v>124.5</v>
       </c>
       <c r="H30" t="n">
-        <v>22.3</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>0.91</v>
+        <v>34.64</v>
       </c>
       <c r="K30" t="n">
-        <v>-58.26</v>
+        <v>43.56</v>
       </c>
       <c r="L30" t="n">
-        <v>58.27</v>
+        <v>55.66</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:33:08</t>
+          <t>05:29:28</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.01</v>
+        <v>3.61</v>
       </c>
       <c r="F31" t="n">
-        <v>8.9</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>124.7</v>
+        <v>124.2</v>
       </c>
       <c r="H31" t="n">
-        <v>3.7</v>
+        <v>17.4</v>
       </c>
       <c r="I31" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>49.96</v>
+        <v>58.38</v>
       </c>
       <c r="K31" t="n">
-        <v>39.84</v>
+        <v>-51.28</v>
       </c>
       <c r="L31" t="n">
-        <v>63.9</v>
+        <v>77.7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:38:03</t>
+          <t>05:35:33</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.76</v>
+        <v>4.18</v>
       </c>
       <c r="F32" t="n">
-        <v>11.51</v>
+        <v>10.22</v>
       </c>
       <c r="G32" t="n">
-        <v>126.4</v>
+        <v>141.7</v>
       </c>
       <c r="H32" t="n">
-        <v>42.4</v>
+        <v>54.4</v>
       </c>
       <c r="I32" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>9.35</v>
+        <v>-15.15</v>
       </c>
       <c r="K32" t="n">
-        <v>82.31999999999999</v>
+        <v>77.83</v>
       </c>
       <c r="L32" t="n">
-        <v>82.84999999999999</v>
+        <v>79.29000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:38:41</t>
+          <t>05:37:03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.3</v>
+        <v>4.11</v>
       </c>
       <c r="F33" t="n">
-        <v>8.09</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>121.7</v>
+        <v>110.8</v>
       </c>
       <c r="H33" t="n">
-        <v>73.8</v>
+        <v>57.9</v>
       </c>
       <c r="I33" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-46.57</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>73.48999999999999</v>
+        <v>-7.53</v>
       </c>
       <c r="L33" t="n">
-        <v>87.01000000000001</v>
+        <v>91.52</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:40:33</t>
+          <t>05:39:10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.47</v>
+        <v>3.66</v>
       </c>
       <c r="F34" t="n">
-        <v>9.199999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>118.6</v>
+        <v>114</v>
       </c>
       <c r="H34" t="n">
-        <v>64.7</v>
+        <v>13.3</v>
       </c>
       <c r="I34" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>13.79</v>
+        <v>-80.67</v>
       </c>
       <c r="K34" t="n">
-        <v>69.29000000000001</v>
+        <v>-37.37</v>
       </c>
       <c r="L34" t="n">
-        <v>70.65000000000001</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:46:41</t>
+          <t>05:44:30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.8</v>
+        <v>3.66</v>
       </c>
       <c r="F35" t="n">
-        <v>12.65</v>
+        <v>10.02</v>
       </c>
       <c r="G35" t="n">
-        <v>113.2</v>
+        <v>117.1</v>
       </c>
       <c r="H35" t="n">
-        <v>64.59999999999999</v>
+        <v>43</v>
       </c>
       <c r="I35" t="n">
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-17.76</v>
+        <v>-54.22</v>
       </c>
       <c r="K35" t="n">
-        <v>137.14</v>
+        <v>-146.63</v>
       </c>
       <c r="L35" t="n">
-        <v>138.28</v>
+        <v>156.33</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:48:43</t>
+          <t>05:46:53</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.44</v>
+        <v>3.55</v>
       </c>
       <c r="F36" t="n">
-        <v>9.51</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>103.7</v>
+        <v>111</v>
       </c>
       <c r="H36" t="n">
-        <v>27.1</v>
+        <v>38.1</v>
       </c>
       <c r="I36" t="n">
         <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>102.26</v>
+        <v>147.23</v>
       </c>
       <c r="K36" t="n">
-        <v>63.47</v>
+        <v>-12.62</v>
       </c>
       <c r="L36" t="n">
-        <v>120.35</v>
+        <v>147.77</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:51:04</t>
+          <t>05:47:57</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.12</v>
+        <v>3.88</v>
       </c>
       <c r="F37" t="n">
-        <v>12.65</v>
+        <v>10.88</v>
       </c>
       <c r="G37" t="n">
-        <v>132.4</v>
+        <v>128</v>
       </c>
       <c r="H37" t="n">
-        <v>44.6</v>
+        <v>19.2</v>
       </c>
       <c r="I37" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>19.73</v>
+        <v>-15.48</v>
       </c>
       <c r="K37" t="n">
-        <v>82.06999999999999</v>
+        <v>148.87</v>
       </c>
       <c r="L37" t="n">
-        <v>84.41</v>
+        <v>149.67</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:55:22</t>
+          <t>05:51:44</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.92</v>
+        <v>3.87</v>
       </c>
       <c r="F38" t="n">
-        <v>7.99</v>
+        <v>11.11</v>
       </c>
       <c r="G38" t="n">
-        <v>127.2</v>
+        <v>121.2</v>
       </c>
       <c r="H38" t="n">
-        <v>13.3</v>
+        <v>24.9</v>
       </c>
       <c r="I38" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>186.98</v>
+        <v>-118.21</v>
       </c>
       <c r="K38" t="n">
-        <v>-196.43</v>
+        <v>204.23</v>
       </c>
       <c r="L38" t="n">
-        <v>271.19</v>
+        <v>235.98</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:57:16</t>
+          <t>05:53:47</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.24</v>
+        <v>3.99</v>
       </c>
       <c r="F39" t="n">
-        <v>7.16</v>
+        <v>7.26</v>
       </c>
       <c r="G39" t="n">
-        <v>128.6</v>
+        <v>105.9</v>
       </c>
       <c r="H39" t="n">
-        <v>26.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-142.56</v>
+        <v>-5.46</v>
       </c>
       <c r="K39" t="n">
-        <v>-125.85</v>
+        <v>278.61</v>
       </c>
       <c r="L39" t="n">
-        <v>190.16</v>
+        <v>278.66</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:59:26</t>
+          <t>05:55:59</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.95</v>
+        <v>3.66</v>
       </c>
       <c r="F40" t="n">
-        <v>12.65</v>
+        <v>7.82</v>
       </c>
       <c r="G40" t="n">
-        <v>119.5</v>
+        <v>128.7</v>
       </c>
       <c r="H40" t="n">
-        <v>54.5</v>
+        <v>18.5</v>
       </c>
       <c r="I40" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>172.5</v>
+        <v>-42.35</v>
       </c>
       <c r="K40" t="n">
-        <v>-73.12</v>
+        <v>-259.56</v>
       </c>
       <c r="L40" t="n">
-        <v>187.36</v>
+        <v>262.99</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:04:06</t>
+          <t>05:59:40</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.45</v>
+        <v>4.72</v>
       </c>
       <c r="F41" t="n">
-        <v>10.02</v>
+        <v>11.32</v>
       </c>
       <c r="G41" t="n">
-        <v>118.6</v>
+        <v>141.6</v>
       </c>
       <c r="H41" t="n">
-        <v>29.8</v>
+        <v>28.7</v>
       </c>
       <c r="I41" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>137.03</v>
+        <v>-207.95</v>
       </c>
       <c r="K41" t="n">
-        <v>-167.24</v>
+        <v>267.8</v>
       </c>
       <c r="L41" t="n">
-        <v>216.21</v>
+        <v>339.06</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:06:22</t>
+          <t>06:00:51</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.91</v>
+        <v>3.65</v>
       </c>
       <c r="F42" t="n">
-        <v>10.02</v>
+        <v>10.11</v>
       </c>
       <c r="G42" t="n">
-        <v>124.6</v>
+        <v>119.2</v>
       </c>
       <c r="H42" t="n">
-        <v>26.7</v>
+        <v>55.3</v>
       </c>
       <c r="I42" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>96.27</v>
+        <v>256.55</v>
       </c>
       <c r="K42" t="n">
-        <v>-273.49</v>
+        <v>-155.58</v>
       </c>
       <c r="L42" t="n">
-        <v>289.94</v>
+        <v>300.04</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:07:50</t>
+          <t>06:02:34</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.18</v>
+        <v>4.33</v>
       </c>
       <c r="F43" t="n">
-        <v>7.98</v>
+        <v>12.65</v>
       </c>
       <c r="G43" t="n">
-        <v>131.1</v>
+        <v>114.8</v>
       </c>
       <c r="H43" t="n">
-        <v>63.2</v>
+        <v>63.8</v>
       </c>
       <c r="I43" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>-188.86</v>
+        <v>265.77</v>
       </c>
       <c r="K43" t="n">
-        <v>-56.5</v>
+        <v>38.3</v>
       </c>
       <c r="L43" t="n">
-        <v>197.13</v>
+        <v>268.51</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:16:14</t>
+          <t>06:15:08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="F44" t="n">
-        <v>11.79</v>
+        <v>12.65</v>
       </c>
       <c r="G44" t="n">
-        <v>128.7</v>
+        <v>120.9</v>
       </c>
       <c r="H44" t="n">
-        <v>41.1</v>
+        <v>45.3</v>
       </c>
       <c r="I44" t="n">
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>56.71</v>
+        <v>-61.31</v>
       </c>
       <c r="K44" t="n">
-        <v>-15.82</v>
+        <v>28.27</v>
       </c>
       <c r="L44" t="n">
-        <v>58.87</v>
+        <v>67.51000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:18:28</t>
+          <t>06:16:04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.13</v>
+        <v>3.8</v>
       </c>
       <c r="F45" t="n">
-        <v>9.26</v>
+        <v>11.04</v>
       </c>
       <c r="G45" t="n">
-        <v>133.2</v>
+        <v>114.1</v>
       </c>
       <c r="H45" t="n">
-        <v>27.6</v>
+        <v>36.5</v>
       </c>
       <c r="I45" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.27</v>
+        <v>11.09</v>
       </c>
       <c r="K45" t="n">
-        <v>-89</v>
+        <v>-60.11</v>
       </c>
       <c r="L45" t="n">
-        <v>89</v>
+        <v>61.13</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:20:34</t>
+          <t>06:17:25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.92</v>
+        <v>4.65</v>
       </c>
       <c r="F46" t="n">
-        <v>9.99</v>
+        <v>12.65</v>
       </c>
       <c r="G46" t="n">
-        <v>129</v>
+        <v>122.9</v>
       </c>
       <c r="H46" t="n">
-        <v>44.4</v>
+        <v>29.3</v>
       </c>
       <c r="I46" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>58.28</v>
+        <v>81.63</v>
       </c>
       <c r="K46" t="n">
-        <v>-12.58</v>
+        <v>-34.36</v>
       </c>
       <c r="L46" t="n">
-        <v>59.62</v>
+        <v>88.56999999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:24:42</t>
+          <t>06:21:37</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.04</v>
+        <v>4.03</v>
       </c>
       <c r="F47" t="n">
-        <v>11.02</v>
+        <v>12.65</v>
       </c>
       <c r="G47" t="n">
-        <v>119</v>
+        <v>126.7</v>
       </c>
       <c r="H47" t="n">
-        <v>57.9</v>
+        <v>41.1</v>
       </c>
       <c r="I47" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>92.20999999999999</v>
+        <v>81.78</v>
       </c>
       <c r="K47" t="n">
-        <v>55.6</v>
+        <v>-72.88</v>
       </c>
       <c r="L47" t="n">
-        <v>107.67</v>
+        <v>109.54</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:26:41</t>
+          <t>06:23:14</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.3</v>
+        <v>4.18</v>
       </c>
       <c r="F48" t="n">
-        <v>8.35</v>
+        <v>11.27</v>
       </c>
       <c r="G48" t="n">
-        <v>118.5</v>
+        <v>130.4</v>
       </c>
       <c r="H48" t="n">
-        <v>68.40000000000001</v>
+        <v>54.9</v>
       </c>
       <c r="I48" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>120.03</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>-30.59</v>
+        <v>-80.81</v>
       </c>
       <c r="L48" t="n">
-        <v>123.86</v>
+        <v>119.24</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:28:10</t>
+          <t>06:25:02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.94</v>
+        <v>4.17</v>
       </c>
       <c r="F49" t="n">
-        <v>9.199999999999999</v>
+        <v>12.65</v>
       </c>
       <c r="G49" t="n">
-        <v>126.6</v>
+        <v>122.2</v>
       </c>
       <c r="H49" t="n">
-        <v>66.2</v>
+        <v>35</v>
       </c>
       <c r="I49" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>132.09</v>
+        <v>-63.31</v>
       </c>
       <c r="K49" t="n">
-        <v>-30.41</v>
+        <v>-92.53</v>
       </c>
       <c r="L49" t="n">
-        <v>135.54</v>
+        <v>112.12</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:33:27</t>
+          <t>06:28:59</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.9</v>
+        <v>4.78</v>
       </c>
       <c r="F50" t="n">
-        <v>10.85</v>
+        <v>12.65</v>
       </c>
       <c r="G50" t="n">
-        <v>117.2</v>
+        <v>138.8</v>
       </c>
       <c r="H50" t="n">
-        <v>50.2</v>
+        <v>23.2</v>
       </c>
       <c r="I50" t="n">
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-61.48</v>
+        <v>-155</v>
       </c>
       <c r="K50" t="n">
-        <v>-132.77</v>
+        <v>-58.04</v>
       </c>
       <c r="L50" t="n">
-        <v>146.31</v>
+        <v>165.51</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:34:49</t>
+          <t>06:31:05</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.54</v>
+        <v>4.26</v>
       </c>
       <c r="F51" t="n">
-        <v>8.699999999999999</v>
+        <v>11.28</v>
       </c>
       <c r="G51" t="n">
-        <v>118.2</v>
+        <v>126.8</v>
       </c>
       <c r="H51" t="n">
-        <v>50</v>
+        <v>31.6</v>
       </c>
       <c r="I51" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-60.03</v>
+        <v>-3.82</v>
       </c>
       <c r="K51" t="n">
-        <v>126.72</v>
+        <v>115.55</v>
       </c>
       <c r="L51" t="n">
-        <v>140.22</v>
+        <v>115.61</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:35:44</t>
+          <t>06:33:08</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.45</v>
+        <v>3.73</v>
       </c>
       <c r="F52" t="n">
-        <v>12.45</v>
+        <v>9.08</v>
       </c>
       <c r="G52" t="n">
-        <v>120.5</v>
+        <v>126.9</v>
       </c>
       <c r="H52" t="n">
-        <v>40.7</v>
+        <v>59.2</v>
       </c>
       <c r="I52" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-185.15</v>
+        <v>59.48</v>
       </c>
       <c r="K52" t="n">
-        <v>-104.06</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>212.39</v>
+        <v>96.81999999999999</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:39:43</t>
+          <t>06:39:18</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2266,31 +2266,31 @@
         <v>3.73</v>
       </c>
       <c r="F53" t="n">
-        <v>9.779999999999999</v>
+        <v>9.18</v>
       </c>
       <c r="G53" t="n">
-        <v>124.4</v>
+        <v>123.8</v>
       </c>
       <c r="H53" t="n">
-        <v>25.9</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>156.21</v>
+        <v>87.45</v>
       </c>
       <c r="K53" t="n">
-        <v>50.84</v>
+        <v>21.88</v>
       </c>
       <c r="L53" t="n">
-        <v>164.27</v>
+        <v>90.15000000000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:41:55</t>
+          <t>06:41:09</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.81</v>
+        <v>3.9</v>
       </c>
       <c r="F54" t="n">
-        <v>9.81</v>
+        <v>11.77</v>
       </c>
       <c r="G54" t="n">
-        <v>116.7</v>
+        <v>121.4</v>
       </c>
       <c r="H54" t="n">
-        <v>40.6</v>
+        <v>66.3</v>
       </c>
       <c r="I54" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J54" t="n">
-        <v>-217.03</v>
+        <v>154.3</v>
       </c>
       <c r="K54" t="n">
-        <v>71.8</v>
+        <v>-126.2</v>
       </c>
       <c r="L54" t="n">
-        <v>228.6</v>
+        <v>199.33</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:44:35</t>
+          <t>06:42:35</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.69</v>
+        <v>3.64</v>
       </c>
       <c r="F55" t="n">
-        <v>10.86</v>
+        <v>6.64</v>
       </c>
       <c r="G55" t="n">
-        <v>116.7</v>
+        <v>117.7</v>
       </c>
       <c r="H55" t="n">
-        <v>53.5</v>
+        <v>68.7</v>
       </c>
       <c r="I55" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>-49.85</v>
+        <v>42.14</v>
       </c>
       <c r="K55" t="n">
-        <v>-104.21</v>
+        <v>219.69</v>
       </c>
       <c r="L55" t="n">
-        <v>115.52</v>
+        <v>223.7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:49:18</t>
+          <t>06:45:46</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.18</v>
+        <v>3.57</v>
       </c>
       <c r="F56" t="n">
-        <v>11.51</v>
+        <v>7.01</v>
       </c>
       <c r="G56" t="n">
-        <v>123.6</v>
+        <v>124.5</v>
       </c>
       <c r="H56" t="n">
-        <v>41.1</v>
+        <v>39.5</v>
       </c>
       <c r="I56" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>334.13</v>
+        <v>-44.76</v>
       </c>
       <c r="K56" t="n">
-        <v>25.67</v>
+        <v>-243.03</v>
       </c>
       <c r="L56" t="n">
-        <v>335.11</v>
+        <v>247.12</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:50:43</t>
+          <t>06:48:02</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.69</v>
+        <v>3.96</v>
       </c>
       <c r="F57" t="n">
-        <v>9.66</v>
+        <v>11.53</v>
       </c>
       <c r="G57" t="n">
-        <v>120.9</v>
+        <v>121.6</v>
       </c>
       <c r="H57" t="n">
-        <v>59.9</v>
+        <v>46.3</v>
       </c>
       <c r="I57" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-63.17</v>
+        <v>-278.11</v>
       </c>
       <c r="K57" t="n">
-        <v>-287.86</v>
+        <v>187.11</v>
       </c>
       <c r="L57" t="n">
-        <v>294.71</v>
+        <v>335.19</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:53:15</t>
+          <t>06:50:08</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.91</v>
+        <v>3.8</v>
       </c>
       <c r="F58" t="n">
-        <v>10.3</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>124.3</v>
+        <v>115.9</v>
       </c>
       <c r="H58" t="n">
-        <v>28.4</v>
+        <v>32.4</v>
       </c>
       <c r="I58" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>161.94</v>
+        <v>251.65</v>
       </c>
       <c r="K58" t="n">
-        <v>-223.85</v>
+        <v>21.61</v>
       </c>
       <c r="L58" t="n">
-        <v>276.29</v>
+        <v>252.58</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:03:49</t>
+          <t>07:00:50</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>5.28</v>
+        <v>4.29</v>
       </c>
       <c r="F59" t="n">
-        <v>12.65</v>
+        <v>9.82</v>
       </c>
       <c r="G59" t="n">
-        <v>136.6</v>
+        <v>132.5</v>
       </c>
       <c r="H59" t="n">
-        <v>67.90000000000001</v>
+        <v>14.7</v>
       </c>
       <c r="I59" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>133.35</v>
+        <v>26.06</v>
       </c>
       <c r="K59" t="n">
-        <v>-12.37</v>
+        <v>76.65000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>133.92</v>
+        <v>80.95</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:05:35</t>
+          <t>07:02:54</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.96</v>
+        <v>4.01</v>
       </c>
       <c r="F60" t="n">
-        <v>12.39</v>
+        <v>12.5</v>
       </c>
       <c r="G60" t="n">
-        <v>143.7</v>
+        <v>117.1</v>
       </c>
       <c r="H60" t="n">
-        <v>18.6</v>
+        <v>51.6</v>
       </c>
       <c r="I60" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>53.33</v>
+        <v>-12.7</v>
       </c>
       <c r="K60" t="n">
-        <v>-26.21</v>
+        <v>67.28</v>
       </c>
       <c r="L60" t="n">
-        <v>59.43</v>
+        <v>68.47</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:07:24</t>
+          <t>07:04:22</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="F61" t="n">
-        <v>9.84</v>
+        <v>12.45</v>
       </c>
       <c r="G61" t="n">
-        <v>116.4</v>
+        <v>132.8</v>
       </c>
       <c r="H61" t="n">
-        <v>7</v>
+        <v>28.7</v>
       </c>
       <c r="I61" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>72.31</v>
+        <v>-70.55</v>
       </c>
       <c r="K61" t="n">
-        <v>8.550000000000001</v>
+        <v>-11.95</v>
       </c>
       <c r="L61" t="n">
-        <v>72.81999999999999</v>
+        <v>71.55</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:12:13</t>
+          <t>07:09:38</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.47</v>
+        <v>4.42</v>
       </c>
       <c r="F62" t="n">
-        <v>12.65</v>
+        <v>10.25</v>
       </c>
       <c r="G62" t="n">
-        <v>134.3</v>
+        <v>122.1</v>
       </c>
       <c r="H62" t="n">
-        <v>24.8</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I62" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>81.06</v>
+        <v>-146.13</v>
       </c>
       <c r="K62" t="n">
-        <v>-21.9</v>
+        <v>-33.57</v>
       </c>
       <c r="L62" t="n">
-        <v>83.95999999999999</v>
+        <v>149.94</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:13:30</t>
+          <t>07:10:55</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.71</v>
+        <v>4.14</v>
       </c>
       <c r="F63" t="n">
-        <v>12.14</v>
+        <v>12.65</v>
       </c>
       <c r="G63" t="n">
-        <v>117</v>
+        <v>125.2</v>
       </c>
       <c r="H63" t="n">
-        <v>26.8</v>
+        <v>49.8</v>
       </c>
       <c r="I63" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-5.39</v>
+        <v>66.45</v>
       </c>
       <c r="K63" t="n">
-        <v>-87.5</v>
+        <v>-85.06</v>
       </c>
       <c r="L63" t="n">
-        <v>87.66</v>
+        <v>107.94</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:15:11</t>
+          <t>07:12:46</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.41</v>
+        <v>4.77</v>
       </c>
       <c r="F64" t="n">
         <v>12.65</v>
       </c>
       <c r="G64" t="n">
-        <v>128.1</v>
+        <v>138.2</v>
       </c>
       <c r="H64" t="n">
-        <v>21.2</v>
+        <v>33.2</v>
       </c>
       <c r="I64" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>-38.38</v>
+        <v>-19.95</v>
       </c>
       <c r="K64" t="n">
-        <v>-103.24</v>
+        <v>-99.03</v>
       </c>
       <c r="L64" t="n">
-        <v>110.14</v>
+        <v>101.02</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:19:17</t>
+          <t>07:16:36</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="F65" t="n">
-        <v>12.65</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="G65" t="n">
-        <v>129.9</v>
+        <v>126.9</v>
       </c>
       <c r="H65" t="n">
-        <v>43.7</v>
+        <v>21.2</v>
       </c>
       <c r="I65" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>91.09</v>
+        <v>103.06</v>
       </c>
       <c r="K65" t="n">
-        <v>204.63</v>
+        <v>79.94</v>
       </c>
       <c r="L65" t="n">
-        <v>223.99</v>
+        <v>130.43</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:21:39</t>
+          <t>07:18:34</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.38</v>
+        <v>4.32</v>
       </c>
       <c r="F66" t="n">
-        <v>8.210000000000001</v>
+        <v>11.51</v>
       </c>
       <c r="G66" t="n">
-        <v>129.8</v>
+        <v>133.6</v>
       </c>
       <c r="H66" t="n">
-        <v>35.1</v>
+        <v>39.4</v>
       </c>
       <c r="I66" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>67.62</v>
+        <v>118.64</v>
       </c>
       <c r="K66" t="n">
-        <v>-112.68</v>
+        <v>132.7</v>
       </c>
       <c r="L66" t="n">
-        <v>131.41</v>
+        <v>178</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:23:22</t>
+          <t>07:20:48</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4</v>
+        <v>4.57</v>
       </c>
       <c r="F67" t="n">
         <v>12.65</v>
       </c>
       <c r="G67" t="n">
-        <v>114.1</v>
+        <v>128</v>
       </c>
       <c r="H67" t="n">
-        <v>3.6</v>
+        <v>51.1</v>
       </c>
       <c r="I67" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-127.38</v>
+        <v>113.81</v>
       </c>
       <c r="K67" t="n">
-        <v>-56.75</v>
+        <v>-73.94</v>
       </c>
       <c r="L67" t="n">
-        <v>139.45</v>
+        <v>135.72</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:27:34</t>
+          <t>07:24:37</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.7</v>
+        <v>4.51</v>
       </c>
       <c r="F68" t="n">
-        <v>12.65</v>
+        <v>11.09</v>
       </c>
       <c r="G68" t="n">
-        <v>121.9</v>
+        <v>112.5</v>
       </c>
       <c r="H68" t="n">
-        <v>36.9</v>
+        <v>48.7</v>
       </c>
       <c r="I68" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>-186.22</v>
+        <v>42.69</v>
       </c>
       <c r="K68" t="n">
-        <v>-191.53</v>
+        <v>-159.33</v>
       </c>
       <c r="L68" t="n">
-        <v>267.13</v>
+        <v>164.95</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:29:34</t>
+          <t>07:26:29</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.37</v>
+        <v>4.24</v>
       </c>
       <c r="F69" t="n">
         <v>12.65</v>
       </c>
       <c r="G69" t="n">
-        <v>137</v>
+        <v>132.2</v>
       </c>
       <c r="H69" t="n">
-        <v>24.4</v>
+        <v>19.1</v>
       </c>
       <c r="I69" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>150.04</v>
+        <v>-58.45</v>
       </c>
       <c r="K69" t="n">
-        <v>130.02</v>
+        <v>224.59</v>
       </c>
       <c r="L69" t="n">
-        <v>198.54</v>
+        <v>232.07</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:31:12</t>
+          <t>07:27:39</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.79</v>
+        <v>4.34</v>
       </c>
       <c r="F70" t="n">
-        <v>11.1</v>
+        <v>11.52</v>
       </c>
       <c r="G70" t="n">
-        <v>119.4</v>
+        <v>114.9</v>
       </c>
       <c r="H70" t="n">
-        <v>1.1</v>
+        <v>100</v>
       </c>
       <c r="I70" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>226.81</v>
+        <v>210.4</v>
       </c>
       <c r="K70" t="n">
-        <v>74.72</v>
+        <v>15.93</v>
       </c>
       <c r="L70" t="n">
-        <v>238.8</v>
+        <v>211</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:36:28</t>
+          <t>07:32:41</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.01</v>
+        <v>3.54</v>
       </c>
       <c r="F71" t="n">
-        <v>9.220000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="G71" t="n">
-        <v>127.4</v>
+        <v>118.9</v>
       </c>
       <c r="H71" t="n">
-        <v>40</v>
+        <v>59.8</v>
       </c>
       <c r="I71" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>181.21</v>
+        <v>184.36</v>
       </c>
       <c r="K71" t="n">
-        <v>45.17</v>
+        <v>-228.07</v>
       </c>
       <c r="L71" t="n">
-        <v>186.75</v>
+        <v>293.27</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:37:21</t>
+          <t>07:34:49</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.21</v>
+        <v>4.49</v>
       </c>
       <c r="F72" t="n">
-        <v>10.53</v>
+        <v>11.54</v>
       </c>
       <c r="G72" t="n">
-        <v>111.4</v>
+        <v>130.7</v>
       </c>
       <c r="H72" t="n">
-        <v>27.4</v>
+        <v>38.9</v>
       </c>
       <c r="I72" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="J72" t="n">
-        <v>-118.53</v>
+        <v>31.57</v>
       </c>
       <c r="K72" t="n">
-        <v>-332.38</v>
+        <v>-298.48</v>
       </c>
       <c r="L72" t="n">
-        <v>352.88</v>
+        <v>300.15</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:38:54</t>
+          <t>07:36:23</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.11</v>
+        <v>3.48</v>
       </c>
       <c r="F73" t="n">
-        <v>12.65</v>
+        <v>11.39</v>
       </c>
       <c r="G73" t="n">
-        <v>109.2</v>
+        <v>123.8</v>
       </c>
       <c r="H73" t="n">
-        <v>26.4</v>
+        <v>55.1</v>
       </c>
       <c r="I73" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>208.09</v>
+        <v>209.38</v>
       </c>
       <c r="K73" t="n">
-        <v>39.15</v>
+        <v>-87.2</v>
       </c>
       <c r="L73" t="n">
-        <v>211.74</v>
+        <v>226.81</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:52:15</t>
+          <t>07:48:35</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.23</v>
+        <v>4.69</v>
       </c>
       <c r="F74" t="n">
         <v>12.65</v>
       </c>
       <c r="G74" t="n">
-        <v>126</v>
+        <v>120.2</v>
       </c>
       <c r="H74" t="n">
-        <v>23.5</v>
+        <v>49.2</v>
       </c>
       <c r="I74" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-60.06</v>
+        <v>107.5</v>
       </c>
       <c r="K74" t="n">
-        <v>61.05</v>
+        <v>55.06</v>
       </c>
       <c r="L74" t="n">
-        <v>85.64</v>
+        <v>120.78</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:53:26</t>
+          <t>07:49:21</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.79</v>
+        <v>3.98</v>
       </c>
       <c r="F75" t="n">
-        <v>12.65</v>
+        <v>12.49</v>
       </c>
       <c r="G75" t="n">
-        <v>127.3</v>
+        <v>109</v>
       </c>
       <c r="H75" t="n">
-        <v>83</v>
+        <v>60.4</v>
       </c>
       <c r="I75" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>74.06</v>
+        <v>-84.38</v>
       </c>
       <c r="K75" t="n">
-        <v>51.79</v>
+        <v>-3.54</v>
       </c>
       <c r="L75" t="n">
-        <v>90.37</v>
+        <v>84.45999999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:55:33</t>
+          <t>07:51:21</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>5.33</v>
+        <v>3.63</v>
       </c>
       <c r="F76" t="n">
-        <v>12.65</v>
+        <v>10.66</v>
       </c>
       <c r="G76" t="n">
-        <v>123.6</v>
+        <v>124.5</v>
       </c>
       <c r="H76" t="n">
-        <v>25.6</v>
+        <v>50</v>
       </c>
       <c r="I76" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J76" t="n">
-        <v>106.94</v>
+        <v>-13.72</v>
       </c>
       <c r="K76" t="n">
-        <v>52.09</v>
+        <v>-76.91</v>
       </c>
       <c r="L76" t="n">
-        <v>118.95</v>
+        <v>78.13</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:59:46</t>
+          <t>07:56:44</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.93</v>
+        <v>4.21</v>
       </c>
       <c r="F77" t="n">
-        <v>12.65</v>
+        <v>12.03</v>
       </c>
       <c r="G77" t="n">
-        <v>128.9</v>
+        <v>119</v>
       </c>
       <c r="H77" t="n">
-        <v>40.8</v>
+        <v>57.9</v>
       </c>
       <c r="I77" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>34.62</v>
+        <v>84.62</v>
       </c>
       <c r="K77" t="n">
-        <v>102.26</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>107.96</v>
+        <v>120.65</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:00:26</t>
+          <t>07:59:02</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.12</v>
+        <v>3.59</v>
       </c>
       <c r="F78" t="n">
-        <v>9.34</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>124.8</v>
+        <v>118.5</v>
       </c>
       <c r="H78" t="n">
-        <v>47.4</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I78" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>81.39</v>
+        <v>133.41</v>
       </c>
       <c r="K78" t="n">
-        <v>-70.45999999999999</v>
+        <v>-25.08</v>
       </c>
       <c r="L78" t="n">
-        <v>107.65</v>
+        <v>135.75</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:02:09</t>
+          <t>07:59:50</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.53</v>
+        <v>4.22</v>
       </c>
       <c r="F79" t="n">
-        <v>12.64</v>
+        <v>10.51</v>
       </c>
       <c r="G79" t="n">
-        <v>124.8</v>
+        <v>126.6</v>
       </c>
       <c r="H79" t="n">
-        <v>64.3</v>
+        <v>66.2</v>
       </c>
       <c r="I79" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>-108.87</v>
+        <v>158.01</v>
       </c>
       <c r="K79" t="n">
-        <v>10.94</v>
+        <v>-17.05</v>
       </c>
       <c r="L79" t="n">
-        <v>109.42</v>
+        <v>158.93</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:07:32</t>
+          <t>08:05:41</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.91</v>
+        <v>4.18</v>
       </c>
       <c r="F80" t="n">
-        <v>8.27</v>
+        <v>12.15</v>
       </c>
       <c r="G80" t="n">
-        <v>106.8</v>
+        <v>117.2</v>
       </c>
       <c r="H80" t="n">
-        <v>9.1</v>
+        <v>50.2</v>
       </c>
       <c r="I80" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-162.39</v>
+        <v>-106.28</v>
       </c>
       <c r="K80" t="n">
-        <v>-50.8</v>
+        <v>-128.04</v>
       </c>
       <c r="L80" t="n">
-        <v>170.15</v>
+        <v>166.4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:09:34</t>
+          <t>08:07:26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.2</v>
+        <v>3.82</v>
       </c>
       <c r="F81" t="n">
-        <v>9.66</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="G81" t="n">
-        <v>120.4</v>
+        <v>118.2</v>
       </c>
       <c r="H81" t="n">
-        <v>3.9</v>
+        <v>50</v>
       </c>
       <c r="I81" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>-87.48</v>
+        <v>-85.8</v>
       </c>
       <c r="K81" t="n">
-        <v>-131.43</v>
+        <v>132.73</v>
       </c>
       <c r="L81" t="n">
-        <v>157.88</v>
+        <v>158.05</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:11:58</t>
+          <t>08:08:11</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.7</v>
+        <v>4.72</v>
       </c>
       <c r="F82" t="n">
-        <v>10.68</v>
+        <v>12.65</v>
       </c>
       <c r="G82" t="n">
-        <v>127.6</v>
+        <v>120.5</v>
       </c>
       <c r="H82" t="n">
-        <v>47.8</v>
+        <v>40.7</v>
       </c>
       <c r="I82" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>-92.61</v>
+        <v>-226.19</v>
       </c>
       <c r="K82" t="n">
-        <v>119.66</v>
+        <v>-66.36</v>
       </c>
       <c r="L82" t="n">
-        <v>151.31</v>
+        <v>235.72</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:16:52</t>
+          <t>08:14:04</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.67</v>
+        <v>4.01</v>
       </c>
       <c r="F83" t="n">
-        <v>8.24</v>
+        <v>11.06</v>
       </c>
       <c r="G83" t="n">
-        <v>120.6</v>
+        <v>124.4</v>
       </c>
       <c r="H83" t="n">
-        <v>41.8</v>
+        <v>25.9</v>
       </c>
       <c r="I83" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>68.06999999999999</v>
+        <v>174.07</v>
       </c>
       <c r="K83" t="n">
-        <v>-211.55</v>
+        <v>102.02</v>
       </c>
       <c r="L83" t="n">
-        <v>222.23</v>
+        <v>201.76</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:19:16</t>
+          <t>08:16:31</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.43</v>
+        <v>4.09</v>
       </c>
       <c r="F84" t="n">
-        <v>12.65</v>
+        <v>11.11</v>
       </c>
       <c r="G84" t="n">
-        <v>120.7</v>
+        <v>116.7</v>
       </c>
       <c r="H84" t="n">
-        <v>45.2</v>
+        <v>40.6</v>
       </c>
       <c r="I84" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>263.01</v>
+        <v>-258.71</v>
       </c>
       <c r="K84" t="n">
-        <v>-56.46</v>
+        <v>95.20999999999999</v>
       </c>
       <c r="L84" t="n">
-        <v>269</v>
+        <v>275.68</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:21:14</t>
+          <t>08:18:03</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>5.08</v>
+        <v>3.97</v>
       </c>
       <c r="F85" t="n">
-        <v>12.65</v>
+        <v>12.13</v>
       </c>
       <c r="G85" t="n">
-        <v>133.3</v>
+        <v>116.7</v>
       </c>
       <c r="H85" t="n">
-        <v>46.9</v>
+        <v>53.5</v>
       </c>
       <c r="I85" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>282.87</v>
+        <v>-122.18</v>
       </c>
       <c r="K85" t="n">
-        <v>-118.31</v>
+        <v>-97.45</v>
       </c>
       <c r="L85" t="n">
-        <v>306.62</v>
+        <v>156.28</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:26:46</t>
+          <t>08:23:32</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.57</v>
+        <v>4.45</v>
       </c>
       <c r="F86" t="n">
-        <v>11.71</v>
+        <v>12.65</v>
       </c>
       <c r="G86" t="n">
-        <v>125.2</v>
+        <v>123.6</v>
       </c>
       <c r="H86" t="n">
-        <v>25.3</v>
+        <v>41.1</v>
       </c>
       <c r="I86" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>-44.9</v>
+        <v>362.81</v>
       </c>
       <c r="K86" t="n">
-        <v>-363.13</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="L86" t="n">
-        <v>365.89</v>
+        <v>375.77</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:28:45</t>
+          <t>08:25:53</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.74</v>
+        <v>3.97</v>
       </c>
       <c r="F87" t="n">
-        <v>12.65</v>
+        <v>10.93</v>
       </c>
       <c r="G87" t="n">
-        <v>110.9</v>
+        <v>120.9</v>
       </c>
       <c r="H87" t="n">
-        <v>37.7</v>
+        <v>59.9</v>
       </c>
       <c r="I87" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>134.27</v>
+        <v>-153.88</v>
       </c>
       <c r="K87" t="n">
-        <v>-79.45999999999999</v>
+        <v>-309.2</v>
       </c>
       <c r="L87" t="n">
-        <v>156.02</v>
+        <v>345.37</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:29:59</t>
+          <t>08:27:14</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.85</v>
+        <v>4.18</v>
       </c>
       <c r="F88" t="n">
-        <v>12.65</v>
+        <v>11.56</v>
       </c>
       <c r="G88" t="n">
-        <v>113.8</v>
+        <v>124.3</v>
       </c>
       <c r="H88" t="n">
-        <v>40.9</v>
+        <v>28.4</v>
       </c>
       <c r="I88" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>22.62</v>
+        <v>159.5</v>
       </c>
       <c r="K88" t="n">
-        <v>387.37</v>
+        <v>-274.91</v>
       </c>
       <c r="L88" t="n">
-        <v>388.03</v>
+        <v>317.83</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-11.xlsx
+++ b/output/2025-07-11.xlsx
@@ -640,13 +640,13 @@
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.37</v>
+        <v>-2.57</v>
       </c>
       <c r="K14" t="n">
-        <v>-58.08</v>
+        <v>-62.99</v>
       </c>
       <c r="L14" t="n">
-        <v>58.13</v>
+        <v>63.04</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-53.59</v>
+        <v>-50.46</v>
       </c>
       <c r="K15" t="n">
-        <v>84.45999999999999</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>100.03</v>
+        <v>94.19</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-46.61</v>
+        <v>-44.65</v>
       </c>
       <c r="K16" t="n">
-        <v>83.7</v>
+        <v>80.18000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>95.8</v>
+        <v>91.77</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>-36.46</v>
+        <v>-39.17</v>
       </c>
       <c r="K17" t="n">
-        <v>69.73999999999999</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>78.69</v>
+        <v>84.55</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>16.43</v>
+        <v>16.23</v>
       </c>
       <c r="K18" t="n">
-        <v>110.74</v>
+        <v>109.42</v>
       </c>
       <c r="L18" t="n">
-        <v>111.95</v>
+        <v>110.62</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>54.64</v>
+        <v>61.43</v>
       </c>
       <c r="K19" t="n">
-        <v>-21.08</v>
+        <v>-23.7</v>
       </c>
       <c r="L19" t="n">
-        <v>58.57</v>
+        <v>65.84</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.01</v>
+        <v>-2.41</v>
       </c>
       <c r="K20" t="n">
-        <v>-47.47</v>
+        <v>-57.04</v>
       </c>
       <c r="L20" t="n">
-        <v>47.51</v>
+        <v>57.09</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-63.26</v>
+        <v>-64.7</v>
       </c>
       <c r="K21" t="n">
-        <v>-119.95</v>
+        <v>-122.69</v>
       </c>
       <c r="L21" t="n">
-        <v>135.61</v>
+        <v>138.7</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-81.73999999999999</v>
+        <v>-96.29000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-12.57</v>
+        <v>-14.8</v>
       </c>
       <c r="L22" t="n">
-        <v>82.7</v>
+        <v>97.42</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>147.78</v>
+        <v>171.06</v>
       </c>
       <c r="K23" t="n">
-        <v>-63.11</v>
+        <v>-73.05</v>
       </c>
       <c r="L23" t="n">
-        <v>160.69</v>
+        <v>186.01</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-142.5</v>
+        <v>-161.37</v>
       </c>
       <c r="K24" t="n">
-        <v>-82.2</v>
+        <v>-93.09</v>
       </c>
       <c r="L24" t="n">
-        <v>164.5</v>
+        <v>186.29</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>53.01</v>
+        <v>57.08</v>
       </c>
       <c r="K25" t="n">
-        <v>206.1</v>
+        <v>221.94</v>
       </c>
       <c r="L25" t="n">
-        <v>212.8</v>
+        <v>229.17</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-291.13</v>
+        <v>-318.72</v>
       </c>
       <c r="K26" t="n">
-        <v>-40.68</v>
+        <v>-44.53</v>
       </c>
       <c r="L26" t="n">
-        <v>293.96</v>
+        <v>321.81</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-231.37</v>
+        <v>-268.63</v>
       </c>
       <c r="K27" t="n">
-        <v>-70.95999999999999</v>
+        <v>-82.39</v>
       </c>
       <c r="L27" t="n">
-        <v>242.01</v>
+        <v>280.98</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>-84.08</v>
+        <v>-109.31</v>
       </c>
       <c r="K28" t="n">
-        <v>147.7</v>
+        <v>192.02</v>
       </c>
       <c r="L28" t="n">
-        <v>169.96</v>
+        <v>220.96</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>18</v>
       </c>
       <c r="J29" t="n">
-        <v>-89.51000000000001</v>
+        <v>-88.18000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.64</v>
+        <v>-3.58</v>
       </c>
       <c r="L29" t="n">
-        <v>89.58</v>
+        <v>88.25</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>-62.22</v>
+        <v>-63.22</v>
       </c>
       <c r="K30" t="n">
-        <v>15.92</v>
+        <v>16.17</v>
       </c>
       <c r="L30" t="n">
-        <v>64.23</v>
+        <v>65.26000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>50.13</v>
+        <v>51.86</v>
       </c>
       <c r="K31" t="n">
-        <v>-28.41</v>
+        <v>-29.39</v>
       </c>
       <c r="L31" t="n">
-        <v>57.62</v>
+        <v>59.61</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>60.66</v>
+        <v>63.55</v>
       </c>
       <c r="K32" t="n">
-        <v>-49.86</v>
+        <v>-52.24</v>
       </c>
       <c r="L32" t="n">
-        <v>78.52</v>
+        <v>82.27</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-33.55</v>
+        <v>-32.74</v>
       </c>
       <c r="K33" t="n">
-        <v>99.78</v>
+        <v>97.36</v>
       </c>
       <c r="L33" t="n">
-        <v>105.27</v>
+        <v>102.72</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>64.27</v>
+        <v>63.62</v>
       </c>
       <c r="K34" t="n">
-        <v>-64.77</v>
+        <v>-64.12</v>
       </c>
       <c r="L34" t="n">
-        <v>91.23999999999999</v>
+        <v>90.31999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-71.22</v>
+        <v>-78.47</v>
       </c>
       <c r="K35" t="n">
-        <v>-79.09</v>
+        <v>-87.15000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>106.43</v>
+        <v>117.27</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>27.74</v>
+        <v>30.14</v>
       </c>
       <c r="K36" t="n">
-        <v>-103.1</v>
+        <v>-112.01</v>
       </c>
       <c r="L36" t="n">
-        <v>106.77</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>143.47</v>
+        <v>150.14</v>
       </c>
       <c r="K37" t="n">
-        <v>-5.86</v>
+        <v>-6.13</v>
       </c>
       <c r="L37" t="n">
-        <v>143.59</v>
+        <v>150.26</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>20.7</v>
+        <v>22.6</v>
       </c>
       <c r="K38" t="n">
-        <v>-171.15</v>
+        <v>-186.87</v>
       </c>
       <c r="L38" t="n">
-        <v>172.39</v>
+        <v>188.23</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>131.86</v>
+        <v>153.08</v>
       </c>
       <c r="K39" t="n">
-        <v>10.19</v>
+        <v>11.83</v>
       </c>
       <c r="L39" t="n">
-        <v>132.26</v>
+        <v>153.54</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>125.17</v>
+        <v>144.63</v>
       </c>
       <c r="K40" t="n">
-        <v>86.45</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>152.12</v>
+        <v>175.78</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>-158.6</v>
+        <v>-184.27</v>
       </c>
       <c r="K41" t="n">
-        <v>-192.97</v>
+        <v>-224.2</v>
       </c>
       <c r="L41" t="n">
-        <v>249.78</v>
+        <v>290.21</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>-19.48</v>
+        <v>-23.82</v>
       </c>
       <c r="K42" t="n">
-        <v>185.45</v>
+        <v>226.68</v>
       </c>
       <c r="L42" t="n">
-        <v>186.47</v>
+        <v>227.93</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>225.29</v>
+        <v>257.14</v>
       </c>
       <c r="K43" t="n">
-        <v>-76.31999999999999</v>
+        <v>-87.11</v>
       </c>
       <c r="L43" t="n">
-        <v>237.87</v>
+        <v>271.49</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>26.39</v>
+        <v>29.12</v>
       </c>
       <c r="K44" t="n">
-        <v>45.07</v>
+        <v>49.73</v>
       </c>
       <c r="L44" t="n">
-        <v>52.23</v>
+        <v>57.62</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="K45" t="n">
-        <v>63.02</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>63.02</v>
+        <v>65.48999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>-68.59999999999999</v>
+        <v>-70.29000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>21.04</v>
+        <v>21.56</v>
       </c>
       <c r="L46" t="n">
-        <v>71.76000000000001</v>
+        <v>73.52</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-93.41</v>
+        <v>-93.28</v>
       </c>
       <c r="K47" t="n">
-        <v>-47.24</v>
+        <v>-47.17</v>
       </c>
       <c r="L47" t="n">
-        <v>104.67</v>
+        <v>104.53</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-57.58</v>
+        <v>-58.53</v>
       </c>
       <c r="K48" t="n">
-        <v>56.55</v>
+        <v>57.47</v>
       </c>
       <c r="L48" t="n">
-        <v>80.70999999999999</v>
+        <v>82.03</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>26.76</v>
+        <v>30.54</v>
       </c>
       <c r="K49" t="n">
-        <v>37.46</v>
+        <v>42.74</v>
       </c>
       <c r="L49" t="n">
-        <v>46.03</v>
+        <v>52.53</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>102.97</v>
+        <v>112.06</v>
       </c>
       <c r="K50" t="n">
-        <v>90.13</v>
+        <v>98.09</v>
       </c>
       <c r="L50" t="n">
-        <v>136.84</v>
+        <v>148.93</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-46.31</v>
+        <v>-49.7</v>
       </c>
       <c r="K51" t="n">
-        <v>-129.99</v>
+        <v>-139.52</v>
       </c>
       <c r="L51" t="n">
-        <v>137.99</v>
+        <v>148.11</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>-29.32</v>
+        <v>-30.7</v>
       </c>
       <c r="K52" t="n">
-        <v>-125.8</v>
+        <v>-131.74</v>
       </c>
       <c r="L52" t="n">
-        <v>129.17</v>
+        <v>135.27</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>92.45</v>
+        <v>107.61</v>
       </c>
       <c r="K53" t="n">
-        <v>-115.3</v>
+        <v>-134.2</v>
       </c>
       <c r="L53" t="n">
-        <v>147.79</v>
+        <v>172.02</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-36.77</v>
+        <v>-44.19</v>
       </c>
       <c r="K54" t="n">
-        <v>139.69</v>
+        <v>167.86</v>
       </c>
       <c r="L54" t="n">
-        <v>144.44</v>
+        <v>173.58</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>-52.45</v>
+        <v>-65.16</v>
       </c>
       <c r="K55" t="n">
-        <v>100.58</v>
+        <v>124.97</v>
       </c>
       <c r="L55" t="n">
-        <v>113.43</v>
+        <v>140.94</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>27.96</v>
+        <v>34.85</v>
       </c>
       <c r="K56" t="n">
-        <v>241.4</v>
+        <v>300.88</v>
       </c>
       <c r="L56" t="n">
-        <v>243.02</v>
+        <v>302.89</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>193.81</v>
+        <v>252.14</v>
       </c>
       <c r="K57" t="n">
-        <v>-19.38</v>
+        <v>-25.21</v>
       </c>
       <c r="L57" t="n">
-        <v>194.77</v>
+        <v>253.4</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>-49.03</v>
+        <v>-62.17</v>
       </c>
       <c r="K58" t="n">
-        <v>217.92</v>
+        <v>276.32</v>
       </c>
       <c r="L58" t="n">
-        <v>223.37</v>
+        <v>283.23</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>-25.95</v>
+        <v>-26.85</v>
       </c>
       <c r="K59" t="n">
-        <v>59.49</v>
+        <v>61.55</v>
       </c>
       <c r="L59" t="n">
-        <v>64.91</v>
+        <v>67.15000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>57.19</v>
+        <v>58.7</v>
       </c>
       <c r="K60" t="n">
-        <v>-22.42</v>
+        <v>-23.01</v>
       </c>
       <c r="L60" t="n">
-        <v>61.43</v>
+        <v>63.05</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>48.61</v>
+        <v>49.77</v>
       </c>
       <c r="K61" t="n">
-        <v>-53.29</v>
+        <v>-54.56</v>
       </c>
       <c r="L61" t="n">
-        <v>72.13</v>
+        <v>73.84999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-2.57</v>
+        <v>-2.61</v>
       </c>
       <c r="K62" t="n">
-        <v>-97.31</v>
+        <v>-98.62</v>
       </c>
       <c r="L62" t="n">
-        <v>97.34999999999999</v>
+        <v>98.66</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-56.96</v>
+        <v>-58.11</v>
       </c>
       <c r="K63" t="n">
-        <v>56.73</v>
+        <v>57.88</v>
       </c>
       <c r="L63" t="n">
-        <v>80.39</v>
+        <v>82.02</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>25.48</v>
+        <v>25.43</v>
       </c>
       <c r="K64" t="n">
-        <v>-94.92</v>
+        <v>-94.70999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>98.28</v>
+        <v>98.06999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>-11.43</v>
+        <v>-12.6</v>
       </c>
       <c r="K65" t="n">
-        <v>-128.44</v>
+        <v>-141.51</v>
       </c>
       <c r="L65" t="n">
-        <v>128.95</v>
+        <v>142.07</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-151.27</v>
+        <v>-161.25</v>
       </c>
       <c r="K66" t="n">
-        <v>-29.41</v>
+        <v>-31.35</v>
       </c>
       <c r="L66" t="n">
-        <v>154.1</v>
+        <v>164.27</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>51.73</v>
+        <v>52.62</v>
       </c>
       <c r="K67" t="n">
-        <v>188.76</v>
+        <v>192.02</v>
       </c>
       <c r="L67" t="n">
-        <v>195.72</v>
+        <v>199.1</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>180.58</v>
+        <v>208.81</v>
       </c>
       <c r="K68" t="n">
-        <v>59.66</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="L68" t="n">
-        <v>190.18</v>
+        <v>219.91</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>-125.63</v>
+        <v>-148.23</v>
       </c>
       <c r="K69" t="n">
-        <v>66.37</v>
+        <v>78.31</v>
       </c>
       <c r="L69" t="n">
-        <v>142.08</v>
+        <v>167.64</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>-37.27</v>
+        <v>-44</v>
       </c>
       <c r="K70" t="n">
-        <v>-135.38</v>
+        <v>-159.8</v>
       </c>
       <c r="L70" t="n">
-        <v>140.42</v>
+        <v>165.75</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>-127.52</v>
+        <v>-144.54</v>
       </c>
       <c r="K71" t="n">
-        <v>280.7</v>
+        <v>318.18</v>
       </c>
       <c r="L71" t="n">
-        <v>308.31</v>
+        <v>349.47</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>27.64</v>
+        <v>32.66</v>
       </c>
       <c r="K72" t="n">
-        <v>-169.47</v>
+        <v>-200.23</v>
       </c>
       <c r="L72" t="n">
-        <v>171.71</v>
+        <v>202.88</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-43.22</v>
+        <v>-47.81</v>
       </c>
       <c r="K73" t="n">
-        <v>-244.59</v>
+        <v>-270.57</v>
       </c>
       <c r="L73" t="n">
-        <v>248.38</v>
+        <v>274.76</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>55.98</v>
+        <v>53.5</v>
       </c>
       <c r="K74" t="n">
-        <v>-67.7</v>
+        <v>-64.7</v>
       </c>
       <c r="L74" t="n">
-        <v>87.84</v>
+        <v>83.95</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-14.13</v>
+        <v>-15.82</v>
       </c>
       <c r="K75" t="n">
-        <v>49.57</v>
+        <v>55.52</v>
       </c>
       <c r="L75" t="n">
-        <v>51.54</v>
+        <v>57.73</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-42.88</v>
+        <v>-45.9</v>
       </c>
       <c r="K76" t="n">
-        <v>-41.25</v>
+        <v>-44.16</v>
       </c>
       <c r="L76" t="n">
-        <v>59.5</v>
+        <v>63.69</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-2.58</v>
+        <v>-2.7</v>
       </c>
       <c r="K77" t="n">
-        <v>-85.55</v>
+        <v>-89.70999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>85.59</v>
+        <v>89.75</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>5.61</v>
+        <v>5.37</v>
       </c>
       <c r="K78" t="n">
-        <v>-115.49</v>
+        <v>-110.49</v>
       </c>
       <c r="L78" t="n">
-        <v>115.63</v>
+        <v>110.62</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>73.89</v>
+        <v>73.87</v>
       </c>
       <c r="K79" t="n">
-        <v>66.89</v>
+        <v>66.87</v>
       </c>
       <c r="L79" t="n">
-        <v>99.67</v>
+        <v>99.64</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>64.83</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>79.39</v>
+        <v>93.54000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>102.5</v>
+        <v>120.78</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.29</v>
+        <v>-0.32</v>
       </c>
       <c r="K81" t="n">
-        <v>113.91</v>
+        <v>125.48</v>
       </c>
       <c r="L81" t="n">
-        <v>113.91</v>
+        <v>125.48</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-90.65000000000001</v>
+        <v>-103.79</v>
       </c>
       <c r="K82" t="n">
-        <v>-11.01</v>
+        <v>-12.61</v>
       </c>
       <c r="L82" t="n">
-        <v>91.31999999999999</v>
+        <v>104.55</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>127.67</v>
+        <v>150.76</v>
       </c>
       <c r="K83" t="n">
-        <v>-62.34</v>
+        <v>-73.61</v>
       </c>
       <c r="L83" t="n">
-        <v>142.08</v>
+        <v>167.78</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-181.72</v>
+        <v>-201.85</v>
       </c>
       <c r="K84" t="n">
-        <v>38.45</v>
+        <v>42.71</v>
       </c>
       <c r="L84" t="n">
-        <v>185.74</v>
+        <v>206.32</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-80.09999999999999</v>
+        <v>-99.12</v>
       </c>
       <c r="K85" t="n">
-        <v>-126.53</v>
+        <v>-156.57</v>
       </c>
       <c r="L85" t="n">
-        <v>149.75</v>
+        <v>185.31</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>224.55</v>
+        <v>251.99</v>
       </c>
       <c r="K86" t="n">
-        <v>121.31</v>
+        <v>136.13</v>
       </c>
       <c r="L86" t="n">
-        <v>255.22</v>
+        <v>286.41</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>6.88</v>
+        <v>8.06</v>
       </c>
       <c r="K87" t="n">
-        <v>-251.46</v>
+        <v>-294.3</v>
       </c>
       <c r="L87" t="n">
-        <v>251.56</v>
+        <v>294.41</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>16.99</v>
+        <v>22.21</v>
       </c>
       <c r="K88" t="n">
-        <v>240.01</v>
+        <v>313.81</v>
       </c>
       <c r="L88" t="n">
-        <v>240.61</v>
+        <v>314.59</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-11.xlsx
+++ b/output/2025-07-11.xlsx
@@ -640,13 +640,13 @@
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.57</v>
+        <v>-2.81</v>
       </c>
       <c r="K14" t="n">
-        <v>-62.99</v>
+        <v>-68.76000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>63.04</v>
+        <v>68.81999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-50.46</v>
+        <v>-56.77</v>
       </c>
       <c r="K15" t="n">
-        <v>79.54000000000001</v>
+        <v>89.48</v>
       </c>
       <c r="L15" t="n">
-        <v>94.19</v>
+        <v>105.97</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-44.65</v>
+        <v>-53.51</v>
       </c>
       <c r="K16" t="n">
-        <v>80.18000000000001</v>
+        <v>96.09</v>
       </c>
       <c r="L16" t="n">
-        <v>91.77</v>
+        <v>109.98</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>-39.17</v>
+        <v>-44.72</v>
       </c>
       <c r="K17" t="n">
-        <v>74.93000000000001</v>
+        <v>85.55</v>
       </c>
       <c r="L17" t="n">
-        <v>84.55</v>
+        <v>96.53</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>16.23</v>
+        <v>19.35</v>
       </c>
       <c r="K18" t="n">
-        <v>109.42</v>
+        <v>130.45</v>
       </c>
       <c r="L18" t="n">
-        <v>110.62</v>
+        <v>131.87</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>61.43</v>
+        <v>63.39</v>
       </c>
       <c r="K19" t="n">
-        <v>-23.7</v>
+        <v>-24.46</v>
       </c>
       <c r="L19" t="n">
-        <v>65.84</v>
+        <v>67.94</v>
       </c>
     </row>
     <row r="20">
@@ -1270,13 +1270,13 @@
         <v>18</v>
       </c>
       <c r="J29" t="n">
-        <v>-88.18000000000001</v>
+        <v>-99</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.58</v>
+        <v>-4.02</v>
       </c>
       <c r="L29" t="n">
-        <v>88.25</v>
+        <v>99.08</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>-63.22</v>
+        <v>-67.42</v>
       </c>
       <c r="K30" t="n">
-        <v>16.17</v>
+        <v>17.25</v>
       </c>
       <c r="L30" t="n">
-        <v>65.26000000000001</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>51.86</v>
+        <v>55.63</v>
       </c>
       <c r="K31" t="n">
-        <v>-29.39</v>
+        <v>-31.52</v>
       </c>
       <c r="L31" t="n">
-        <v>59.61</v>
+        <v>63.94</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>63.55</v>
+        <v>68.11</v>
       </c>
       <c r="K32" t="n">
-        <v>-52.24</v>
+        <v>-55.99</v>
       </c>
       <c r="L32" t="n">
-        <v>82.27</v>
+        <v>88.17</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-32.74</v>
+        <v>-37.96</v>
       </c>
       <c r="K33" t="n">
-        <v>97.36</v>
+        <v>112.89</v>
       </c>
       <c r="L33" t="n">
-        <v>102.72</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>63.62</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>-64.12</v>
+        <v>-68.02</v>
       </c>
       <c r="L34" t="n">
-        <v>90.31999999999999</v>
+        <v>95.83</v>
       </c>
     </row>
     <row r="35">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>29.12</v>
+        <v>36.8</v>
       </c>
       <c r="K44" t="n">
-        <v>49.73</v>
+        <v>62.85</v>
       </c>
       <c r="L44" t="n">
-        <v>57.62</v>
+        <v>72.83</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>0.63</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>65.48999999999999</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>65.48999999999999</v>
+        <v>83.95999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>-70.29000000000001</v>
+        <v>-82.19</v>
       </c>
       <c r="K46" t="n">
-        <v>21.56</v>
+        <v>25.21</v>
       </c>
       <c r="L46" t="n">
-        <v>73.52</v>
+        <v>85.97</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-93.28</v>
+        <v>-107.32</v>
       </c>
       <c r="K47" t="n">
-        <v>-47.17</v>
+        <v>-54.27</v>
       </c>
       <c r="L47" t="n">
-        <v>104.53</v>
+        <v>120.26</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-58.53</v>
+        <v>-63.19</v>
       </c>
       <c r="K48" t="n">
-        <v>57.47</v>
+        <v>62.05</v>
       </c>
       <c r="L48" t="n">
-        <v>82.03</v>
+        <v>88.56</v>
       </c>
     </row>
     <row r="49">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>-26.85</v>
+        <v>-30.64</v>
       </c>
       <c r="K59" t="n">
-        <v>61.55</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>67.15000000000001</v>
+        <v>76.63</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>58.7</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>-23.01</v>
+        <v>-30.72</v>
       </c>
       <c r="L60" t="n">
-        <v>63.05</v>
+        <v>84.16</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>49.77</v>
+        <v>57.49</v>
       </c>
       <c r="K61" t="n">
-        <v>-54.56</v>
+        <v>-63.03</v>
       </c>
       <c r="L61" t="n">
-        <v>73.84999999999999</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-2.61</v>
+        <v>-3.24</v>
       </c>
       <c r="K62" t="n">
-        <v>-98.62</v>
+        <v>-122.58</v>
       </c>
       <c r="L62" t="n">
-        <v>98.66</v>
+        <v>122.63</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-58.11</v>
+        <v>-65.44</v>
       </c>
       <c r="K63" t="n">
-        <v>57.88</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>82.02</v>
+        <v>92.36</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>25.43</v>
+        <v>26.82</v>
       </c>
       <c r="K64" t="n">
-        <v>-94.70999999999999</v>
+        <v>-99.91</v>
       </c>
       <c r="L64" t="n">
-        <v>98.06999999999999</v>
+        <v>103.45</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>53.5</v>
+        <v>57.27</v>
       </c>
       <c r="K74" t="n">
-        <v>-64.7</v>
+        <v>-69.26000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>83.95</v>
+        <v>89.88</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-15.82</v>
+        <v>-18.96</v>
       </c>
       <c r="K75" t="n">
-        <v>55.52</v>
+        <v>66.53</v>
       </c>
       <c r="L75" t="n">
-        <v>57.73</v>
+        <v>69.18000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-45.9</v>
+        <v>-55.57</v>
       </c>
       <c r="K76" t="n">
-        <v>-44.16</v>
+        <v>-53.47</v>
       </c>
       <c r="L76" t="n">
-        <v>63.69</v>
+        <v>77.12</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-2.7</v>
+        <v>-3.27</v>
       </c>
       <c r="K77" t="n">
-        <v>-89.70999999999999</v>
+        <v>-108.62</v>
       </c>
       <c r="L77" t="n">
-        <v>89.75</v>
+        <v>108.67</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>5.37</v>
+        <v>6.29</v>
       </c>
       <c r="K78" t="n">
-        <v>-110.49</v>
+        <v>-129.5</v>
       </c>
       <c r="L78" t="n">
-        <v>110.62</v>
+        <v>129.65</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>73.87</v>
+        <v>78.94</v>
       </c>
       <c r="K79" t="n">
-        <v>66.87</v>
+        <v>71.45</v>
       </c>
       <c r="L79" t="n">
-        <v>99.64</v>
+        <v>106.48</v>
       </c>
     </row>
     <row r="80">
